--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>33491</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>42805</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>17042</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>3189</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -62796,19 +62796,19 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>2492</v>
+        <v>36852</v>
       </c>
       <c r="C2715" t="n">
         <v>2.70000004768372</v>
       </c>
       <c r="D2715" t="n">
-        <v>2.66000008583069</v>
+        <v>2.65000009536743</v>
       </c>
       <c r="E2715" t="n">
-        <v>2.66000008583069</v>
+        <v>2.65000009536743</v>
       </c>
       <c r="F2715" t="n">
         <v>2.67000007629395</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>19028</v>
+        <v>2492</v>
       </c>
       <c r="C2716" t="n">
-        <v>2.6800000667572</v>
+        <v>2.70000004768372</v>
       </c>
       <c r="D2716" t="n">
-        <v>2.61999988555908</v>
+        <v>2.66000008583069</v>
       </c>
       <c r="E2716" t="n">
-        <v>2.65000009536743</v>
+        <v>2.66000008583069</v>
       </c>
       <c r="F2716" t="n">
-        <v>2.6800000667572</v>
+        <v>2.67000007629395</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>15469</v>
+        <v>19028</v>
       </c>
       <c r="C2717" t="n">
-        <v>2.67000007629395</v>
+        <v>2.6800000667572</v>
       </c>
       <c r="D2717" t="n">
         <v>2.61999988555908</v>
       </c>
       <c r="E2717" t="n">
-        <v>2.66000008583069</v>
+        <v>2.65000009536743</v>
       </c>
       <c r="F2717" t="n">
-        <v>2.66000008583069</v>
+        <v>2.6800000667572</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,19 +62865,19 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>5819</v>
+        <v>15469</v>
       </c>
       <c r="C2718" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="E2718" t="n">
         <v>2.66000008583069</v>
-      </c>
-      <c r="D2718" t="n">
-        <v>2.63000011444092</v>
-      </c>
-      <c r="E2718" t="n">
-        <v>2.65000009536743</v>
       </c>
       <c r="F2718" t="n">
         <v>2.66000008583069</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>33491</v>
+        <v>5819</v>
       </c>
       <c r="C2719" t="n">
-        <v>2.67000007629395</v>
+        <v>2.66000008583069</v>
       </c>
       <c r="D2719" t="n">
-        <v>2.61999988555908</v>
+        <v>2.63000011444092</v>
       </c>
       <c r="E2719" t="n">
-        <v>2.63000011444092</v>
+        <v>2.65000009536743</v>
       </c>
       <c r="F2719" t="n">
-        <v>2.67000007629395</v>
+        <v>2.66000008583069</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>42805</v>
+        <v>33491</v>
       </c>
       <c r="C2720" t="n">
         <v>2.67000007629395</v>
       </c>
       <c r="D2720" t="n">
-        <v>2.54999995231628</v>
+        <v>2.61999988555908</v>
       </c>
       <c r="E2720" t="n">
         <v>2.63000011444092</v>
       </c>
       <c r="F2720" t="n">
-        <v>2.66000008583069</v>
+        <v>2.67000007629395</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>17042</v>
+        <v>42805</v>
       </c>
       <c r="C2721" t="n">
-        <v>2.69000005722046</v>
+        <v>2.67000007629395</v>
       </c>
       <c r="D2721" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E2721" t="n">
         <v>2.63000011444092</v>
       </c>
-      <c r="E2721" t="n">
-        <v>2.64000010490417</v>
-      </c>
       <c r="F2721" t="n">
-        <v>2.69000005722046</v>
+        <v>2.66000008583069</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>3189</v>
+        <v>17042</v>
       </c>
       <c r="C2722" t="n">
         <v>2.69000005722046</v>
       </c>
       <c r="D2722" t="n">
-        <v>2.66000008583069</v>
+        <v>2.63000011444092</v>
       </c>
       <c r="E2722" t="n">
-        <v>2.6800000667572</v>
+        <v>2.64000010490417</v>
       </c>
       <c r="F2722" t="n">
-        <v>2.66000008583069</v>
+        <v>2.69000005722046</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>28231</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -421,7 +421,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>0.859297633171082</v>
+        <v>0.859297692775726</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G9" t="n">
-        <v>0.859297633171082</v>
+        <v>0.859297692775726</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G13" t="n">
-        <v>0.802303493022919</v>
+        <v>0.802303433418274</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G15" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>0.929499983787537</v>
       </c>
       <c r="G16" t="n">
-        <v>0.815017521381378</v>
+        <v>0.815017461776733</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>0.908999979496002</v>
       </c>
       <c r="G20" t="n">
-        <v>0.797042429447174</v>
+        <v>0.797042369842529</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>0.899500012397766</v>
       </c>
       <c r="G22" t="n">
-        <v>0.788712501525879</v>
+        <v>0.788712441921234</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G23" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G24" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G25" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.844500005245209</v>
       </c>
       <c r="G28" t="n">
-        <v>0.740486562252045</v>
+        <v>0.740486621856689</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>0.841499984264374</v>
       </c>
       <c r="G34" t="n">
-        <v>0.737856090068817</v>
+        <v>0.737856149673462</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>0.854499995708466</v>
       </c>
       <c r="G38" t="n">
-        <v>0.749254941940308</v>
+        <v>0.749255001544952</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.806500017642975</v>
       </c>
       <c r="G39" t="n">
-        <v>0.707166969776154</v>
+        <v>0.707166910171509</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G42" t="n">
-        <v>0.770737409591675</v>
+        <v>0.77073734998703</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>0.929000020027161</v>
       </c>
       <c r="G48" t="n">
-        <v>0.814579129219055</v>
+        <v>0.8145791888237</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G49" t="n">
-        <v>0.810194969177246</v>
+        <v>0.810194909572601</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.916499972343445</v>
       </c>
       <c r="G51" t="n">
-        <v>0.803618669509888</v>
+        <v>0.803618729114532</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G52" t="n">
-        <v>0.806249141693115</v>
+        <v>0.80624920129776</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G53" t="n">
-        <v>0.809318125247955</v>
+        <v>0.809318065643311</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G56" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G57" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G58" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G59" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G60" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G64" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>0.854499995708466</v>
       </c>
       <c r="G68" t="n">
-        <v>0.749254941940308</v>
+        <v>0.749255001544952</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G71" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092126369476</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G73" t="n">
-        <v>0.770737409591675</v>
+        <v>0.77073734998703</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>0.865499973297119</v>
       </c>
       <c r="G74" t="n">
-        <v>0.758900046348572</v>
+        <v>0.758900105953217</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G76" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G80" t="n">
-        <v>0.753200769424438</v>
+        <v>0.753200709819794</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G85" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>0.877499997615814</v>
       </c>
       <c r="G86" t="n">
-        <v>0.769422173500061</v>
+        <v>0.769422113895416</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G89" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G90" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G91" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G97" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G98" t="n">
-        <v>0.770737409591675</v>
+        <v>0.77073734998703</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G99" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G100" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G102" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G103" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G107" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>0.876500010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>0.768545269966125</v>
+        <v>0.76854532957077</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G113" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>0.897499978542328</v>
       </c>
       <c r="G121" t="n">
-        <v>0.786958754062653</v>
+        <v>0.786958813667297</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G122" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G125" t="n">
-        <v>0.64841902256012</v>
+        <v>0.648418962955475</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G127" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930814266205</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>0.795499980449677</v>
       </c>
       <c r="G129" t="n">
-        <v>0.6975217461586</v>
+        <v>0.697521686553955</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G135" t="n">
-        <v>0.687438130378723</v>
+        <v>0.687438189983368</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>0.791000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>0.693575978279114</v>
+        <v>0.693576037883759</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G146" t="n">
-        <v>0.709359049797058</v>
+        <v>0.709358990192413</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>0.819500029087067</v>
       </c>
       <c r="G153" t="n">
-        <v>0.718565821647644</v>
+        <v>0.718565762042999</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>0.800999999046326</v>
       </c>
       <c r="G159" t="n">
-        <v>0.702344298362732</v>
+        <v>0.702344238758087</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>0.80349999666214</v>
       </c>
       <c r="G164" t="n">
-        <v>0.704536378383636</v>
+        <v>0.704536318778992</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G167" t="n">
-        <v>0.697083353996277</v>
+        <v>0.697083413600922</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G169" t="n">
-        <v>0.695329666137695</v>
+        <v>0.695329606533051</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>0.791000008583069</v>
       </c>
       <c r="G170" t="n">
-        <v>0.693575978279114</v>
+        <v>0.693576037883759</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>0.808499991893768</v>
       </c>
       <c r="G171" t="n">
-        <v>0.70892059803009</v>
+        <v>0.708920538425446</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G175" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930814266205</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G181" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930814266205</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>0.769500017166138</v>
       </c>
       <c r="G190" t="n">
-        <v>0.674723982810974</v>
+        <v>0.674724042415619</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>0.769500017166138</v>
       </c>
       <c r="G191" t="n">
-        <v>0.674723982810974</v>
+        <v>0.674724042415619</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G192" t="n">
-        <v>0.670778214931488</v>
+        <v>0.670778274536133</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G194" t="n">
-        <v>0.654118359088898</v>
+        <v>0.654118418693542</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>0.640089154243469</v>
+        <v>0.640089094638824</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>0.716499984264374</v>
       </c>
       <c r="G199" t="n">
-        <v>0.628251731395721</v>
+        <v>0.628251791000366</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G201" t="n">
-        <v>0.626936495304108</v>
+        <v>0.626936554908752</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G206" t="n">
-        <v>0.613784074783325</v>
+        <v>0.61378401517868</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G207" t="n">
-        <v>0.613784074783325</v>
+        <v>0.61378401517868</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G211" t="n">
-        <v>0.60764616727829</v>
+        <v>0.607646226882935</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G212" t="n">
-        <v>0.613784074783325</v>
+        <v>0.61378401517868</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G213" t="n">
-        <v>0.613784074783325</v>
+        <v>0.61378401517868</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>0.607207715511322</v>
+        <v>0.607207775115967</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>0.607207715511322</v>
+        <v>0.607207775115967</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G218" t="n">
-        <v>0.610276639461517</v>
+        <v>0.610276699066162</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G219" t="n">
-        <v>0.613784074783325</v>
+        <v>0.61378401517868</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>0.689499974250793</v>
       </c>
       <c r="G220" t="n">
-        <v>0.60457718372345</v>
+        <v>0.604577243328094</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G222" t="n">
-        <v>0.587479054927826</v>
+        <v>0.587478995323181</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G224" t="n">
-        <v>0.596247315406799</v>
+        <v>0.596247375011444</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G225" t="n">
-        <v>0.587479054927826</v>
+        <v>0.587478995323181</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>0.669000029563904</v>
       </c>
       <c r="G228" t="n">
-        <v>0.58660215139389</v>
+        <v>0.586602210998535</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G231" t="n">
-        <v>0.614222407341003</v>
+        <v>0.614222526550293</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G234" t="n">
-        <v>0.61816817522049</v>
+        <v>0.618168115615845</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>0.611153662204742</v>
+        <v>0.611153602600098</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G237" t="n">
-        <v>0.605892479419708</v>
+        <v>0.605892539024353</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G238" t="n">
-        <v>0.605892479419708</v>
+        <v>0.605892539024353</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G239" t="n">
-        <v>0.594493687152863</v>
+        <v>0.594493627548218</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G241" t="n">
-        <v>0.595370531082153</v>
+        <v>0.595370590686798</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G242" t="n">
-        <v>0.596247315406799</v>
+        <v>0.596247375011444</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G243" t="n">
-        <v>0.598000943660736</v>
+        <v>0.598001003265381</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G245" t="n">
-        <v>0.609399855136871</v>
+        <v>0.609399914741516</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>0.699500024318695</v>
       </c>
       <c r="G254" t="n">
-        <v>0.613345682621002</v>
+        <v>0.613345623016357</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G257" t="n">
-        <v>0.644473195075989</v>
+        <v>0.644473254680634</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>0.768999993801117</v>
       </c>
       <c r="G258" t="n">
-        <v>0.674285650253296</v>
+        <v>0.674285590648651</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>0.771499991416931</v>
       </c>
       <c r="G263" t="n">
-        <v>0.676477611064911</v>
+        <v>0.676477670669556</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G265" t="n">
-        <v>0.669901490211487</v>
+        <v>0.669901430606842</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G266" t="n">
-        <v>0.671655058860779</v>
+        <v>0.671655118465424</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G272" t="n">
-        <v>0.671655058860779</v>
+        <v>0.671655118465424</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>0.769500017166138</v>
       </c>
       <c r="G280" t="n">
-        <v>0.674723982810974</v>
+        <v>0.674724042415619</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G282" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930814266205</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G284" t="n">
-        <v>0.670778214931488</v>
+        <v>0.670778274536133</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G290" t="n">
-        <v>0.670778214931488</v>
+        <v>0.670778274536133</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>0.819500029087067</v>
       </c>
       <c r="G304" t="n">
-        <v>0.718565821647644</v>
+        <v>0.718565762042999</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G328" t="n">
-        <v>0.723388373851776</v>
+        <v>0.723388314247131</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G329" t="n">
-        <v>0.723388373851776</v>
+        <v>0.723388314247131</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G337" t="n">
-        <v>0.723388373851776</v>
+        <v>0.723388314247131</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>0.813000023365021</v>
       </c>
       <c r="G340" t="n">
-        <v>0.712866306304932</v>
+        <v>0.712866365909576</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G344" t="n">
-        <v>0.716373682022095</v>
+        <v>0.71637362241745</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>0.8125</v>
       </c>
       <c r="G345" t="n">
-        <v>0.712427854537964</v>
+        <v>0.712427914142609</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>0.813000023365021</v>
       </c>
       <c r="G349" t="n">
-        <v>0.712866306304932</v>
+        <v>0.712866365909576</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>0.8125</v>
       </c>
       <c r="G351" t="n">
-        <v>0.712427854537964</v>
+        <v>0.712427914142609</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>0.811500012874603</v>
       </c>
       <c r="G352" t="n">
-        <v>0.711551129817963</v>
+        <v>0.711551070213318</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>0.819500029087067</v>
       </c>
       <c r="G357" t="n">
-        <v>0.718565821647644</v>
+        <v>0.718565762042999</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>0.823499977588654</v>
       </c>
       <c r="G360" t="n">
-        <v>0.722073018550873</v>
+        <v>0.722073078155518</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G365" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G370" t="n">
-        <v>0.89086377620697</v>
+        <v>0.890863716602325</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G371" t="n">
-        <v>0.887356221675873</v>
+        <v>0.887356281280518</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G372" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.05099999904633</v>
       </c>
       <c r="G373" t="n">
-        <v>0.921552896499634</v>
+        <v>0.921552836894989</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G374" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G376" t="n">
-        <v>0.936459183692932</v>
+        <v>0.936459064483643</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G379" t="n">
-        <v>0.965394616127014</v>
+        <v>0.965394496917725</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G380" t="n">
-        <v>0.965394616127014</v>
+        <v>0.965394496917725</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G381" t="n">
-        <v>0.965394616127014</v>
+        <v>0.965394496917725</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G382" t="n">
-        <v>0.965394616127014</v>
+        <v>0.965394496917725</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G383" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G385" t="n">
-        <v>1.01888132095337</v>
+        <v>1.01888155937195</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G388" t="n">
-        <v>1.05307805538177</v>
+        <v>1.05307817459106</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G389" t="n">
-        <v>1.05921590328217</v>
+        <v>1.05921578407288</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G391" t="n">
-        <v>1.055708527565</v>
+        <v>1.05570864677429</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G395" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G396" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G397" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G398" t="n">
-        <v>1.055708527565</v>
+        <v>1.05570864677429</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G399" t="n">
-        <v>1.05132448673248</v>
+        <v>1.05132436752319</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G400" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G404" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G405" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G406" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G408" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G409" t="n">
-        <v>1.05921590328217</v>
+        <v>1.05921578407288</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G411" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G412" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G414" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G415" t="n">
-        <v>1.05307805538177</v>
+        <v>1.05307817459106</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G416" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G417" t="n">
-        <v>1.053955078125</v>
+        <v>1.05395495891571</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G418" t="n">
-        <v>1.053955078125</v>
+        <v>1.05395495891571</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G419" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G420" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G421" t="n">
-        <v>1.04606342315674</v>
+        <v>1.04606330394745</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G422" t="n">
-        <v>1.055708527565</v>
+        <v>1.05570864677429</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G423" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G424" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G425" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G426" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G427" t="n">
-        <v>1.055708527565</v>
+        <v>1.05570864677429</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G428" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.5</v>
       </c>
       <c r="G429" t="n">
-        <v>1.31525158882141</v>
+        <v>1.31525146961212</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G431" t="n">
-        <v>1.13988447189331</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G434" t="n">
-        <v>1.17671167850494</v>
+        <v>1.17671155929565</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G435" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.26699995994568</v>
       </c>
       <c r="G441" t="n">
-        <v>1.11094903945923</v>
+        <v>1.11094915866852</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G444" t="n">
-        <v>1.14163827896118</v>
+        <v>1.14163839817047</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G445" t="n">
-        <v>1.16794335842133</v>
+        <v>1.16794347763062</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303707122803</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>1.3289999961853</v>
       </c>
       <c r="G450" t="n">
-        <v>1.16531276702881</v>
+        <v>1.1653128862381</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G453" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.34099996089935</v>
       </c>
       <c r="G454" t="n">
-        <v>1.17583465576172</v>
+        <v>1.17583477497101</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G457" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G458" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G459" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G460" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G468" t="n">
-        <v>1.21441543102264</v>
+        <v>1.21441555023193</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G469" t="n">
-        <v>1.2091543674469</v>
+        <v>1.20915448665619</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G470" t="n">
-        <v>1.2074009180069</v>
+        <v>1.20740079879761</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G471" t="n">
-        <v>1.19424843788147</v>
+        <v>1.19424831867218</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G473" t="n">
-        <v>1.21353876590729</v>
+        <v>1.213538646698</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G475" t="n">
-        <v>1.1924946308136</v>
+        <v>1.19249475002289</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G478" t="n">
-        <v>1.1924946308136</v>
+        <v>1.19249475002289</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G479" t="n">
-        <v>1.19074106216431</v>
+        <v>1.1907411813736</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>1.33200001716614</v>
       </c>
       <c r="G481" t="n">
-        <v>1.16794335842133</v>
+        <v>1.16794347763062</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.13988447189331</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G490" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G494" t="n">
-        <v>1.18723368644714</v>
+        <v>1.18723380565643</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G497" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.3289999961853</v>
       </c>
       <c r="G501" t="n">
-        <v>1.16531276702881</v>
+        <v>1.1653128862381</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G503" t="n">
-        <v>1.14163827896118</v>
+        <v>1.14163839817047</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.29299998283386</v>
       </c>
       <c r="G506" t="n">
-        <v>1.1337468624115</v>
+        <v>1.13374674320221</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G508" t="n">
-        <v>1.13988447189331</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G509" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G512" t="n">
-        <v>1.13988447189331</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303707122803</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G514" t="n">
-        <v>1.13988447189331</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G517" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G518" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G520" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G523" t="n">
-        <v>1.26702570915222</v>
+        <v>1.26702582836151</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G524" t="n">
-        <v>1.25387299060822</v>
+        <v>1.2538731098175</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G525" t="n">
-        <v>1.23633635044098</v>
+        <v>1.23633623123169</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G527" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G529" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G530" t="n">
-        <v>1.25387299060822</v>
+        <v>1.2538731098175</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G531" t="n">
-        <v>1.25387299060822</v>
+        <v>1.2538731098175</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G532" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G534" t="n">
-        <v>1.21441543102264</v>
+        <v>1.21441555023193</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>1.21441543102264</v>
+        <v>1.21441555023193</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>1.18811058998108</v>
+        <v>1.18811047077179</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G540" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G543" t="n">
-        <v>1.1924946308136</v>
+        <v>1.19249475002289</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>1.17057383060455</v>
+        <v>1.17057394981384</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G548" t="n">
-        <v>1.21879971027374</v>
+        <v>1.21879982948303</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G552" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G554" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G559" t="n">
-        <v>1.17057383060455</v>
+        <v>1.17057394981384</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>1.18811058998108</v>
+        <v>1.18811047077179</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G561" t="n">
-        <v>1.1924946308136</v>
+        <v>1.19249475002289</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G562" t="n">
-        <v>1.18811058998108</v>
+        <v>1.18811047077179</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G565" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G567" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G569" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G571" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G572" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G573" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303707122803</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303707122803</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G575" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G576" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G577" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303707122803</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303707122803</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G579" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G581" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303707122803</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>1.13988447189331</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G590" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>1.13988447189331</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G594" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>1.13988447189331</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G596" t="n">
-        <v>1.13988447189331</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G597" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G601" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G602" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303707122803</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G609" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G611" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G612" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G613" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>1.13988447189331</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G618" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G620" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G631" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G632" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G633" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G636" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G638" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G640" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G648" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G649" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G650" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G652" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G654" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G656" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>1.07850635051727</v>
+        <v>1.07850623130798</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G672" t="n">
-        <v>1.08727467060089</v>
+        <v>1.0872745513916</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G673" t="n">
-        <v>1.07850635051727</v>
+        <v>1.07850623130798</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G674" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G675" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973814964294</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G676" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973814964294</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G677" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973814964294</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G678" t="n">
-        <v>1.04343283176422</v>
+        <v>1.04343295097351</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G679" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G680" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973814964294</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G684" t="n">
-        <v>1.07850635051727</v>
+        <v>1.07850623130798</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>1.07850635051727</v>
+        <v>1.07850623130798</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G686" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973814964294</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G695" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>1.08727467060089</v>
+        <v>1.0872745513916</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G702" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G707" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G709" t="n">
-        <v>1.12673211097717</v>
+        <v>1.12673223018646</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G710" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G726" t="n">
-        <v>1.09165871143341</v>
+        <v>1.0916588306427</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G727" t="n">
-        <v>1.08727467060089</v>
+        <v>1.0872745513916</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G728" t="n">
-        <v>1.08727467060089</v>
+        <v>1.0872745513916</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G730" t="n">
-        <v>1.08727467060089</v>
+        <v>1.0872745513916</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G731" t="n">
-        <v>1.09165871143341</v>
+        <v>1.0916588306427</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G733" t="n">
-        <v>1.09165871143341</v>
+        <v>1.0916588306427</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G734" t="n">
-        <v>1.09165871143341</v>
+        <v>1.0916588306427</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G735" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G736" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G737" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G741" t="n">
-        <v>1.03466463088989</v>
+        <v>1.0346645116806</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G742" t="n">
-        <v>1.03466463088989</v>
+        <v>1.0346645116806</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G743" t="n">
-        <v>1.03466463088989</v>
+        <v>1.0346645116806</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G744" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.02151191234589</v>
+        <v>1.02151203155518</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G753" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G756" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G764" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G766" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G769" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G771" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G772" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G773" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G774" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G775" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G776" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G780" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G781" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G782" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G783" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G784" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G790" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G791" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G792" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G793" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G798" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G800" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G802" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G805" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G806" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G807" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G808" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G815" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G817" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G818" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G819" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G820" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G821" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G823" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G825" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G829" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G830" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G832" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G833" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G834" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G835" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G843" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G844" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G845" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G846" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G863" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G864" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G865" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G866" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G872" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G876" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G877" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G878" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G879" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G880" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G881" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G883" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G884" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G885" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G889" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G891" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G892" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G893" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G894" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G895" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G896" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G897" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G899" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G900" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G901" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G902" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G905" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G906" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G909" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G915" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G916" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G917" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G918" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G919" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G924" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G929" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G931" t="n">
-        <v>0.907523572444916</v>
+        <v>0.907523453235626</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G934" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G935" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G936" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G937" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G938" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G939" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G944" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G945" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G946" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G947" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G948" t="n">
-        <v>0.942597031593323</v>
+        <v>0.942596971988678</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G949" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G950" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G951" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G952" t="n">
-        <v>0.93382865190506</v>
+        <v>0.933828592300415</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G953" t="n">
-        <v>0.93382865190506</v>
+        <v>0.933828592300415</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G954" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G955" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G956" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G957" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G958" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G959" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G960" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G961" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G962" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G963" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G964" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G965" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G966" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G967" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G968" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G969" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G970" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G971" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G972" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G973" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G974" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G975" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G976" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G977" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G978" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G979" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G980" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G987" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G989" t="n">
-        <v>0.942597031593323</v>
+        <v>0.942596971988678</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G990" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G991" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G993" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G994" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G995" t="n">
-        <v>0.942597031593323</v>
+        <v>0.942596971988678</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G996" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G997" t="n">
-        <v>0.93382865190506</v>
+        <v>0.933828592300415</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G998" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G999" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.93382865190506</v>
+        <v>0.933828592300415</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.93382865190506</v>
+        <v>0.933828592300415</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.942597031593323</v>
+        <v>0.942596971988678</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1018" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.942597031593323</v>
+        <v>0.942596971988678</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1036" t="n">
-        <v>0.942597031593323</v>
+        <v>0.942596971988678</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1037" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.894370973110199</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1041" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1042" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.894370973110199</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1044" t="n">
-        <v>0.898755192756653</v>
+        <v>0.898755252361298</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.894370973110199</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.875080645084381</v>
+        <v>0.875080704689026</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.864558696746826</v>
+        <v>0.864558637142181</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.75</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.638335347175598</v>
+        <v>0.638335406780243</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.720757782459259</v>
+        <v>0.720757842063904</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.752323806285858</v>
+        <v>0.752323865890503</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.752323806285858</v>
+        <v>0.752323865890503</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092126369476</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.752323806285858</v>
+        <v>0.752323865890503</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.741801857948303</v>
+        <v>0.741801798343658</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.740048170089722</v>
+        <v>0.740048229694366</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.741801857948303</v>
+        <v>0.741801798343658</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.720757782459259</v>
+        <v>0.720757842063904</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.703221142292023</v>
+        <v>0.703221201896667</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.706728458404541</v>
+        <v>0.706728518009186</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930814266205</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.671655058860779</v>
+        <v>0.671655118465424</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>0.75</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>0.75</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.655872106552124</v>
+        <v>0.655872046947479</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.680423438549042</v>
+        <v>0.680423498153687</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.680423438549042</v>
+        <v>0.680423498153687</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.671655058860779</v>
+        <v>0.671655118465424</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.671655058860779</v>
+        <v>0.671655118465424</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.668147802352905</v>
+        <v>0.66814786195755</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.668147802352905</v>
+        <v>0.66814786195755</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.720757782459259</v>
+        <v>0.720757842063904</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.752323806285858</v>
+        <v>0.752323865890503</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.687438130378723</v>
+        <v>0.687438189983368</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>0.75</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.661133110523224</v>
+        <v>0.661133170127869</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930814266205</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>0.75</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>0.75</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.650611102581024</v>
+        <v>0.650611042976379</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.669901490211487</v>
+        <v>0.669901430606842</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.669901490211487</v>
+        <v>0.669901430606842</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.669901490211487</v>
+        <v>0.669901430606842</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.669901490211487</v>
+        <v>0.669901430606842</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930814266205</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930814266205</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930814266205</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.661133110523224</v>
+        <v>0.661133170127869</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.650611102581024</v>
+        <v>0.650611042976379</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.661133110523224</v>
+        <v>0.661133170127869</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.640089154243469</v>
+        <v>0.640089094638824</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>0.75</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.655872106552124</v>
+        <v>0.655872046947479</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.654118359088898</v>
+        <v>0.654118418693542</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.654118359088898</v>
+        <v>0.654118418693542</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.650611102581024</v>
+        <v>0.650611042976379</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.720757782459259</v>
+        <v>0.720757842063904</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.703221142292023</v>
+        <v>0.703221201896667</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.80844122171402</v>
+        <v>0.808441281318665</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092126369476</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.762845873832703</v>
+        <v>0.762845814228058</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092126369476</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.757584869861603</v>
+        <v>0.757584929466248</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092126369476</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092126369476</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092126369476</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092126369476</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.757584869861603</v>
+        <v>0.757584929466248</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.775121629238129</v>
+        <v>0.775121569633484</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.789150834083557</v>
+        <v>0.789150893688202</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>0.924000024795532</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.810194969177246</v>
+        <v>0.810194909572601</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.845268309116364</v>
+        <v>0.845268249511719</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.854036629199982</v>
+        <v>0.854036688804626</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.845268309116364</v>
+        <v>0.845268249511719</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.845268309116364</v>
+        <v>0.845268249511719</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.848775625228882</v>
+        <v>0.848775565624237</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.829485297203064</v>
+        <v>0.829485237598419</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.845268309116364</v>
+        <v>0.845268249511719</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.848775625228882</v>
+        <v>0.848775565624237</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.829485297203064</v>
+        <v>0.829485237598419</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.894370973110199</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.894370973110199</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.881218552589417</v>
+        <v>0.881218492984772</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.894370973110199</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.907523572444916</v>
+        <v>0.907523453235626</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.898755192756653</v>
+        <v>0.898755252361298</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.907523572444916</v>
+        <v>0.907523453235626</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.894370973110199</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1433" t="n">
-        <v>0.898755192756653</v>
+        <v>0.898755252361298</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.881218552589417</v>
+        <v>0.881218492984772</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.881218552589417</v>
+        <v>0.881218492984772</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.894370973110199</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.881218552589417</v>
+        <v>0.881218492984772</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.875080645084381</v>
+        <v>0.875080704689026</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.881218552589417</v>
+        <v>0.881218492984772</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.894370973110199</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.898755192756653</v>
+        <v>0.898755252361298</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.942597031593323</v>
+        <v>0.942596971988678</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1477" t="n">
-        <v>1.07412219047546</v>
+        <v>1.07412207126617</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.03466463088989</v>
+        <v>1.0346645116806</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1480" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973814964294</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.07412219047546</v>
+        <v>1.07412207126617</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.04343283176422</v>
+        <v>1.04343295097351</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.03466463088989</v>
+        <v>1.0346645116806</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.03466463088989</v>
+        <v>1.0346645116806</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.03904867172241</v>
+        <v>1.03904855251312</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.03466463088989</v>
+        <v>1.0346645116806</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.04343283176422</v>
+        <v>1.04343295097351</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.03904867172241</v>
+        <v>1.03904855251312</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973814964294</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1501" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.999590992927551</v>
+        <v>0.999591112136841</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.93382865190506</v>
+        <v>0.933828592300415</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.93382865190506</v>
+        <v>0.933828592300415</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.942597031593323</v>
+        <v>0.942596971988678</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1567" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.859297633171082</v>
+        <v>0.859297692775726</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.938212811946869</v>
+        <v>0.938212752342224</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.93382865190506</v>
+        <v>0.933828592300415</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1580" t="n">
-        <v>0.93382865190506</v>
+        <v>0.933828592300415</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1581" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444253444672</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676052570343</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1585" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1632" t="n">
-        <v>1.01784527301788</v>
+        <v>1.01784539222717</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.954792737960815</v>
+        <v>0.954792857170105</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1641" t="n">
-        <v>0.968304097652435</v>
+        <v>0.968304216861725</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1645" t="n">
-        <v>0.954792737960815</v>
+        <v>0.954792857170105</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.936777949333191</v>
+        <v>0.936777830123901</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1649" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.963800489902496</v>
+        <v>0.963800370693207</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.936777949333191</v>
+        <v>0.936777830123901</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1661" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918762922286987</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.914259195327759</v>
+        <v>0.914259254932404</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.914259195327759</v>
+        <v>0.914259254932404</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.932274281978607</v>
+        <v>0.932274222373962</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.954792737960815</v>
+        <v>0.954792857170105</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918762922286987</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.936777949333191</v>
+        <v>0.936777830123901</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1676" t="n">
-        <v>0.968304097652435</v>
+        <v>0.968304216861725</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1679" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918762922286987</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.936777949333191</v>
+        <v>0.936777830123901</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1681" t="n">
-        <v>0.932274281978607</v>
+        <v>0.932274222373962</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.936777949333191</v>
+        <v>0.936777830123901</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1685" t="n">
-        <v>0.914259195327759</v>
+        <v>0.914259254932404</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918762922286987</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.914259195327759</v>
+        <v>0.914259254932404</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.914259195327759</v>
+        <v>0.914259254932404</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.914259195327759</v>
+        <v>0.914259254932404</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1692" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1694" t="n">
-        <v>0.914259195327759</v>
+        <v>0.914259254932404</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.914259195327759</v>
+        <v>0.914259254932404</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.914259195327759</v>
+        <v>0.914259254932404</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.853909075260162</v>
+        <v>0.853909134864807</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.882733047008514</v>
+        <v>0.882733106613159</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.875527083873749</v>
+        <v>0.875527024269104</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G1721" t="n">
-        <v>0.875527083873749</v>
+        <v>0.875527024269104</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.879130005836487</v>
+        <v>0.879130065441132</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.866519570350647</v>
+        <v>0.866519629955292</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.866519570350647</v>
+        <v>0.866519629955292</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G1735" t="n">
-        <v>0.866519570350647</v>
+        <v>0.866519629955292</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.866519570350647</v>
+        <v>0.866519629955292</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1756" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.853909075260162</v>
+        <v>0.853909134864807</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.853909075260162</v>
+        <v>0.853909134864807</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.882733047008514</v>
+        <v>0.882733106613159</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.882733047008514</v>
+        <v>0.882733106613159</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.875527083873749</v>
+        <v>0.875527024269104</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.875527083873749</v>
+        <v>0.875527024269104</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1771" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1783" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1784" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1788" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1789" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G1793" t="n">
-        <v>0.866519570350647</v>
+        <v>0.866519629955292</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1804" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918762922286987</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1805" t="n">
-        <v>0.968304097652435</v>
+        <v>0.968304216861725</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1806" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918762922286987</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.905251801013947</v>
+        <v>0.905251741409302</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.914259195327759</v>
+        <v>0.914259254932404</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.905251801013947</v>
+        <v>0.905251741409302</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1816" t="n">
-        <v>0.905251801013947</v>
+        <v>0.905251741409302</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.882733047008514</v>
+        <v>0.882733106613159</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.871924102306366</v>
+        <v>0.871924042701721</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.882733047008514</v>
+        <v>0.882733106613159</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.866519570350647</v>
+        <v>0.866519629955292</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918762922286987</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.888137578964233</v>
+        <v>0.888137519359589</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.888137578964233</v>
+        <v>0.888137519359589</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1863" t="n">
-        <v>0.882733047008514</v>
+        <v>0.882733106613159</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1866" t="n">
-        <v>0.905251801013947</v>
+        <v>0.905251741409302</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918762922286987</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918762922286987</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>2.66000008583069</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>17874</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>2.63000011444092</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>2.66000008583069</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>3107</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>2.66000008583069</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>2.67000007629395</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>6362</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>2.63000011444092</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>2.67000007629395</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>13823</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>2.60999989509583</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>2.63000011444092</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>7154</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>33259</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -421,7 +421,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G12" t="n">
-        <v>0.815455973148346</v>
+        <v>0.815455913543701</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>0.889500021934509</v>
       </c>
       <c r="G14" t="n">
-        <v>0.779944181442261</v>
+        <v>0.779944121837616</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G15" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G18" t="n">
-        <v>0.806687533855438</v>
+        <v>0.806687653064728</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>0.927500009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>0.813263773918152</v>
+        <v>0.813263833522797</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G29" t="n">
-        <v>0.735664069652557</v>
+        <v>0.735664010047913</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G32" t="n">
-        <v>0.736540794372559</v>
+        <v>0.736540853977203</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.806500017642975</v>
       </c>
       <c r="G39" t="n">
-        <v>0.707166910171509</v>
+        <v>0.707166850566864</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G40" t="n">
-        <v>0.735664069652557</v>
+        <v>0.735664010047913</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G42" t="n">
-        <v>0.770737409591675</v>
+        <v>0.77073734998703</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G44" t="n">
-        <v>0.824224352836609</v>
+        <v>0.824224233627319</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G45" t="n">
-        <v>0.824224352836609</v>
+        <v>0.824224233627319</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>0.929000020027161</v>
       </c>
       <c r="G48" t="n">
-        <v>0.814579129219055</v>
+        <v>0.8145791888237</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.916499972343445</v>
       </c>
       <c r="G51" t="n">
-        <v>0.803618609905243</v>
+        <v>0.803618729114532</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G53" t="n">
-        <v>0.809318125247955</v>
+        <v>0.809318065643311</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G56" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G57" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.889500021934509</v>
       </c>
       <c r="G63" t="n">
-        <v>0.779944181442261</v>
+        <v>0.779944121837616</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G65" t="n">
-        <v>0.768106877803802</v>
+        <v>0.768106937408447</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G70" t="n">
-        <v>0.759338617324829</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G73" t="n">
-        <v>0.770737409591675</v>
+        <v>0.77073734998703</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>0.865499973297119</v>
       </c>
       <c r="G74" t="n">
-        <v>0.758900046348572</v>
+        <v>0.758900105953217</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>0.758461654186249</v>
+        <v>0.758461713790894</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G80" t="n">
-        <v>0.753200769424438</v>
+        <v>0.753200709819794</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>0.74969345331192</v>
+        <v>0.749693393707275</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>0.875</v>
       </c>
       <c r="G83" t="n">
-        <v>0.767230033874512</v>
+        <v>0.767230093479156</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>0.879499971866608</v>
       </c>
       <c r="G84" t="n">
-        <v>0.771175742149353</v>
+        <v>0.771175801753998</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>0.758461654186249</v>
+        <v>0.758461713790894</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G98" t="n">
-        <v>0.770737409591675</v>
+        <v>0.77073734998703</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G101" t="n">
-        <v>0.768106877803802</v>
+        <v>0.768106937408447</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>0.758461654186249</v>
+        <v>0.758461713790894</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>0.876500010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>0.768545269966125</v>
+        <v>0.76854532957077</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>0.875</v>
       </c>
       <c r="G109" t="n">
-        <v>0.767230033874512</v>
+        <v>0.767230093479156</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>0.875</v>
       </c>
       <c r="G110" t="n">
-        <v>0.767230033874512</v>
+        <v>0.767230093479156</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>0.869499981403351</v>
       </c>
       <c r="G111" t="n">
-        <v>0.76240748167038</v>
+        <v>0.762407422065735</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>0.875</v>
       </c>
       <c r="G114" t="n">
-        <v>0.767230033874512</v>
+        <v>0.767230093479156</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G119" t="n">
-        <v>0.748816430568695</v>
+        <v>0.748816549777985</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>0.869499981403351</v>
       </c>
       <c r="G120" t="n">
-        <v>0.76240748167038</v>
+        <v>0.762407422065735</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>0.897499978542328</v>
       </c>
       <c r="G121" t="n">
-        <v>0.786958754062653</v>
+        <v>0.786958813667297</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G125" t="n">
-        <v>0.648418962955475</v>
+        <v>0.64841890335083</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G126" t="n">
-        <v>0.675162434577942</v>
+        <v>0.675162374973297</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G127" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930695056915</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G128" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>0.795499980449677</v>
       </c>
       <c r="G129" t="n">
-        <v>0.697521686553955</v>
+        <v>0.6975217461586</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G130" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>0.798500001430511</v>
       </c>
       <c r="G131" t="n">
-        <v>0.700152218341827</v>
+        <v>0.700152277946472</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G132" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G133" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G134" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G135" t="n">
-        <v>0.687438130378723</v>
+        <v>0.687438070774078</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G136" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G137" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G138" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>0.828999996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>0.72689563035965</v>
+        <v>0.726895689964294</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>0.824500024318695</v>
       </c>
       <c r="G145" t="n">
-        <v>0.722949922084808</v>
+        <v>0.722949981689453</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G146" t="n">
-        <v>0.709359049797058</v>
+        <v>0.709358990192413</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G148" t="n">
-        <v>0.721634745597839</v>
+        <v>0.72163462638855</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G151" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G154" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G155" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G156" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G157" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>0.800999999046326</v>
       </c>
       <c r="G159" t="n">
-        <v>0.702344357967377</v>
+        <v>0.702344298362732</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G160" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G161" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G162" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G163" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>0.80349999666214</v>
       </c>
       <c r="G164" t="n">
-        <v>0.704536378383636</v>
+        <v>0.704536437988281</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G165" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G166" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G167" t="n">
-        <v>0.697083353996277</v>
+        <v>0.697083294391632</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G168" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>0.808499991893768</v>
       </c>
       <c r="G171" t="n">
-        <v>0.70892059803009</v>
+        <v>0.708920538425446</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G172" t="n">
-        <v>0.69971376657486</v>
+        <v>0.699713826179504</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G174" t="n">
-        <v>0.696206450462341</v>
+        <v>0.696206510066986</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G175" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930695056915</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G176" t="n">
-        <v>0.685684442520142</v>
+        <v>0.685684502124786</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G178" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G179" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G181" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930695056915</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>0.779500007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>0.683492362499237</v>
+        <v>0.683492422103882</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>0.666394054889679</v>
+        <v>0.666394114494324</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>0.675162434577942</v>
+        <v>0.675162374973297</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>0.675162434577942</v>
+        <v>0.675162374973297</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>0.763499975204468</v>
       </c>
       <c r="G187" t="n">
-        <v>0.669463038444519</v>
+        <v>0.669462978839874</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G192" t="n">
-        <v>0.670778214931488</v>
+        <v>0.670778274536133</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G196" t="n">
-        <v>0.633074402809143</v>
+        <v>0.633074343204498</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G197" t="n">
-        <v>0.633074402809143</v>
+        <v>0.633074343204498</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G198" t="n">
-        <v>0.631320774555206</v>
+        <v>0.631320714950562</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G200" t="n">
-        <v>0.647980570793152</v>
+        <v>0.647980690002441</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G201" t="n">
-        <v>0.626936495304108</v>
+        <v>0.626936554908752</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G202" t="n">
-        <v>0.622552335262299</v>
+        <v>0.622552454471588</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>0.709500014781952</v>
       </c>
       <c r="G203" t="n">
-        <v>0.62211400270462</v>
+        <v>0.622113943099976</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G206" t="n">
-        <v>0.61378401517868</v>
+        <v>0.613784074783325</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G207" t="n">
-        <v>0.61378401517868</v>
+        <v>0.613784074783325</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G211" t="n">
-        <v>0.60764616727829</v>
+        <v>0.607646226882935</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G212" t="n">
-        <v>0.61378401517868</v>
+        <v>0.613784074783325</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G213" t="n">
-        <v>0.61378401517868</v>
+        <v>0.613784074783325</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>0.607207775115967</v>
+        <v>0.607207834720612</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>0.607207775115967</v>
+        <v>0.607207834720612</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G217" t="n">
-        <v>0.615537822246552</v>
+        <v>0.615537703037262</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G218" t="n">
-        <v>0.610276639461517</v>
+        <v>0.610276699066162</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G219" t="n">
-        <v>0.61378401517868</v>
+        <v>0.613784074783325</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>0.689499974250793</v>
       </c>
       <c r="G220" t="n">
-        <v>0.60457718372345</v>
+        <v>0.604577243328094</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G221" t="n">
-        <v>0.59186315536499</v>
+        <v>0.591863214969635</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G222" t="n">
-        <v>0.587479054927826</v>
+        <v>0.587478995323181</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G225" t="n">
-        <v>0.587479054927826</v>
+        <v>0.587478995323181</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>0.668500006198883</v>
       </c>
       <c r="G226" t="n">
-        <v>0.586163759231567</v>
+        <v>0.586163818836212</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>0.672999978065491</v>
       </c>
       <c r="G227" t="n">
-        <v>0.590109467506409</v>
+        <v>0.590109527111053</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>0.697499990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>0.611591935157776</v>
+        <v>0.611591994762421</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G231" t="n">
-        <v>0.614222407341003</v>
+        <v>0.614222466945648</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.709500014781952</v>
       </c>
       <c r="G233" t="n">
-        <v>0.62211400270462</v>
+        <v>0.622113943099976</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G234" t="n">
-        <v>0.618168234825134</v>
+        <v>0.61816817522049</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>0.691500008106232</v>
       </c>
       <c r="G235" t="n">
-        <v>0.606330931186676</v>
+        <v>0.606330990791321</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>0.611153602600098</v>
+        <v>0.611153542995453</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G237" t="n">
-        <v>0.605892539024353</v>
+        <v>0.605892479419708</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G238" t="n">
-        <v>0.605892539024353</v>
+        <v>0.605892479419708</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G239" t="n">
-        <v>0.594493627548218</v>
+        <v>0.594493687152863</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>0.672999978065491</v>
       </c>
       <c r="G240" t="n">
-        <v>0.590109467506409</v>
+        <v>0.590109527111053</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G243" t="n">
-        <v>0.598000943660736</v>
+        <v>0.598001003265381</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>0.694999992847443</v>
       </c>
       <c r="G245" t="n">
-        <v>0.609399855136871</v>
+        <v>0.609399914741516</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>0.703499972820282</v>
       </c>
       <c r="G246" t="n">
-        <v>0.616852998733521</v>
+        <v>0.616852939128876</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>0.749499976634979</v>
       </c>
       <c r="G247" t="n">
-        <v>0.657187402248383</v>
+        <v>0.657187342643738</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G248" t="n">
-        <v>0.631320774555206</v>
+        <v>0.631320714950562</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G249" t="n">
-        <v>0.614660859107971</v>
+        <v>0.614660799503326</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>0.702499985694885</v>
       </c>
       <c r="G251" t="n">
-        <v>0.615976095199585</v>
+        <v>0.61597615480423</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G252" t="n">
-        <v>0.615537822246552</v>
+        <v>0.615537703037262</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G256" t="n">
-        <v>0.631320774555206</v>
+        <v>0.631320714950562</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G257" t="n">
-        <v>0.644473254680634</v>
+        <v>0.644473195075989</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>0.768999993801117</v>
       </c>
       <c r="G258" t="n">
-        <v>0.674285650253296</v>
+        <v>0.674285590648651</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>0.666394054889679</v>
+        <v>0.666394114494324</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>0.666394054889679</v>
+        <v>0.666394114494324</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G261" t="n">
-        <v>0.66200989484787</v>
+        <v>0.662009954452515</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G264" t="n">
-        <v>0.676916122436523</v>
+        <v>0.676916182041168</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G266" t="n">
-        <v>0.671654999256134</v>
+        <v>0.671655058860779</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>0.675162434577942</v>
+        <v>0.675162374973297</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>0.778500020503998</v>
       </c>
       <c r="G271" t="n">
-        <v>0.682615578174591</v>
+        <v>0.682615518569946</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G272" t="n">
-        <v>0.671654999256134</v>
+        <v>0.671655058860779</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>0.763000011444092</v>
       </c>
       <c r="G273" t="n">
-        <v>0.669024586677551</v>
+        <v>0.669024646282196</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G274" t="n">
-        <v>0.69971376657486</v>
+        <v>0.699713826179504</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G277" t="n">
-        <v>0.696206450462341</v>
+        <v>0.696206510066986</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>0.666394054889679</v>
+        <v>0.666394114494324</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.761500000953674</v>
       </c>
       <c r="G279" t="n">
-        <v>0.667709350585938</v>
+        <v>0.667709290981293</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G282" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930695056915</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G283" t="n">
-        <v>0.679546654224396</v>
+        <v>0.679546594619751</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G284" t="n">
-        <v>0.670778214931488</v>
+        <v>0.670778274536133</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>0.761500000953674</v>
       </c>
       <c r="G285" t="n">
-        <v>0.667709350585938</v>
+        <v>0.667709290981293</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>0.763499975204468</v>
       </c>
       <c r="G288" t="n">
-        <v>0.669463038444519</v>
+        <v>0.669462978839874</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.761500000953674</v>
       </c>
       <c r="G289" t="n">
-        <v>0.667709350585938</v>
+        <v>0.667709290981293</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G290" t="n">
-        <v>0.670778214931488</v>
+        <v>0.670778274536133</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G292" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G293" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G294" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G296" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G299" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G309" t="n">
-        <v>0.726018905639648</v>
+        <v>0.726018846035004</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G311" t="n">
-        <v>0.711989521980286</v>
+        <v>0.711989462375641</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G312" t="n">
-        <v>0.711989521980286</v>
+        <v>0.711989462375641</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>0.810999989509583</v>
       </c>
       <c r="G313" t="n">
-        <v>0.71111273765564</v>
+        <v>0.71111261844635</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G314" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G315" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G317" t="n">
-        <v>0.717250525951385</v>
+        <v>0.717250466346741</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G318" t="n">
-        <v>0.721634745597839</v>
+        <v>0.72163462638855</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G321" t="n">
-        <v>0.731279909610748</v>
+        <v>0.731279790401459</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>0.833000004291534</v>
       </c>
       <c r="G322" t="n">
-        <v>0.730403065681458</v>
+        <v>0.730403006076813</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G323" t="n">
-        <v>0.72777247428894</v>
+        <v>0.727772533893585</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>0.828999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>0.72689563035965</v>
+        <v>0.726895689964294</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G327" t="n">
-        <v>0.721634745597839</v>
+        <v>0.72163462638855</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G328" t="n">
-        <v>0.723388373851776</v>
+        <v>0.723388314247131</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G329" t="n">
-        <v>0.723388373851776</v>
+        <v>0.723388314247131</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G332" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>0.828499972820282</v>
       </c>
       <c r="G333" t="n">
-        <v>0.726457178592682</v>
+        <v>0.726457238197327</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G335" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>0.824500024318695</v>
       </c>
       <c r="G336" t="n">
-        <v>0.722949922084808</v>
+        <v>0.722949981689453</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>0.824999988079071</v>
       </c>
       <c r="G337" t="n">
-        <v>0.723388373851776</v>
+        <v>0.723388314247131</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>0.813000023365021</v>
       </c>
       <c r="G340" t="n">
-        <v>0.712866306304932</v>
+        <v>0.712866246700287</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G342" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>0.810999989509583</v>
       </c>
       <c r="G343" t="n">
-        <v>0.71111273765564</v>
+        <v>0.71111261844635</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G344" t="n">
-        <v>0.716373682022095</v>
+        <v>0.71637374162674</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>0.8125</v>
       </c>
       <c r="G345" t="n">
-        <v>0.712427854537964</v>
+        <v>0.712427973747253</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>0.813000023365021</v>
       </c>
       <c r="G349" t="n">
-        <v>0.712866306304932</v>
+        <v>0.712866246700287</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>0.8125</v>
       </c>
       <c r="G351" t="n">
-        <v>0.712427854537964</v>
+        <v>0.712427973747253</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G353" t="n">
-        <v>0.717250525951385</v>
+        <v>0.717250466346741</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>0.810999989509583</v>
       </c>
       <c r="G356" t="n">
-        <v>0.71111273765564</v>
+        <v>0.71111261844635</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>0.823499977588654</v>
       </c>
       <c r="G360" t="n">
-        <v>0.722073018550873</v>
+        <v>0.722073078155518</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G361" t="n">
-        <v>0.725580394268036</v>
+        <v>0.725580453872681</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>0.828499972820282</v>
       </c>
       <c r="G363" t="n">
-        <v>0.726457178592682</v>
+        <v>0.726457238197327</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G365" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G367" t="n">
-        <v>0.72777247428894</v>
+        <v>0.727772533893585</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G368" t="n">
-        <v>0.736540794372559</v>
+        <v>0.736540853977203</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>0.83899998664856</v>
       </c>
       <c r="G369" t="n">
-        <v>0.735664069652557</v>
+        <v>0.735664010047913</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.01600003242493</v>
       </c>
       <c r="G370" t="n">
-        <v>0.89086377620697</v>
+        <v>0.890863716602325</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G371" t="n">
-        <v>0.887356221675873</v>
+        <v>0.887356400489807</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G372" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G374" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G376" t="n">
-        <v>0.936459124088287</v>
+        <v>0.936459064483643</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G377" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G383" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G384" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G388" t="n">
-        <v>1.05307805538177</v>
+        <v>1.05307793617249</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.22899997234344</v>
       </c>
       <c r="G394" t="n">
-        <v>1.07762932777405</v>
+        <v>1.07762944698334</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G395" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G396" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G397" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G400" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G404" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G405" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G406" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.20299994945526</v>
       </c>
       <c r="G407" t="n">
-        <v>1.05483162403107</v>
+        <v>1.05483174324036</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G408" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G411" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G412" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G413" t="n">
-        <v>1.05658543109894</v>
+        <v>1.05658555030823</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G414" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G415" t="n">
-        <v>1.05307805538177</v>
+        <v>1.05307793617249</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G416" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G417" t="n">
-        <v>1.05395495891571</v>
+        <v>1.05395483970642</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G418" t="n">
-        <v>1.05395495891571</v>
+        <v>1.05395483970642</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G419" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G420" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G421" t="n">
-        <v>1.04606342315674</v>
+        <v>1.04606318473816</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G423" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G424" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G425" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G426" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G428" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G430" t="n">
-        <v>1.20477032661438</v>
+        <v>1.20477044582367</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G431" t="n">
-        <v>1.1398845911026</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.27699995040894</v>
       </c>
       <c r="G432" t="n">
-        <v>1.11971735954285</v>
+        <v>1.11971747875214</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G434" t="n">
-        <v>1.17671167850494</v>
+        <v>1.17671179771423</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G435" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G438" t="n">
-        <v>1.09691965579987</v>
+        <v>1.09691977500916</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.26699995994568</v>
       </c>
       <c r="G441" t="n">
-        <v>1.11094903945923</v>
+        <v>1.11094915866852</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>1.32299995422363</v>
       </c>
       <c r="G443" t="n">
-        <v>1.16005182266235</v>
+        <v>1.16005170345306</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G444" t="n">
-        <v>1.14163827896118</v>
+        <v>1.14163851737976</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G446" t="n">
-        <v>1.14952993392944</v>
+        <v>1.14952981472015</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G448" t="n">
-        <v>1.14076149463654</v>
+        <v>1.14076137542725</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.31700003147125</v>
       </c>
       <c r="G449" t="n">
-        <v>1.1547908782959</v>
+        <v>1.15479099750519</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.33899998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>1.17408120632172</v>
+        <v>1.17408132553101</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G453" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.34099996089935</v>
       </c>
       <c r="G454" t="n">
-        <v>1.17583477497101</v>
+        <v>1.1758348941803</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G455" t="n">
-        <v>1.15917503833771</v>
+        <v>1.159175157547</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G456" t="n">
-        <v>1.15917503833771</v>
+        <v>1.159175157547</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G457" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G458" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G459" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G460" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G461" t="n">
-        <v>1.16618978977203</v>
+        <v>1.16618990898132</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G462" t="n">
-        <v>1.16618978977203</v>
+        <v>1.16618990898132</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G463" t="n">
-        <v>1.18372631072998</v>
+        <v>1.18372642993927</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.34899997711182</v>
       </c>
       <c r="G464" t="n">
-        <v>1.18284952640533</v>
+        <v>1.18284940719604</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G466" t="n">
-        <v>1.18372631072998</v>
+        <v>1.18372642993927</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G468" t="n">
-        <v>1.21441555023193</v>
+        <v>1.21441566944122</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G469" t="n">
-        <v>1.2091543674469</v>
+        <v>1.20915448665619</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G470" t="n">
-        <v>1.2074009180069</v>
+        <v>1.20740079879761</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G471" t="n">
-        <v>1.19424843788147</v>
+        <v>1.19424831867218</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G473" t="n">
-        <v>1.21353876590729</v>
+        <v>1.21353852748871</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G476" t="n">
-        <v>1.20477032661438</v>
+        <v>1.20477044582367</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G480" t="n">
-        <v>1.17934226989746</v>
+        <v>1.17934215068817</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>1.31700003147125</v>
       </c>
       <c r="G483" t="n">
-        <v>1.1547908782959</v>
+        <v>1.15479099750519</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G485" t="n">
-        <v>1.14076149463654</v>
+        <v>1.14076137542725</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.1398845911026</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G487" t="n">
-        <v>1.14952993392944</v>
+        <v>1.14952981472015</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>1.33899998664856</v>
       </c>
       <c r="G489" t="n">
-        <v>1.17408120632172</v>
+        <v>1.17408132553101</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G490" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G491" t="n">
-        <v>1.18109571933746</v>
+        <v>1.18109595775604</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>1.375</v>
       </c>
       <c r="G492" t="n">
-        <v>1.2056473493576</v>
+        <v>1.20564723014832</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G494" t="n">
-        <v>1.18723368644714</v>
+        <v>1.18723356723785</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G495" t="n">
-        <v>1.18548011779785</v>
+        <v>1.18547999858856</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G496" t="n">
-        <v>1.18372631072998</v>
+        <v>1.18372642993927</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G497" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G499" t="n">
-        <v>1.18109571933746</v>
+        <v>1.18109595775604</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.34300005435944</v>
       </c>
       <c r="G500" t="n">
-        <v>1.17758870124817</v>
+        <v>1.17758846282959</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G503" t="n">
-        <v>1.14163827896118</v>
+        <v>1.14163851737976</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.28299999237061</v>
       </c>
       <c r="G507" t="n">
-        <v>1.1249783039093</v>
+        <v>1.12497842311859</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G508" t="n">
-        <v>1.1398845911026</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G509" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>1.28100001811981</v>
       </c>
       <c r="G511" t="n">
-        <v>1.1232248544693</v>
+        <v>1.12322461605072</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G512" t="n">
-        <v>1.1398845911026</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G514" t="n">
-        <v>1.1398845911026</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G515" t="n">
-        <v>1.13550043106079</v>
+        <v>1.13550055027008</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G517" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G518" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G520" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G522" t="n">
-        <v>1.17934226989746</v>
+        <v>1.17934215068817</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G524" t="n">
-        <v>1.25387299060822</v>
+        <v>1.2538731098175</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G525" t="n">
-        <v>1.23633646965027</v>
+        <v>1.23633635044098</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G526" t="n">
-        <v>1.23195219039917</v>
+        <v>1.23195230960846</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G527" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G528" t="n">
-        <v>1.2451046705246</v>
+        <v>1.24510490894318</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G529" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G530" t="n">
-        <v>1.25387299060822</v>
+        <v>1.2538731098175</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G531" t="n">
-        <v>1.25387299060822</v>
+        <v>1.2538731098175</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G532" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G533" t="n">
-        <v>1.23195219039917</v>
+        <v>1.23195230960846</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G534" t="n">
-        <v>1.21441555023193</v>
+        <v>1.21441566944122</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G535" t="n">
-        <v>1.2451046705246</v>
+        <v>1.24510490894318</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>1.21441555023193</v>
+        <v>1.21441566944122</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>1.18811058998108</v>
+        <v>1.18811070919037</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G540" t="n">
-        <v>1.22756803035736</v>
+        <v>1.22756814956665</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>1.22318387031555</v>
+        <v>1.22318398952484</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>1.17057383060455</v>
+        <v>1.17057394981384</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>1.375</v>
       </c>
       <c r="G546" t="n">
-        <v>1.2056473493576</v>
+        <v>1.20564723014832</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G548" t="n">
-        <v>1.21879971027374</v>
+        <v>1.21879982948303</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>1.375</v>
       </c>
       <c r="G550" t="n">
-        <v>1.2056473493576</v>
+        <v>1.20564723014832</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>1.17934226989746</v>
+        <v>1.17934215068817</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G552" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G553" t="n">
-        <v>1.18372631072998</v>
+        <v>1.18372642993927</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G554" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G557" t="n">
-        <v>1.18372631072998</v>
+        <v>1.18372642993927</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G558" t="n">
-        <v>1.17934226989746</v>
+        <v>1.17934215068817</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G559" t="n">
-        <v>1.17057383060455</v>
+        <v>1.17057394981384</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>1.18811058998108</v>
+        <v>1.18811070919037</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G562" t="n">
-        <v>1.18811058998108</v>
+        <v>1.18811070919037</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G563" t="n">
-        <v>1.18372631072998</v>
+        <v>1.18372642993927</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>1.17934226989746</v>
+        <v>1.17934215068817</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G565" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G567" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G569" t="n">
-        <v>1.17495810985565</v>
+        <v>1.17495799064636</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G571" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G572" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G575" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G576" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G579" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>1.1398845911026</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G588" t="n">
-        <v>1.13550043106079</v>
+        <v>1.13550055027008</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G589" t="n">
-        <v>1.13550043106079</v>
+        <v>1.13550055027008</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G591" t="n">
-        <v>1.13550043106079</v>
+        <v>1.13550055027008</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>1.1398845911026</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G593" t="n">
-        <v>1.13550043106079</v>
+        <v>1.13550055027008</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G594" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>1.1398845911026</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G596" t="n">
-        <v>1.1398845911026</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G597" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G598" t="n">
-        <v>1.16618978977203</v>
+        <v>1.16618990898132</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G601" t="n">
-        <v>1.15742146968842</v>
+        <v>1.15742135047913</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G604" t="n">
-        <v>1.13550043106079</v>
+        <v>1.13550055027008</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G609" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G611" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G612" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>1.1398845911026</v>
+        <v>1.13988471031189</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G618" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G622" t="n">
-        <v>1.13550043106079</v>
+        <v>1.13550055027008</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G628" t="n">
-        <v>1.13550043106079</v>
+        <v>1.13550055027008</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G629" t="n">
-        <v>1.13550043106079</v>
+        <v>1.13550055027008</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G630" t="n">
-        <v>1.13550043106079</v>
+        <v>1.13550055027008</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G635" t="n">
-        <v>1.13550043106079</v>
+        <v>1.13550055027008</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G640" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G645" t="n">
-        <v>1.13550043106079</v>
+        <v>1.13550055027008</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G650" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G652" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G656" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G664" t="n">
-        <v>1.08289039134979</v>
+        <v>1.08289051055908</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>1.07850635051727</v>
+        <v>1.07850623130798</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G672" t="n">
-        <v>1.0872745513916</v>
+        <v>1.08727467060089</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G673" t="n">
-        <v>1.07850635051727</v>
+        <v>1.07850623130798</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G674" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G675" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973779201508</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G676" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973779201508</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G677" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973779201508</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G679" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G680" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G681" t="n">
-        <v>1.06096947193146</v>
+        <v>1.06096959114075</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G682" t="n">
-        <v>1.05658543109894</v>
+        <v>1.05658555030823</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973779201508</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G684" t="n">
-        <v>1.07850635051727</v>
+        <v>1.07850623130798</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G685" t="n">
-        <v>1.07850635051727</v>
+        <v>1.07850623130798</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G686" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973779201508</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>1.0872745513916</v>
+        <v>1.08727467060089</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G702" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G707" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G710" t="n">
-        <v>1.12234783172607</v>
+        <v>1.12234795093536</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G727" t="n">
-        <v>1.0872745513916</v>
+        <v>1.08727467060089</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G728" t="n">
-        <v>1.0872745513916</v>
+        <v>1.08727467060089</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G730" t="n">
-        <v>1.0872745513916</v>
+        <v>1.08727467060089</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G732" t="n">
-        <v>1.08289039134979</v>
+        <v>1.08289051055908</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G735" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G736" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G737" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G738" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712775230408</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>1.06096947193146</v>
+        <v>1.06096959114075</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>1.06096947193146</v>
+        <v>1.06096959114075</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G744" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.02151203155518</v>
+        <v>1.02151191234589</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G746" t="n">
-        <v>1.0302802324295</v>
+        <v>1.03028035163879</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G747" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712775230408</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G748" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712775230408</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G749" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G750" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G751" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G752" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G754" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.125</v>
       </c>
       <c r="G755" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G758" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G759" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G760" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G764" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G766" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G768" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.01274359226227</v>
+        <v>1.01274371147156</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G771" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G772" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G773" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G774" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G775" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G776" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.125</v>
       </c>
       <c r="G777" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G779" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G780" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G785" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G786" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G787" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G788" t="n">
-        <v>0.960133612155914</v>
+        <v>0.960133731365204</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G794" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G796" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G797" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712775230408</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.125</v>
       </c>
       <c r="G809" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.125</v>
       </c>
       <c r="G813" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G817" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G824" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G826" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G827" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G831" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G835" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.125</v>
       </c>
       <c r="G836" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.125</v>
       </c>
       <c r="G837" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.125</v>
       </c>
       <c r="G838" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.125</v>
       </c>
       <c r="G839" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G841" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G843" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G844" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G845" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G848" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G850" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.125</v>
       </c>
       <c r="G851" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G852" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G853" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G857" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G858" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G859" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G860" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G861" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G862" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G863" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G864" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G865" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G866" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G868" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G869" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G873" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G882" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G888" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.125</v>
       </c>
       <c r="G890" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G903" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G904" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G908" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G909" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G910" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G911" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G912" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G913" t="n">
-        <v>0.960133612155914</v>
+        <v>0.960133731365204</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G914" t="n">
-        <v>0.960133612155914</v>
+        <v>0.960133731365204</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G915" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G916" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G917" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G918" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G919" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G921" t="n">
-        <v>0.889986872673035</v>
+        <v>0.88998681306839</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G924" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G925" t="n">
-        <v>0.889986872673035</v>
+        <v>0.88998681306839</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G926" t="n">
-        <v>0.889986872673035</v>
+        <v>0.88998681306839</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G928" t="n">
-        <v>0.889986872673035</v>
+        <v>0.88998681306839</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G929" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G930" t="n">
-        <v>0.889986872673035</v>
+        <v>0.88998681306839</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G932" t="n">
-        <v>0.916291892528534</v>
+        <v>0.916291832923889</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G934" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G935" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G936" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G937" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G938" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G939" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G940" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G941" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G942" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G943" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G944" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G945" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G946" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G947" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G948" t="n">
-        <v>0.942597091197968</v>
+        <v>0.942597031593323</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G949" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G950" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G951" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G952" t="n">
-        <v>0.933828711509705</v>
+        <v>0.93382865190506</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G953" t="n">
-        <v>0.933828711509705</v>
+        <v>0.93382865190506</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G954" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G955" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G956" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G957" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G958" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G959" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G960" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G961" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G962" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G963" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G964" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G965" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G967" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G968" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G969" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G970" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G971" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G972" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G973" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G974" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G975" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G976" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G977" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G978" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G979" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G980" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G986" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G987" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G988" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G989" t="n">
-        <v>0.942597091197968</v>
+        <v>0.942597031593323</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G991" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G992" t="n">
-        <v>0.916291892528534</v>
+        <v>0.916291832923889</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G993" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G994" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G995" t="n">
-        <v>0.942597091197968</v>
+        <v>0.942597031593323</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G997" t="n">
-        <v>0.933828711509705</v>
+        <v>0.93382865190506</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G998" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G999" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.933828711509705</v>
+        <v>0.93382865190506</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1004" t="n">
-        <v>0.933828711509705</v>
+        <v>0.93382865190506</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.960133612155914</v>
+        <v>0.960133731365204</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1007" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1009" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.125</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1011" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.942597091197968</v>
+        <v>0.942597031593323</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.960133612155914</v>
+        <v>0.960133731365204</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1021" t="n">
-        <v>0.960133612155914</v>
+        <v>0.960133731365204</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.960133612155914</v>
+        <v>0.960133731365204</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.942597091197968</v>
+        <v>0.942597031593323</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.916291892528534</v>
+        <v>0.916291832923889</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1036" t="n">
-        <v>0.942597091197968</v>
+        <v>0.942597031593323</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.916291892528534</v>
+        <v>0.916291832923889</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.916291892528534</v>
+        <v>0.916291832923889</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.894371032714844</v>
+        <v>0.894371092319489</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1041" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1042" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.894371032714844</v>
+        <v>0.894371092319489</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.889986872673035</v>
+        <v>0.88998681306839</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.88560277223587</v>
+        <v>0.885602712631226</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.894371032714844</v>
+        <v>0.894371092319489</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.88560277223587</v>
+        <v>0.885602712631226</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.875080704689026</v>
+        <v>0.875080764293671</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.864558637142181</v>
+        <v>0.864558696746826</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.850529372692108</v>
+        <v>0.850529313087463</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.768106877803802</v>
+        <v>0.768106937408447</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.736540794372559</v>
+        <v>0.736540853977203</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.675162434577942</v>
+        <v>0.675162374973297</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.666394054889679</v>
+        <v>0.666394114494324</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.638335347175598</v>
+        <v>0.638335406780243</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.675162434577942</v>
+        <v>0.675162374973297</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.736540794372559</v>
+        <v>0.736540853977203</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.736540794372559</v>
+        <v>0.736540853977203</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.720757842063904</v>
+        <v>0.720757901668549</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.72777247428894</v>
+        <v>0.727772533893585</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.736540794372559</v>
+        <v>0.736540853977203</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.722511470317841</v>
+        <v>0.722511529922485</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.741801857948303</v>
+        <v>0.741801917552948</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.740048229694366</v>
+        <v>0.740048170089722</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.736540794372559</v>
+        <v>0.736540853977203</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.741801857948303</v>
+        <v>0.741801917552948</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.720757842063904</v>
+        <v>0.720757901668549</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.72777247428894</v>
+        <v>0.727772533893585</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.72777247428894</v>
+        <v>0.727772533893585</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.748816430568695</v>
+        <v>0.748816549777985</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.726018905639648</v>
+        <v>0.726018846035004</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.72777247428894</v>
+        <v>0.727772533893585</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.731279909610748</v>
+        <v>0.731279790401459</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.729526162147522</v>
+        <v>0.729526281356812</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.729526162147522</v>
+        <v>0.729526281356812</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.708482146263123</v>
+        <v>0.708482205867767</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.722511470317841</v>
+        <v>0.722511529922485</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.708482146263123</v>
+        <v>0.708482205867767</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.69445276260376</v>
+        <v>0.694452822208405</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.717250525951385</v>
+        <v>0.717250466346741</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930695056915</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.676916122436523</v>
+        <v>0.676916182041168</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.676916122436523</v>
+        <v>0.676916182041168</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.678669691085815</v>
+        <v>0.67866975069046</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.671654999256134</v>
+        <v>0.671655058860779</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.645350098609924</v>
+        <v>0.64535003900528</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.645350098609924</v>
+        <v>0.64535003900528</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.676916122436523</v>
+        <v>0.676916182041168</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.666394054889679</v>
+        <v>0.666394114494324</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.69445276260376</v>
+        <v>0.694452822208405</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.680423438549042</v>
+        <v>0.680423498153687</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.680423438549042</v>
+        <v>0.680423498153687</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.662886798381805</v>
+        <v>0.662886738777161</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.671654999256134</v>
+        <v>0.671655058860779</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.671654999256134</v>
+        <v>0.671655058860779</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.736540794372559</v>
+        <v>0.736540853977203</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.720757842063904</v>
+        <v>0.720757901668549</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.722511470317841</v>
+        <v>0.722511529922485</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.736540794372559</v>
+        <v>0.736540853977203</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.72777247428894</v>
+        <v>0.727772533893585</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.726018905639648</v>
+        <v>0.726018846035004</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.726018905639648</v>
+        <v>0.726018846035004</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.726018905639648</v>
+        <v>0.726018846035004</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.726018905639648</v>
+        <v>0.726018846035004</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.717250525951385</v>
+        <v>0.717250466346741</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.717250525951385</v>
+        <v>0.717250466346741</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.722511470317841</v>
+        <v>0.722511529922485</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.69445276260376</v>
+        <v>0.694452822208405</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.675162434577942</v>
+        <v>0.675162374973297</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.687438130378723</v>
+        <v>0.687438070774078</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.675162434577942</v>
+        <v>0.675162374973297</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.666394054889679</v>
+        <v>0.666394114494324</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.661133110523224</v>
+        <v>0.661133170127869</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930695056915</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.662886798381805</v>
+        <v>0.662886738777161</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.659379363059998</v>
+        <v>0.659379422664642</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.666394054889679</v>
+        <v>0.666394114494324</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930695056915</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.675162434577942</v>
+        <v>0.675162374973297</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.69971376657486</v>
+        <v>0.699713826179504</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.69971376657486</v>
+        <v>0.699713826179504</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930695056915</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.68393075466156</v>
+        <v>0.683930695056915</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.661133110523224</v>
+        <v>0.661133170127869</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.631320774555206</v>
+        <v>0.631320714950562</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.676916122436523</v>
+        <v>0.676916182041168</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.661133110523224</v>
+        <v>0.661133170127869</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.69971376657486</v>
+        <v>0.699713826179504</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.69445276260376</v>
+        <v>0.694452822208405</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.685684442520142</v>
+        <v>0.685684502124786</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.720757842063904</v>
+        <v>0.720757901668549</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.710235774517059</v>
+        <v>0.710235834121704</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.717250525951385</v>
+        <v>0.717250466346741</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.72777247428894</v>
+        <v>0.727772533893585</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.708482146263123</v>
+        <v>0.708482205867767</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.701467573642731</v>
+        <v>0.701467454433441</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.72777247428894</v>
+        <v>0.727772533893585</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.850529372692108</v>
+        <v>0.850529313087463</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.815455973148346</v>
+        <v>0.815455913543701</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.768106877803802</v>
+        <v>0.768106937408447</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.759338617324829</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.747062861919403</v>
+        <v>0.747062802314758</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.759338617324829</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.757584869861603</v>
+        <v>0.757584929466248</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.759338617324829</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.759338617324829</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.803180277347565</v>
+        <v>0.80318021774292</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.815455973148346</v>
+        <v>0.815455913543701</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.815455973148346</v>
+        <v>0.815455913543701</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.806687533855438</v>
+        <v>0.806687653064728</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.794411897659302</v>
+        <v>0.794411957263947</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.773368000984192</v>
+        <v>0.773367941379547</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.759338617324829</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.757584869861603</v>
+        <v>0.757584929466248</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.748816430568695</v>
+        <v>0.748816549777985</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.747062861919403</v>
+        <v>0.747062802314758</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.776875138282776</v>
+        <v>0.776875197887421</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.759338617324829</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.773368000984192</v>
+        <v>0.773367941379547</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.785643637180328</v>
+        <v>0.785643577575684</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.776875138282776</v>
+        <v>0.776875197887421</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.785643637180328</v>
+        <v>0.785643577575684</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.785643637180328</v>
+        <v>0.785643577575684</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.789150893688202</v>
+        <v>0.789150953292847</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.815455973148346</v>
+        <v>0.815455913543701</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.815455973148346</v>
+        <v>0.815455913543701</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.818963229656219</v>
+        <v>0.818963289260864</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.83650004863739</v>
+        <v>0.836499989032745</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.845268249511719</v>
+        <v>0.845268309116364</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.824224352836609</v>
+        <v>0.824224233627319</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.83650004863739</v>
+        <v>0.836499989032745</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.825977861881256</v>
+        <v>0.825977981090546</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.831238985061646</v>
+        <v>0.831238925457001</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.83650004863739</v>
+        <v>0.836499989032745</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.845268249511719</v>
+        <v>0.845268309116364</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.845268249511719</v>
+        <v>0.845268309116364</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.848775625228882</v>
+        <v>0.848775684833527</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.83650004863739</v>
+        <v>0.836499989032745</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.829485297203064</v>
+        <v>0.829485237598419</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.825977861881256</v>
+        <v>0.825977981090546</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.845268249511719</v>
+        <v>0.845268309116364</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.843514680862427</v>
+        <v>0.843514621257782</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.848775625228882</v>
+        <v>0.848775684833527</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.850529372692108</v>
+        <v>0.850529313087463</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.850529372692108</v>
+        <v>0.850529313087463</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.850529372692108</v>
+        <v>0.850529313087463</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1405" t="n">
-        <v>0.83650004863739</v>
+        <v>0.836499989032745</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.829485297203064</v>
+        <v>0.829485237598419</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.831238985061646</v>
+        <v>0.831238925457001</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.850529372692108</v>
+        <v>0.850529313087463</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.83650004863739</v>
+        <v>0.836499989032745</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.850529372692108</v>
+        <v>0.850529313087463</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.894371032714844</v>
+        <v>0.894371092319489</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.88560277223587</v>
+        <v>0.885602712631226</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.889986872673035</v>
+        <v>0.88998681306839</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.894371032714844</v>
+        <v>0.894371092319489</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.881218552589417</v>
+        <v>0.881218492984772</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.894371032714844</v>
+        <v>0.894371092319489</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.894371032714844</v>
+        <v>0.894371092319489</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.889986872673035</v>
+        <v>0.88998681306839</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.881218552589417</v>
+        <v>0.881218492984772</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.881218552589417</v>
+        <v>0.881218492984772</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.894371032714844</v>
+        <v>0.894371092319489</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.881218552589417</v>
+        <v>0.881218492984772</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.875080704689026</v>
+        <v>0.875080764293671</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.881218552589417</v>
+        <v>0.881218492984772</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.88560277223587</v>
+        <v>0.885602712631226</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.889986872673035</v>
+        <v>0.88998681306839</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.916291892528534</v>
+        <v>0.916291832923889</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.916291892528534</v>
+        <v>0.916291832923889</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.894371032714844</v>
+        <v>0.894371092319489</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.942597091197968</v>
+        <v>0.942597031593323</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.01274359226227</v>
+        <v>1.01274371147156</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.01274359226227</v>
+        <v>1.01274371147156</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.06535387039185</v>
+        <v>1.06535375118256</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1480" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973779201508</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.05220115184784</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.02589619159698</v>
+        <v>1.0258960723877</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.01274359226227</v>
+        <v>1.01274371147156</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.0302802324295</v>
+        <v>1.03028035163879</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712775230408</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.08289039134979</v>
+        <v>1.08289051055908</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.06973803043365</v>
+        <v>1.06973779201508</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.06535387039185</v>
+        <v>1.06535375118256</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.0302802324295</v>
+        <v>1.03028035163879</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.0302802324295</v>
+        <v>1.03028035163879</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.125</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>1.125</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>1.125</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.995207071304321</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.125</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>1.125</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>1.125</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.960133612155914</v>
+        <v>0.960133731365204</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>1.125</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1535" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.960133612155914</v>
+        <v>0.960133731365204</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.933828711509705</v>
+        <v>0.93382865190506</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.933828711509705</v>
+        <v>0.93382865190506</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.942597091197968</v>
+        <v>0.942597031593323</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1551" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1552" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1555" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>1.125</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1560" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1567" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.911907732486725</v>
+        <v>0.91190767288208</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.88560277223587</v>
+        <v>0.885602712631226</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.916291892528534</v>
+        <v>0.916291832923889</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.933828711509705</v>
+        <v>0.93382865190506</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1580" t="n">
-        <v>0.933828711509705</v>
+        <v>0.93382865190506</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1581" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.929444313049316</v>
+        <v>0.929444372653961</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.920675992965698</v>
+        <v>0.920676112174988</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1585" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.925060153007507</v>
+        <v>0.925060272216797</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1588" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712775230408</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712775230408</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.01274359226227</v>
+        <v>1.01274371147156</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712775230408</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.982054471969604</v>
+        <v>0.982054531574249</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.973286211490631</v>
+        <v>0.973286151885986</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>1.125</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.977670252323151</v>
+        <v>0.97767037153244</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.960133612155914</v>
+        <v>0.960133731365204</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.960133612155914</v>
+        <v>0.960133731365204</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.95574951171875</v>
+        <v>0.95574939250946</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.964517772197723</v>
+        <v>0.964517891407013</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.951365232467651</v>
+        <v>0.951365351676941</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.968901932239532</v>
+        <v>0.968902051448822</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>1.125</v>
       </c>
       <c r="G1623" t="n">
-        <v>0.986438751220703</v>
+        <v>0.986438691616058</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1631" t="n">
-        <v>0.986319065093994</v>
+        <v>0.986319184303284</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.972807943820953</v>
+        <v>0.972807884216309</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.95479279756546</v>
+        <v>0.954792857170105</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1641" t="n">
-        <v>0.96830415725708</v>
+        <v>0.968304216861725</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.972807943820953</v>
+        <v>0.972807884216309</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.950289070606232</v>
+        <v>0.950289189815521</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.972807943820953</v>
+        <v>0.972807884216309</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1645" t="n">
-        <v>0.95479279756546</v>
+        <v>0.954792857170105</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.936777949333191</v>
+        <v>0.936777889728546</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1649" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1650" t="n">
-        <v>0.950289070606232</v>
+        <v>0.950289189815521</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.950289070606232</v>
+        <v>0.950289189815521</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.936777949333191</v>
+        <v>0.936777889728546</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1654" t="n">
-        <v>0.950289070606232</v>
+        <v>0.950289189815521</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.950289070606232</v>
+        <v>0.950289189815521</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1659" t="n">
-        <v>0.927770435810089</v>
+        <v>0.927770376205444</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.927770435810089</v>
+        <v>0.927770376205444</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1661" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918763041496277</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.932274222373962</v>
+        <v>0.932274162769318</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.927770435810089</v>
+        <v>0.927770376205444</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.95479279756546</v>
+        <v>0.954792857170105</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.941281676292419</v>
+        <v>0.941281616687775</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918763041496277</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.936777949333191</v>
+        <v>0.936777889728546</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.950289070606232</v>
+        <v>0.950289189815521</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.950289070606232</v>
+        <v>0.950289189815521</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.950289070606232</v>
+        <v>0.950289189815521</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.950289070606232</v>
+        <v>0.950289189815521</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1676" t="n">
-        <v>0.96830415725708</v>
+        <v>0.968304216861725</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.950289070606232</v>
+        <v>0.950289189815521</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1679" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918763041496277</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.936777949333191</v>
+        <v>0.936777889728546</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1681" t="n">
-        <v>0.932274222373962</v>
+        <v>0.932274162769318</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.936777949333191</v>
+        <v>0.936777889728546</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.927770435810089</v>
+        <v>0.927770376205444</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918763041496277</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1692" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1693" t="n">
-        <v>0.927770435810089</v>
+        <v>0.927770376205444</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.945785343647003</v>
+        <v>0.945785462856293</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.882733106613159</v>
+        <v>0.882733047008514</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.879130005836487</v>
+        <v>0.879130065441132</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1731" t="n">
-        <v>0.848504602909088</v>
+        <v>0.848504662513733</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.855710566043854</v>
+        <v>0.855710625648499</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.848504602909088</v>
+        <v>0.848504662513733</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.848504602909088</v>
+        <v>0.848504662513733</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.855710566043854</v>
+        <v>0.855710625648499</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.861115038394928</v>
+        <v>0.861115097999573</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.855710566043854</v>
+        <v>0.855710625648499</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.855710566043854</v>
+        <v>0.855710625648499</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.855710566043854</v>
+        <v>0.855710625648499</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.855710566043854</v>
+        <v>0.855710625648499</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.882733106613159</v>
+        <v>0.882733047008514</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.882733106613159</v>
+        <v>0.882733047008514</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.884534597396851</v>
+        <v>0.884534537792206</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G1772" t="n">
-        <v>0.857512176036835</v>
+        <v>0.85751211643219</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.855710566043854</v>
+        <v>0.855710625648499</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.855710566043854</v>
+        <v>0.855710625648499</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1776" t="n">
-        <v>0.855710566043854</v>
+        <v>0.855710625648499</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.857512176036835</v>
+        <v>0.85751211643219</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.861115038394928</v>
+        <v>0.861115097999573</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1802" t="n">
-        <v>0.927770435810089</v>
+        <v>0.927770376205444</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1804" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918763041496277</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1805" t="n">
-        <v>0.96830415725708</v>
+        <v>0.968304216861725</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1806" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918763041496277</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.941281676292419</v>
+        <v>0.941281616687775</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.905251801013947</v>
+        <v>0.905251741409302</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1813" t="n">
-        <v>0.927770435810089</v>
+        <v>0.927770376205444</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.927770435810089</v>
+        <v>0.927770376205444</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.905251801013947</v>
+        <v>0.905251741409302</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1816" t="n">
-        <v>0.905251801013947</v>
+        <v>0.905251741409302</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.882733106613159</v>
+        <v>0.882733047008514</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.868321061134338</v>
+        <v>0.868321120738983</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.882733106613159</v>
+        <v>0.882733047008514</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.857512176036835</v>
+        <v>0.85751211643219</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G1838" t="n">
-        <v>0.868321061134338</v>
+        <v>0.868321120738983</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.855710566043854</v>
+        <v>0.855710625648499</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1842" t="n">
-        <v>0.855710566043854</v>
+        <v>0.855710625648499</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.855710566043854</v>
+        <v>0.855710625648499</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.868321061134338</v>
+        <v>0.868321120738983</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918763041496277</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.888137519359589</v>
+        <v>0.888137578964233</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.888137519359589</v>
+        <v>0.888137578964233</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1863" t="n">
-        <v>0.882733106613159</v>
+        <v>0.882733047008514</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.927770435810089</v>
+        <v>0.927770376205444</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1866" t="n">
-        <v>0.905251801013947</v>
+        <v>0.905251741409302</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918763041496277</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.918762981891632</v>
+        <v>0.918763041496277</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.941281676292419</v>
+        <v>0.941281616687775</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.941281676292419</v>
+        <v>0.941281616687775</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>2.59999990463257</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>3597</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -421,7 +421,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>0.868066012859344</v>
+        <v>0.868066072463989</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>0.999499976634979</v>
       </c>
       <c r="G3" t="n">
-        <v>0.876395881175995</v>
+        <v>0.87639594078064</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>0.868066012859344</v>
+        <v>0.868066072463989</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>0.868066012859344</v>
+        <v>0.868066072463989</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>0.868066012859344</v>
+        <v>0.868066072463989</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>0.868066012859344</v>
+        <v>0.868066072463989</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G12" t="n">
-        <v>0.815455913543701</v>
+        <v>0.815455973148346</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>0.915000021457672</v>
       </c>
       <c r="G13" t="n">
-        <v>0.802303493022919</v>
+        <v>0.802303433418274</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>0.889500021934509</v>
       </c>
       <c r="G14" t="n">
-        <v>0.779944121837616</v>
+        <v>0.779944181442261</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G15" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G17" t="n">
-        <v>0.79791933298111</v>
+        <v>0.797919273376465</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G18" t="n">
-        <v>0.806687653064728</v>
+        <v>0.806687593460083</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>0.919000029563904</v>
       </c>
       <c r="G21" t="n">
-        <v>0.805810809135437</v>
+        <v>0.805810749530792</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G23" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G24" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G25" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G26" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G27" t="n">
-        <v>0.745309233665466</v>
+        <v>0.745309293270111</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>0.844500005245209</v>
       </c>
       <c r="G28" t="n">
-        <v>0.740486562252045</v>
+        <v>0.740486621856689</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G30" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G35" t="n">
-        <v>0.745309233665466</v>
+        <v>0.745309293270111</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>0.835500001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>0.732595086097717</v>
+        <v>0.732595026493073</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G37" t="n">
-        <v>0.745309233665466</v>
+        <v>0.745309293270111</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>0.806500017642975</v>
       </c>
       <c r="G39" t="n">
-        <v>0.707166850566864</v>
+        <v>0.707166910171509</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G42" t="n">
-        <v>0.77073734998703</v>
+        <v>0.770737409591675</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G43" t="n">
-        <v>0.79791933298111</v>
+        <v>0.797919273376465</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G44" t="n">
-        <v>0.824224233627319</v>
+        <v>0.824224293231964</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G45" t="n">
-        <v>0.824224233627319</v>
+        <v>0.824224293231964</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>0.827731668949127</v>
+        <v>0.827731609344482</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>0.929000020027161</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8145791888237</v>
+        <v>0.814579129219055</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G50" t="n">
-        <v>0.79791933298111</v>
+        <v>0.797919273376465</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>0.916499972343445</v>
       </c>
       <c r="G51" t="n">
-        <v>0.803618729114532</v>
+        <v>0.803618669509888</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G52" t="n">
-        <v>0.806249141693115</v>
+        <v>0.80624920129776</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G53" t="n">
-        <v>0.809318065643311</v>
+        <v>0.809318125247955</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G54" t="n">
-        <v>0.79791933298111</v>
+        <v>0.797919273376465</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G55" t="n">
-        <v>0.79791933298111</v>
+        <v>0.797919273376465</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G56" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G57" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G58" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G59" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G60" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G62" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>0.889500021934509</v>
       </c>
       <c r="G63" t="n">
-        <v>0.779944121837616</v>
+        <v>0.779944181442261</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G64" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G66" t="n">
-        <v>0.764599502086639</v>
+        <v>0.764599561691284</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G71" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092245578766</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>0.873000025749207</v>
       </c>
       <c r="G72" t="n">
-        <v>0.765476405620575</v>
+        <v>0.76547646522522</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G73" t="n">
-        <v>0.77073734998703</v>
+        <v>0.770737409591675</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G75" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G80" t="n">
-        <v>0.753200709819794</v>
+        <v>0.753200769424438</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>0.749693393707275</v>
+        <v>0.74969345331192</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>0.867500007152557</v>
       </c>
       <c r="G82" t="n">
-        <v>0.760653793811798</v>
+        <v>0.760653734207153</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>0.879499971866608</v>
       </c>
       <c r="G84" t="n">
-        <v>0.771175801753998</v>
+        <v>0.771175742149353</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G97" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>0.879000008106232</v>
       </c>
       <c r="G98" t="n">
-        <v>0.77073734998703</v>
+        <v>0.770737409591675</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G99" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G105" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G113" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G116" t="n">
-        <v>0.745309233665466</v>
+        <v>0.745309293270111</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G117" t="n">
-        <v>0.750570237636566</v>
+        <v>0.750570178031921</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G118" t="n">
-        <v>0.750570237636566</v>
+        <v>0.750570178031921</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G119" t="n">
-        <v>0.748816549777985</v>
+        <v>0.74881649017334</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G122" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G124" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G125" t="n">
-        <v>0.64841890335083</v>
+        <v>0.648418962955475</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G126" t="n">
-        <v>0.675162374973297</v>
+        <v>0.675162434577942</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G127" t="n">
-        <v>0.683930695056915</v>
+        <v>0.68393075466156</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G128" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G130" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G132" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G135" t="n">
-        <v>0.687438070774078</v>
+        <v>0.687438130378723</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G137" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G138" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>0.791000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>0.693575978279114</v>
+        <v>0.693575918674469</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G140" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G143" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G144" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>0.824500024318695</v>
       </c>
       <c r="G145" t="n">
-        <v>0.722949981689453</v>
+        <v>0.722949862480164</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G148" t="n">
-        <v>0.72163462638855</v>
+        <v>0.721634745597839</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G150" t="n">
-        <v>0.745309233665466</v>
+        <v>0.745309293270111</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G152" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>0.819500029087067</v>
       </c>
       <c r="G153" t="n">
-        <v>0.718565821647644</v>
+        <v>0.718565702438354</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G155" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G156" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G157" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G158" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G161" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G167" t="n">
-        <v>0.697083294391632</v>
+        <v>0.697083353996277</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G168" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G169" t="n">
-        <v>0.695329666137695</v>
+        <v>0.695329606533051</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>0.791000008583069</v>
       </c>
       <c r="G170" t="n">
-        <v>0.693575978279114</v>
+        <v>0.693575918674469</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>0.808499991893768</v>
       </c>
       <c r="G171" t="n">
-        <v>0.708920538425446</v>
+        <v>0.70892059803009</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G172" t="n">
-        <v>0.699713826179504</v>
+        <v>0.69971376657486</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G175" t="n">
-        <v>0.683930695056915</v>
+        <v>0.68393075466156</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G176" t="n">
-        <v>0.685684502124786</v>
+        <v>0.685684442520142</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G177" t="n">
-        <v>0.689191877841949</v>
+        <v>0.68919175863266</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G178" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G179" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G181" t="n">
-        <v>0.683930695056915</v>
+        <v>0.68393075466156</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>0.666394114494324</v>
+        <v>0.666394054889679</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>0.675162374973297</v>
+        <v>0.675162434577942</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>0.675162374973297</v>
+        <v>0.675162434577942</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>0.763499975204468</v>
       </c>
       <c r="G187" t="n">
-        <v>0.669462978839874</v>
+        <v>0.669463038444519</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G192" t="n">
-        <v>0.670778274536133</v>
+        <v>0.670778214931488</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G195" t="n">
-        <v>0.640089094638824</v>
+        <v>0.640089154243469</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G196" t="n">
-        <v>0.633074343204498</v>
+        <v>0.633074462413788</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G197" t="n">
-        <v>0.633074343204498</v>
+        <v>0.633074462413788</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G198" t="n">
-        <v>0.631320714950562</v>
+        <v>0.631320774555206</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>0.714999973773956</v>
       </c>
       <c r="G201" t="n">
-        <v>0.626936554908752</v>
+        <v>0.626936614513397</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G202" t="n">
-        <v>0.622552454471588</v>
+        <v>0.622552394866943</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>0.709500014781952</v>
       </c>
       <c r="G203" t="n">
-        <v>0.622113943099976</v>
+        <v>0.622113883495331</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>0.704500019550323</v>
       </c>
       <c r="G205" t="n">
-        <v>0.617729783058167</v>
+        <v>0.617729842662811</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>0.695500016212463</v>
       </c>
       <c r="G208" t="n">
-        <v>0.609838306903839</v>
+        <v>0.609838247299194</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>0.698499977588654</v>
       </c>
       <c r="G209" t="n">
-        <v>0.612468779087067</v>
+        <v>0.612468719482422</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>0.607207834720612</v>
+        <v>0.607207775115967</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>0.607207834720612</v>
+        <v>0.607207775115967</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G216" t="n">
-        <v>0.599754691123962</v>
+        <v>0.599754750728607</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G217" t="n">
-        <v>0.615537703037262</v>
+        <v>0.615537762641907</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G221" t="n">
-        <v>0.591863214969635</v>
+        <v>0.59186315536499</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G223" t="n">
-        <v>0.599754691123962</v>
+        <v>0.599754750728607</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G224" t="n">
-        <v>0.596247375011444</v>
+        <v>0.596247315406799</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>0.668500006198883</v>
       </c>
       <c r="G226" t="n">
-        <v>0.586163818836212</v>
+        <v>0.586163759231567</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>0.697499990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>0.611591994762421</v>
+        <v>0.611591935157776</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G231" t="n">
-        <v>0.614222466945648</v>
+        <v>0.614222407341003</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.709500014781952</v>
       </c>
       <c r="G233" t="n">
-        <v>0.622113943099976</v>
+        <v>0.622113883495331</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>0.704999983310699</v>
       </c>
       <c r="G234" t="n">
-        <v>0.61816817522049</v>
+        <v>0.618168234825134</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>0.691500008106232</v>
       </c>
       <c r="G235" t="n">
-        <v>0.606330990791321</v>
+        <v>0.606330931186676</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>0.611153542995453</v>
+        <v>0.611153602600098</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G237" t="n">
-        <v>0.605892479419708</v>
+        <v>0.605892539024353</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.690999984741211</v>
       </c>
       <c r="G238" t="n">
-        <v>0.605892479419708</v>
+        <v>0.605892539024353</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G239" t="n">
-        <v>0.594493687152863</v>
+        <v>0.594493627548218</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G241" t="n">
-        <v>0.595370531082153</v>
+        <v>0.595370590686798</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G242" t="n">
-        <v>0.596247375011444</v>
+        <v>0.596247315406799</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>0.685000002384186</v>
       </c>
       <c r="G244" t="n">
-        <v>0.600631535053253</v>
+        <v>0.600631475448608</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G248" t="n">
-        <v>0.631320714950562</v>
+        <v>0.631320774555206</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>0.702499985694885</v>
       </c>
       <c r="G251" t="n">
-        <v>0.61597615480423</v>
+        <v>0.615976095199585</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G252" t="n">
-        <v>0.615537703037262</v>
+        <v>0.615537762641907</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G256" t="n">
-        <v>0.631320714950562</v>
+        <v>0.631320774555206</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>0.735000014305115</v>
       </c>
       <c r="G257" t="n">
-        <v>0.644473195075989</v>
+        <v>0.644473254680634</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>0.768999993801117</v>
       </c>
       <c r="G258" t="n">
-        <v>0.674285590648651</v>
+        <v>0.674285531044006</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G259" t="n">
-        <v>0.666394114494324</v>
+        <v>0.666394054889679</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>0.666394114494324</v>
+        <v>0.666394054889679</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>0.754999995231628</v>
       </c>
       <c r="G261" t="n">
-        <v>0.662009954452515</v>
+        <v>0.66200989484787</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G264" t="n">
-        <v>0.676916182041168</v>
+        <v>0.676916062831879</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G265" t="n">
-        <v>0.669901490211487</v>
+        <v>0.669901371002197</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G266" t="n">
-        <v>0.671655058860779</v>
+        <v>0.671655118465424</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>0.682177186012268</v>
+        <v>0.682177066802979</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G269" t="n">
-        <v>0.682177186012268</v>
+        <v>0.682177066802979</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>0.675162374973297</v>
+        <v>0.675162434577942</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>0.778500020503998</v>
       </c>
       <c r="G271" t="n">
-        <v>0.682615518569946</v>
+        <v>0.682615578174591</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G272" t="n">
-        <v>0.671655058860779</v>
+        <v>0.671655118465424</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G274" t="n">
-        <v>0.699713826179504</v>
+        <v>0.69971376657486</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G278" t="n">
-        <v>0.666394114494324</v>
+        <v>0.666394054889679</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>0.761500000953674</v>
       </c>
       <c r="G279" t="n">
-        <v>0.667709290981293</v>
+        <v>0.667709350585938</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G282" t="n">
-        <v>0.683930695056915</v>
+        <v>0.68393075466156</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G284" t="n">
-        <v>0.670778274536133</v>
+        <v>0.670778214931488</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>0.761500000953674</v>
       </c>
       <c r="G285" t="n">
-        <v>0.667709290981293</v>
+        <v>0.667709350585938</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>0.767000019550323</v>
       </c>
       <c r="G286" t="n">
-        <v>0.672531962394714</v>
+        <v>0.67253190279007</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>0.763499975204468</v>
       </c>
       <c r="G288" t="n">
-        <v>0.669462978839874</v>
+        <v>0.669463038444519</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>0.761500000953674</v>
       </c>
       <c r="G289" t="n">
-        <v>0.667709290981293</v>
+        <v>0.667709350585938</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G290" t="n">
-        <v>0.670778274536133</v>
+        <v>0.670778214931488</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G292" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G295" t="n">
-        <v>0.713743150234222</v>
+        <v>0.713743209838867</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G301" t="n">
-        <v>0.713743150234222</v>
+        <v>0.713743209838867</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>0.819500029087067</v>
       </c>
       <c r="G304" t="n">
-        <v>0.718565821647644</v>
+        <v>0.718565702438354</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G306" t="n">
-        <v>0.745309233665466</v>
+        <v>0.745309293270111</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G307" t="n">
-        <v>0.745309233665466</v>
+        <v>0.745309293270111</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>0.810999989509583</v>
       </c>
       <c r="G313" t="n">
-        <v>0.71111261844635</v>
+        <v>0.711112678050995</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G314" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G316" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G317" t="n">
-        <v>0.717250466346741</v>
+        <v>0.717250525951385</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G318" t="n">
-        <v>0.72163462638855</v>
+        <v>0.721634745597839</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G321" t="n">
-        <v>0.731279790401459</v>
+        <v>0.731279909610748</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G323" t="n">
-        <v>0.727772533893585</v>
+        <v>0.72777247428894</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G324" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G326" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G327" t="n">
-        <v>0.72163462638855</v>
+        <v>0.721634745597839</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>0.819000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>0.718127310276031</v>
+        <v>0.718127369880676</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>0.828499972820282</v>
       </c>
       <c r="G333" t="n">
-        <v>0.726457238197327</v>
+        <v>0.726457178592682</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G334" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>0.824500024318695</v>
       </c>
       <c r="G336" t="n">
-        <v>0.722949981689453</v>
+        <v>0.722949862480164</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>0.813000023365021</v>
       </c>
       <c r="G340" t="n">
-        <v>0.712866246700287</v>
+        <v>0.712866306304932</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>0.810999989509583</v>
       </c>
       <c r="G343" t="n">
-        <v>0.71111261844635</v>
+        <v>0.711112678050995</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G344" t="n">
-        <v>0.71637374162674</v>
+        <v>0.71637362241745</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>0.8125</v>
       </c>
       <c r="G345" t="n">
-        <v>0.712427973747253</v>
+        <v>0.712427914142609</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>0.819000005722046</v>
       </c>
       <c r="G346" t="n">
-        <v>0.718127310276031</v>
+        <v>0.718127369880676</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G347" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G348" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>0.813000023365021</v>
       </c>
       <c r="G349" t="n">
-        <v>0.712866246700287</v>
+        <v>0.712866306304932</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>0.810500025749207</v>
       </c>
       <c r="G350" t="n">
-        <v>0.710674226284027</v>
+        <v>0.710674285888672</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>0.8125</v>
       </c>
       <c r="G351" t="n">
-        <v>0.712427973747253</v>
+        <v>0.712427914142609</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G353" t="n">
-        <v>0.717250466346741</v>
+        <v>0.717250525951385</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G354" t="n">
-        <v>0.713743150234222</v>
+        <v>0.713743209838867</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>0.810999989509583</v>
       </c>
       <c r="G356" t="n">
-        <v>0.71111261844635</v>
+        <v>0.711112678050995</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>0.819500029087067</v>
       </c>
       <c r="G357" t="n">
-        <v>0.718565821647644</v>
+        <v>0.718565702438354</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>0.819000005722046</v>
       </c>
       <c r="G358" t="n">
-        <v>0.718127310276031</v>
+        <v>0.718127369880676</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>0.820500016212463</v>
       </c>
       <c r="G359" t="n">
-        <v>0.71944260597229</v>
+        <v>0.719442665576935</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>0.823499977588654</v>
       </c>
       <c r="G360" t="n">
-        <v>0.722073078155518</v>
+        <v>0.722073018550873</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G361" t="n">
-        <v>0.725580453872681</v>
+        <v>0.725580394268036</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>0.828499972820282</v>
       </c>
       <c r="G363" t="n">
-        <v>0.726457238197327</v>
+        <v>0.726457178592682</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G365" t="n">
-        <v>0.724265098571777</v>
+        <v>0.724265158176422</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>0.826499998569489</v>
       </c>
       <c r="G366" t="n">
-        <v>0.72470360994339</v>
+        <v>0.724703550338745</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G367" t="n">
-        <v>0.727772533893585</v>
+        <v>0.72777247428894</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G371" t="n">
-        <v>0.887356400489807</v>
+        <v>0.887356340885162</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G372" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.05099999904633</v>
       </c>
       <c r="G373" t="n">
-        <v>0.921552896499634</v>
+        <v>0.921552777290344</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G374" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>1.06299996376038</v>
       </c>
       <c r="G375" t="n">
-        <v>0.932074844837189</v>
+        <v>0.932074904441833</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G376" t="n">
-        <v>0.936459064483643</v>
+        <v>0.936459004878998</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G383" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G384" t="n">
-        <v>1.00835955142975</v>
+        <v>1.00835943222046</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G385" t="n">
-        <v>1.01888144016266</v>
+        <v>1.01888155937195</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G388" t="n">
-        <v>1.05307793617249</v>
+        <v>1.05307805538177</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G391" t="n">
-        <v>1.055708527565</v>
+        <v>1.05570864677429</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G393" t="n">
-        <v>1.04781699180603</v>
+        <v>1.04781711101532</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G398" t="n">
-        <v>1.055708527565</v>
+        <v>1.05570864677429</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G399" t="n">
-        <v>1.05132448673248</v>
+        <v>1.05132436752319</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.20299994945526</v>
       </c>
       <c r="G407" t="n">
-        <v>1.05483174324036</v>
+        <v>1.05483162403107</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G413" t="n">
-        <v>1.05658555030823</v>
+        <v>1.05658543109894</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G415" t="n">
-        <v>1.05307793617249</v>
+        <v>1.05307805538177</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G417" t="n">
-        <v>1.05395483970642</v>
+        <v>1.05395495891571</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G418" t="n">
-        <v>1.05395483970642</v>
+        <v>1.05395495891571</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G421" t="n">
-        <v>1.04606318473816</v>
+        <v>1.04606342315674</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G422" t="n">
-        <v>1.055708527565</v>
+        <v>1.05570864677429</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G427" t="n">
-        <v>1.055708527565</v>
+        <v>1.05570864677429</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G428" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G430" t="n">
-        <v>1.20477044582367</v>
+        <v>1.20477032661438</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G431" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>1.27699995040894</v>
       </c>
       <c r="G432" t="n">
-        <v>1.11971747875214</v>
+        <v>1.11971735954285</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G434" t="n">
-        <v>1.17671179771423</v>
+        <v>1.17671167850494</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G437" t="n">
-        <v>1.11621010303497</v>
+        <v>1.11621022224426</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G439" t="n">
-        <v>1.12760901451111</v>
+        <v>1.12760889530182</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G440" t="n">
-        <v>1.10831868648529</v>
+        <v>1.108318567276</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>1.32299995422363</v>
       </c>
       <c r="G443" t="n">
-        <v>1.16005170345306</v>
+        <v>1.16005182266235</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G444" t="n">
-        <v>1.14163851737976</v>
+        <v>1.14163839817047</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G446" t="n">
-        <v>1.14952981472015</v>
+        <v>1.14952993392944</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G447" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303730964661</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G448" t="n">
-        <v>1.14076137542725</v>
+        <v>1.14076149463654</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.33899998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>1.17408132553101</v>
+        <v>1.17408120632172</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.34099996089935</v>
       </c>
       <c r="G454" t="n">
-        <v>1.1758348941803</v>
+        <v>1.17583501338959</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G455" t="n">
-        <v>1.159175157547</v>
+        <v>1.15917503833771</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>1.32200002670288</v>
       </c>
       <c r="G456" t="n">
-        <v>1.159175157547</v>
+        <v>1.15917503833771</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G458" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G459" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G461" t="n">
-        <v>1.16618990898132</v>
+        <v>1.16618978977203</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G462" t="n">
-        <v>1.16618990898132</v>
+        <v>1.16618978977203</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G463" t="n">
-        <v>1.18372642993927</v>
+        <v>1.18372631072998</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.34899997711182</v>
       </c>
       <c r="G464" t="n">
-        <v>1.18284940719604</v>
+        <v>1.18284952640533</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G466" t="n">
-        <v>1.18372642993927</v>
+        <v>1.18372631072998</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G468" t="n">
-        <v>1.21441566944122</v>
+        <v>1.21441555023193</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G471" t="n">
-        <v>1.19424831867218</v>
+        <v>1.19424843788147</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G472" t="n">
-        <v>1.21967661380768</v>
+        <v>1.21967649459839</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G473" t="n">
-        <v>1.21353852748871</v>
+        <v>1.21353876590729</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G475" t="n">
-        <v>1.19249475002289</v>
+        <v>1.1924946308136</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G476" t="n">
-        <v>1.20477044582367</v>
+        <v>1.20477032661438</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G478" t="n">
-        <v>1.19249475002289</v>
+        <v>1.1924946308136</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G479" t="n">
-        <v>1.19074106216431</v>
+        <v>1.1907411813736</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G480" t="n">
-        <v>1.17934215068817</v>
+        <v>1.17934226989746</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G485" t="n">
-        <v>1.14076137542725</v>
+        <v>1.14076149463654</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G487" t="n">
-        <v>1.14952981472015</v>
+        <v>1.14952993392944</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>1.33899998664856</v>
       </c>
       <c r="G489" t="n">
-        <v>1.17408132553101</v>
+        <v>1.17408120632172</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G490" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G491" t="n">
-        <v>1.18109595775604</v>
+        <v>1.18109583854675</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G493" t="n">
-        <v>1.20126307010651</v>
+        <v>1.20126295089722</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.35399997234344</v>
       </c>
       <c r="G494" t="n">
-        <v>1.18723356723785</v>
+        <v>1.18723368644714</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G495" t="n">
-        <v>1.18547999858856</v>
+        <v>1.18548011779785</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G496" t="n">
-        <v>1.18372642993927</v>
+        <v>1.18372631072998</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G497" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G499" t="n">
-        <v>1.18109595775604</v>
+        <v>1.18109583854675</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.34300005435944</v>
       </c>
       <c r="G500" t="n">
-        <v>1.17758846282959</v>
+        <v>1.17758870124817</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G503" t="n">
-        <v>1.14163851737976</v>
+        <v>1.14163839817047</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.28299999237061</v>
       </c>
       <c r="G507" t="n">
-        <v>1.12497842311859</v>
+        <v>1.12497854232788</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G508" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>1.28100001811981</v>
       </c>
       <c r="G511" t="n">
-        <v>1.12322461605072</v>
+        <v>1.1232248544693</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G512" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303730964661</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G514" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G515" t="n">
-        <v>1.13550055027008</v>
+        <v>1.13550043106079</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G519" t="n">
-        <v>1.16180562973022</v>
+        <v>1.16180574893951</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G520" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G522" t="n">
-        <v>1.17934215068817</v>
+        <v>1.17934226989746</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G523" t="n">
-        <v>1.26702570915222</v>
+        <v>1.26702558994293</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G524" t="n">
-        <v>1.2538731098175</v>
+        <v>1.25387322902679</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G525" t="n">
-        <v>1.23633635044098</v>
+        <v>1.23633646965027</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G526" t="n">
-        <v>1.23195230960846</v>
+        <v>1.23195219039917</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G528" t="n">
-        <v>1.24510490894318</v>
+        <v>1.24510478973389</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G530" t="n">
-        <v>1.2538731098175</v>
+        <v>1.25387322902679</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G531" t="n">
-        <v>1.2538731098175</v>
+        <v>1.25387322902679</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G533" t="n">
-        <v>1.23195230960846</v>
+        <v>1.23195219039917</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G534" t="n">
-        <v>1.21441566944122</v>
+        <v>1.21441555023193</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G535" t="n">
-        <v>1.24510490894318</v>
+        <v>1.24510478973389</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>1.21441566944122</v>
+        <v>1.21441555023193</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G537" t="n">
-        <v>1.18811070919037</v>
+        <v>1.18811058998108</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G539" t="n">
-        <v>1.1968789100647</v>
+        <v>1.19687879085541</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>1.22318398952484</v>
+        <v>1.22318387031555</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G542" t="n">
-        <v>1.20126307010651</v>
+        <v>1.20126295089722</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G543" t="n">
-        <v>1.19249475002289</v>
+        <v>1.1924946308136</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G544" t="n">
-        <v>1.20126307010651</v>
+        <v>1.20126295089722</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G547" t="n">
-        <v>1.20126307010651</v>
+        <v>1.20126295089722</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G549" t="n">
-        <v>1.20126307010651</v>
+        <v>1.20126295089722</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>1.17934215068817</v>
+        <v>1.17934226989746</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G553" t="n">
-        <v>1.18372642993927</v>
+        <v>1.18372631072998</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G554" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G557" t="n">
-        <v>1.18372642993927</v>
+        <v>1.18372631072998</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G558" t="n">
-        <v>1.17934215068817</v>
+        <v>1.17934226989746</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G560" t="n">
-        <v>1.18811070919037</v>
+        <v>1.18811058998108</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G561" t="n">
-        <v>1.19249475002289</v>
+        <v>1.1924946308136</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G562" t="n">
-        <v>1.18811070919037</v>
+        <v>1.18811058998108</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G563" t="n">
-        <v>1.18372642993927</v>
+        <v>1.18372631072998</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>1.17934215068817</v>
+        <v>1.17934226989746</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G565" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G567" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G568" t="n">
-        <v>1.16180562973022</v>
+        <v>1.16180574893951</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G571" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G572" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G573" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303730964661</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303730964661</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G575" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G576" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G577" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303730964661</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G578" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303730964661</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G579" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G581" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303730964661</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G583" t="n">
-        <v>1.16180562973022</v>
+        <v>1.16180574893951</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G584" t="n">
-        <v>1.16180562973022</v>
+        <v>1.16180574893951</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G588" t="n">
-        <v>1.13550055027008</v>
+        <v>1.13550043106079</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G589" t="n">
-        <v>1.13550055027008</v>
+        <v>1.13550043106079</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G591" t="n">
-        <v>1.13550055027008</v>
+        <v>1.13550043106079</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G593" t="n">
-        <v>1.13550055027008</v>
+        <v>1.13550043106079</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G594" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G596" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G597" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G598" t="n">
-        <v>1.16618990898132</v>
+        <v>1.16618978977203</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G599" t="n">
-        <v>1.16180562973022</v>
+        <v>1.16180574893951</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G600" t="n">
-        <v>1.16180562973022</v>
+        <v>1.16180574893951</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G601" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G602" t="n">
-        <v>1.15303719043732</v>
+        <v>1.15303730964661</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G604" t="n">
-        <v>1.13550055027008</v>
+        <v>1.13550043106079</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G605" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G606" t="n">
-        <v>1.11796391010284</v>
+        <v>1.11796379089355</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G607" t="n">
-        <v>1.11796391010284</v>
+        <v>1.11796379089355</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G608" t="n">
-        <v>1.11796391010284</v>
+        <v>1.11796379089355</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G610" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G619" t="n">
-        <v>1.11796391010284</v>
+        <v>1.11796379089355</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G622" t="n">
-        <v>1.13550055027008</v>
+        <v>1.13550043106079</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G623" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G628" t="n">
-        <v>1.13550055027008</v>
+        <v>1.13550043106079</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G629" t="n">
-        <v>1.13550055027008</v>
+        <v>1.13550043106079</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G630" t="n">
-        <v>1.13550055027008</v>
+        <v>1.13550043106079</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G634" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G635" t="n">
-        <v>1.13550055027008</v>
+        <v>1.13550043106079</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G639" t="n">
-        <v>1.11796391010284</v>
+        <v>1.11796379089355</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G641" t="n">
-        <v>1.10481131076813</v>
+        <v>1.10481119155884</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G642" t="n">
-        <v>1.11796391010284</v>
+        <v>1.11796379089355</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G643" t="n">
-        <v>1.10481131076813</v>
+        <v>1.10481119155884</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G645" t="n">
-        <v>1.13550055027008</v>
+        <v>1.13550043106079</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G651" t="n">
-        <v>1.10481131076813</v>
+        <v>1.10481119155884</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G653" t="n">
-        <v>1.10481131076813</v>
+        <v>1.10481119155884</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G655" t="n">
-        <v>1.10481131076813</v>
+        <v>1.10481119155884</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G661" t="n">
-        <v>1.10481131076813</v>
+        <v>1.10481119155884</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G662" t="n">
-        <v>1.10481131076813</v>
+        <v>1.10481119155884</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G663" t="n">
-        <v>1.10481131076813</v>
+        <v>1.10481119155884</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.25</v>
       </c>
       <c r="G669" t="n">
-        <v>1.09604299068451</v>
+        <v>1.09604287147522</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>1.25</v>
       </c>
       <c r="G671" t="n">
-        <v>1.09604299068451</v>
+        <v>1.09604287147522</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G672" t="n">
-        <v>1.08727467060089</v>
+        <v>1.0872745513916</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G675" t="n">
-        <v>1.06973779201508</v>
+        <v>1.06973791122437</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G676" t="n">
-        <v>1.06973779201508</v>
+        <v>1.06973791122437</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G677" t="n">
-        <v>1.06973779201508</v>
+        <v>1.06973791122437</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G682" t="n">
-        <v>1.05658555030823</v>
+        <v>1.05658543109894</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>1.06973779201508</v>
+        <v>1.06973791122437</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G686" t="n">
-        <v>1.06973779201508</v>
+        <v>1.06973791122437</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G696" t="n">
-        <v>1.08727467060089</v>
+        <v>1.0872745513916</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G697" t="n">
-        <v>1.10481131076813</v>
+        <v>1.10481119155884</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>1.13111615180969</v>
+        <v>1.13111627101898</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.25</v>
       </c>
       <c r="G708" t="n">
-        <v>1.09604299068451</v>
+        <v>1.09604287147522</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.25</v>
       </c>
       <c r="G718" t="n">
-        <v>1.09604299068451</v>
+        <v>1.09604287147522</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.25</v>
       </c>
       <c r="G719" t="n">
-        <v>1.09604299068451</v>
+        <v>1.09604287147522</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.25</v>
       </c>
       <c r="G721" t="n">
-        <v>1.09604299068451</v>
+        <v>1.09604287147522</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.25</v>
       </c>
       <c r="G722" t="n">
-        <v>1.09604299068451</v>
+        <v>1.09604287147522</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.25</v>
       </c>
       <c r="G723" t="n">
-        <v>1.09604299068451</v>
+        <v>1.09604287147522</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.25</v>
       </c>
       <c r="G724" t="n">
-        <v>1.09604299068451</v>
+        <v>1.09604287147522</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.25</v>
       </c>
       <c r="G725" t="n">
-        <v>1.09604299068451</v>
+        <v>1.09604287147522</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G727" t="n">
-        <v>1.08727467060089</v>
+        <v>1.0872745513916</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G728" t="n">
-        <v>1.08727467060089</v>
+        <v>1.0872745513916</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.25</v>
       </c>
       <c r="G729" t="n">
-        <v>1.09604299068451</v>
+        <v>1.09604287147522</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G730" t="n">
-        <v>1.08727467060089</v>
+        <v>1.0872745513916</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G738" t="n">
-        <v>1.01712775230408</v>
+        <v>1.01712787151337</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G744" t="n">
-        <v>1.0258960723877</v>
+        <v>1.02589619159698</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.02151191234589</v>
+        <v>1.02151203155518</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G747" t="n">
-        <v>1.01712775230408</v>
+        <v>1.01712787151337</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G748" t="n">
-        <v>1.01712775230408</v>
+        <v>1.01712787151337</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G749" t="n">
-        <v>1.00835955142975</v>
+        <v>1.00835943222046</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G750" t="n">
-        <v>1.00835955142975</v>
+        <v>1.00835943222046</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G751" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G754" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.125</v>
       </c>
       <c r="G755" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G760" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1</v>
       </c>
       <c r="G762" t="n">
-        <v>0.876834332942963</v>
+        <v>0.876834392547607</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G766" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G767" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G768" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.01274371147156</v>
+        <v>1.01274347305298</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G771" t="n">
-        <v>1.0258960723877</v>
+        <v>1.02589619159698</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G772" t="n">
-        <v>1.0258960723877</v>
+        <v>1.02589619159698</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G773" t="n">
-        <v>1.0258960723877</v>
+        <v>1.02589619159698</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G774" t="n">
-        <v>1.0258960723877</v>
+        <v>1.02589619159698</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G775" t="n">
-        <v>1.0258960723877</v>
+        <v>1.02589619159698</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G776" t="n">
-        <v>1.0258960723877</v>
+        <v>1.02589619159698</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.125</v>
       </c>
       <c r="G777" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G778" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G779" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G780" t="n">
-        <v>1.0258960723877</v>
+        <v>1.02589619159698</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G788" t="n">
-        <v>0.960133731365204</v>
+        <v>0.960133671760559</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G796" t="n">
-        <v>1.00835955142975</v>
+        <v>1.00835943222046</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G797" t="n">
-        <v>1.01712775230408</v>
+        <v>1.01712787151337</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G798" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G803" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.125</v>
       </c>
       <c r="G809" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G811" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G812" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.125</v>
       </c>
       <c r="G813" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G814" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G817" t="n">
-        <v>1.0258960723877</v>
+        <v>1.02589619159698</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G823" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G824" t="n">
-        <v>1.00835955142975</v>
+        <v>1.00835943222046</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G825" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G826" t="n">
-        <v>1.00835955142975</v>
+        <v>1.00835943222046</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G827" t="n">
-        <v>1.00835955142975</v>
+        <v>1.00835943222046</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G835" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.125</v>
       </c>
       <c r="G836" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.125</v>
       </c>
       <c r="G837" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.125</v>
       </c>
       <c r="G838" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.125</v>
       </c>
       <c r="G839" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G841" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G843" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G844" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G845" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G849" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.125</v>
       </c>
       <c r="G851" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G852" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G854" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G855" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G856" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G857" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G859" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G860" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G861" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G862" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G863" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G864" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G865" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G866" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G868" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G870" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G880" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G887" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G888" t="n">
-        <v>1.00835955142975</v>
+        <v>1.00835943222046</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G889" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.125</v>
       </c>
       <c r="G890" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G898" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G899" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G900" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G901" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G902" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G903" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G904" t="n">
-        <v>1.00835955142975</v>
+        <v>1.00835943222046</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G905" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G907" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G908" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G909" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G911" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G913" t="n">
-        <v>0.960133731365204</v>
+        <v>0.960133671760559</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G914" t="n">
-        <v>0.960133731365204</v>
+        <v>0.960133671760559</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G916" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G917" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G918" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G921" t="n">
-        <v>0.88998681306839</v>
+        <v>0.889986872673035</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1</v>
       </c>
       <c r="G922" t="n">
-        <v>0.876834332942963</v>
+        <v>0.876834392547607</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1</v>
       </c>
       <c r="G923" t="n">
-        <v>0.876834332942963</v>
+        <v>0.876834392547607</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G924" t="n">
-        <v>0.868066012859344</v>
+        <v>0.868066072463989</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G925" t="n">
-        <v>0.88998681306839</v>
+        <v>0.889986872673035</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G926" t="n">
-        <v>0.88998681306839</v>
+        <v>0.889986872673035</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1</v>
       </c>
       <c r="G927" t="n">
-        <v>0.876834332942963</v>
+        <v>0.876834392547607</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G928" t="n">
-        <v>0.88998681306839</v>
+        <v>0.889986872673035</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G930" t="n">
-        <v>0.88998681306839</v>
+        <v>0.889986872673035</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G932" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G934" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G935" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G936" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G937" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G938" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G939" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G942" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G944" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G945" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G946" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G949" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G950" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G951" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G954" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G955" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G956" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G957" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G958" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G959" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G960" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G961" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G962" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G963" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G964" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G965" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G967" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G969" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G970" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G971" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G972" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G973" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G974" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G975" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G976" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G977" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G978" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G979" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G980" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G981" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G985" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G986" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G987" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G988" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G991" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G992" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G993" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G994" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G999" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.960133731365204</v>
+        <v>0.960133671760559</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1007" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.125</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1011" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1019" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.960133731365204</v>
+        <v>0.960133671760559</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1021" t="n">
-        <v>0.960133731365204</v>
+        <v>0.960133671760559</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.960133731365204</v>
+        <v>0.960133671760559</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1035" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1040" t="n">
-        <v>0.894371092319489</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1041" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1042" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.894371092319489</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1044" t="n">
-        <v>0.898755192756653</v>
+        <v>0.898755133152008</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1045" t="n">
-        <v>0.88998681306839</v>
+        <v>0.889986872673035</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.885602712631226</v>
+        <v>0.88560277223587</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>0.894371092319489</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.885602712631226</v>
+        <v>0.88560277223587</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.875080764293671</v>
+        <v>0.875080704689026</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.876834332942963</v>
+        <v>0.876834392547607</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.866312384605408</v>
+        <v>0.866312325000763</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.868066012859344</v>
+        <v>0.868066072463989</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.675162374973297</v>
+        <v>0.675162434577942</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.666394114494324</v>
+        <v>0.666394054889679</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.638335406780243</v>
+        <v>0.638335347175598</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.675162374973297</v>
+        <v>0.675162434577942</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.724265098571777</v>
+        <v>0.724265158176422</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.720757901668549</v>
+        <v>0.720757842063904</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.727772533893585</v>
+        <v>0.72777247428894</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.724265098571777</v>
+        <v>0.724265158176422</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.752323806285858</v>
+        <v>0.752323925495148</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.752323806285858</v>
+        <v>0.752323925495148</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092245578766</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.752323806285858</v>
+        <v>0.752323925495148</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.750570237636566</v>
+        <v>0.750570178031921</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.750570237636566</v>
+        <v>0.750570178031921</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.745309233665466</v>
+        <v>0.745309293270111</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.720757901668549</v>
+        <v>0.720757842063904</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.727772533893585</v>
+        <v>0.72777247428894</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.727772533893585</v>
+        <v>0.72777247428894</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.748816549777985</v>
+        <v>0.74881649017334</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.745309233665466</v>
+        <v>0.745309293270111</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.727772533893585</v>
+        <v>0.72777247428894</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.731279790401459</v>
+        <v>0.731279909610748</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.729526281356812</v>
+        <v>0.729526221752167</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.729526281356812</v>
+        <v>0.729526221752167</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.708482205867767</v>
+        <v>0.708482146263123</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.724265098571777</v>
+        <v>0.724265158176422</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.708482205867767</v>
+        <v>0.708482146263123</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.713743150234222</v>
+        <v>0.713743209838867</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.703221142292023</v>
+        <v>0.703221201896667</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.713743150234222</v>
+        <v>0.713743209838867</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.717250466346741</v>
+        <v>0.717250525951385</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.689191877841949</v>
+        <v>0.68919175863266</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.683930695056915</v>
+        <v>0.68393075466156</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.676916182041168</v>
+        <v>0.676916062831879</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.676916182041168</v>
+        <v>0.676916062831879</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.671655058860779</v>
+        <v>0.671655118465424</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.64535003900528</v>
+        <v>0.645350098609924</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.64535003900528</v>
+        <v>0.645350098609924</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.676916182041168</v>
+        <v>0.676916062831879</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.666394114494324</v>
+        <v>0.666394054889679</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.682177186012268</v>
+        <v>0.682177066802979</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.671655058860779</v>
+        <v>0.671655118465424</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.671655058860779</v>
+        <v>0.671655118465424</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.668147802352905</v>
+        <v>0.66814774274826</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.668147802352905</v>
+        <v>0.66814774274826</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.720757901668549</v>
+        <v>0.720757842063904</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.752323806285858</v>
+        <v>0.752323925495148</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.727772533893585</v>
+        <v>0.72777247428894</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.704974830150604</v>
+        <v>0.704974770545959</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.724265098571777</v>
+        <v>0.724265158176422</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.704974830150604</v>
+        <v>0.704974770545959</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.704974830150604</v>
+        <v>0.704974770545959</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.704974830150604</v>
+        <v>0.704974770545959</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.717250466346741</v>
+        <v>0.717250525951385</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.717250466346741</v>
+        <v>0.717250525951385</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.675162374973297</v>
+        <v>0.675162434577942</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.687438070774078</v>
+        <v>0.687438130378723</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.675162374973297</v>
+        <v>0.675162434577942</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.666394114494324</v>
+        <v>0.666394054889679</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.661133170127869</v>
+        <v>0.661133110523224</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.683930695056915</v>
+        <v>0.68393075466156</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.669901490211487</v>
+        <v>0.669901371002197</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.669901490211487</v>
+        <v>0.669901371002197</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.669901490211487</v>
+        <v>0.669901371002197</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.669901490211487</v>
+        <v>0.669901371002197</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.666394114494324</v>
+        <v>0.666394054889679</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.683930695056915</v>
+        <v>0.68393075466156</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.675162374973297</v>
+        <v>0.675162434577942</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.699713826179504</v>
+        <v>0.69971376657486</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.699713826179504</v>
+        <v>0.69971376657486</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.683930695056915</v>
+        <v>0.68393075466156</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.683930695056915</v>
+        <v>0.68393075466156</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.661133170127869</v>
+        <v>0.661133110523224</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.631320714950562</v>
+        <v>0.631320774555206</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.676916182041168</v>
+        <v>0.676916062831879</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.661133170127869</v>
+        <v>0.661133110523224</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.640089094638824</v>
+        <v>0.640089154243469</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.652364730834961</v>
+        <v>0.652364790439606</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.652364730834961</v>
+        <v>0.652364790439606</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.699713826179504</v>
+        <v>0.69971376657486</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.685684502124786</v>
+        <v>0.685684442520142</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.720757901668549</v>
+        <v>0.720757842063904</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.689191877841949</v>
+        <v>0.68919175863266</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.704974830150604</v>
+        <v>0.704974770545959</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.717250466346741</v>
+        <v>0.717250525951385</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.703221142292023</v>
+        <v>0.703221201896667</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.727772533893585</v>
+        <v>0.72777247428894</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.708482205867767</v>
+        <v>0.708482146263123</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.724265098571777</v>
+        <v>0.724265158176422</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.727772533893585</v>
+        <v>0.72777247428894</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.808441281318665</v>
+        <v>0.80844122171402</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.820716917514801</v>
+        <v>0.820716857910156</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.79791933298111</v>
+        <v>0.797919273376465</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.815455913543701</v>
+        <v>0.815455973148346</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.750570237636566</v>
+        <v>0.750570178031921</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.764599502086639</v>
+        <v>0.764599561691284</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.747062802314758</v>
+        <v>0.747062861919403</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092245578766</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092245578766</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092245578766</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092245578766</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.778628945350647</v>
+        <v>0.778628826141357</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.79791933298111</v>
+        <v>0.797919273376465</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.80318021774292</v>
+        <v>0.803180277347565</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.815455913543701</v>
+        <v>0.815455973148346</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.815455913543701</v>
+        <v>0.815455973148346</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.806687653064728</v>
+        <v>0.806687593460083</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.794411957263947</v>
+        <v>0.794411897659302</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092245578766</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.761092185974121</v>
+        <v>0.761092245578766</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.748816549777985</v>
+        <v>0.74881649017334</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.747062802314758</v>
+        <v>0.747062861919403</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.745309233665466</v>
+        <v>0.745309293270111</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.778628945350647</v>
+        <v>0.778628826141357</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.778628945350647</v>
+        <v>0.778628826141357</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.776875197887421</v>
+        <v>0.776875138282776</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.771614193916321</v>
+        <v>0.771614253520966</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.775121569633484</v>
+        <v>0.775121510028839</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.776875197887421</v>
+        <v>0.776875138282776</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.79791933298111</v>
+        <v>0.797919273376465</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.780382573604584</v>
+        <v>0.780382513999939</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.79791933298111</v>
+        <v>0.797919273376465</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.789150953292847</v>
+        <v>0.789150834083557</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.79791933298111</v>
+        <v>0.797919273376465</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.815455913543701</v>
+        <v>0.815455973148346</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.815455913543701</v>
+        <v>0.815455973148346</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.813702285289764</v>
+        <v>0.81370222568512</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.813702285289764</v>
+        <v>0.81370222568512</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.836499989032745</v>
+        <v>0.836499929428101</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.824224233627319</v>
+        <v>0.824224293231964</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.836499989032745</v>
+        <v>0.836499929428101</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.836499989032745</v>
+        <v>0.836499929428101</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.854036629199982</v>
+        <v>0.854036688804626</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.836499989032745</v>
+        <v>0.836499929428101</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.829485237598419</v>
+        <v>0.829485297203064</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.843514621257782</v>
+        <v>0.843514680862427</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1405" t="n">
-        <v>0.836499989032745</v>
+        <v>0.836499929428101</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.829485237598419</v>
+        <v>0.829485297203064</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.836499989032745</v>
+        <v>0.836499929428101</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.894371092319489</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.885602712631226</v>
+        <v>0.88560277223587</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.88998681306839</v>
+        <v>0.889986872673035</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.894371092319489</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>1</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.876834332942963</v>
+        <v>0.876834392547607</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>1</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.876834332942963</v>
+        <v>0.876834392547607</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.881218492984772</v>
+        <v>0.881218552589417</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.894371092319489</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.898755192756653</v>
+        <v>0.898755133152008</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.894371092319489</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.88998681306839</v>
+        <v>0.889986872673035</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1433" t="n">
-        <v>0.898755192756653</v>
+        <v>0.898755133152008</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.881218492984772</v>
+        <v>0.881218552589417</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.881218492984772</v>
+        <v>0.881218552589417</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.894371092319489</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.881218492984772</v>
+        <v>0.881218552589417</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.875080764293671</v>
+        <v>0.875080704689026</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.881218492984772</v>
+        <v>0.881218552589417</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.885602712631226</v>
+        <v>0.88560277223587</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.88998681306839</v>
+        <v>0.889986872673035</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.894371092319489</v>
+        <v>0.894371032714844</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.898755192756653</v>
+        <v>0.898755133152008</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.01274371147156</v>
+        <v>1.01274347305298</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.01274371147156</v>
+        <v>1.01274347305298</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.00835955142975</v>
+        <v>1.00835943222046</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.06535375118256</v>
+        <v>1.06535387039185</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1480" t="n">
-        <v>1.06973779201508</v>
+        <v>1.06973791122437</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.0258960723877</v>
+        <v>1.02589619159698</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.01274371147156</v>
+        <v>1.01274347305298</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.01712775230408</v>
+        <v>1.01712787151337</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.06973779201508</v>
+        <v>1.06973791122437</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.06535375118256</v>
+        <v>1.06535387039185</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1501" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>1.125</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1510" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>1.125</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>1.125</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>1.125</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>1.125</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>1.125</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.960133731365204</v>
+        <v>0.960133671760559</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>1.125</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1535" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.960133731365204</v>
+        <v>0.960133671760559</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>1.125</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1567" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>1</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.876834332942963</v>
+        <v>0.876834392547607</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.885602712631226</v>
+        <v>0.88560277223587</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1581" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.929444372653961</v>
+        <v>0.929444313049316</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.920676112174988</v>
+        <v>0.920675992965698</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1585" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.925060272216797</v>
+        <v>0.925060212612152</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1588" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1590" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.01712775230408</v>
+        <v>1.01712787151337</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.01712775230408</v>
+        <v>1.01712787151337</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.01274371147156</v>
+        <v>1.01274347305298</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1595" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.00835955142975</v>
+        <v>1.00835943222046</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.01712775230408</v>
+        <v>1.01712787151337</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.00397527217865</v>
+        <v>1.00397515296936</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1601" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1602" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1603" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.982054531574249</v>
+        <v>0.982054591178894</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1610" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1611" t="n">
-        <v>0.973286151885986</v>
+        <v>0.973286211490631</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>1.125</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.97767037153244</v>
+        <v>0.977670311927795</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.960133731365204</v>
+        <v>0.960133671760559</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.960133731365204</v>
+        <v>0.960133671760559</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.95574939250946</v>
+        <v>0.95574951171875</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.951365351676941</v>
+        <v>0.951365232467651</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.968902051448822</v>
+        <v>0.968901991844177</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>1.125</v>
       </c>
       <c r="G1623" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.990822792053223</v>
+        <v>0.990822911262512</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>2.59999990463257</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>7349</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CED.MI.xlsx
+++ b/data/CED.MI.xlsx
@@ -427,7 +427,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H2" t="n">
         <v>1873</v>
@@ -456,7 +456,7 @@
         <v>0.999499976634979</v>
       </c>
       <c r="G3" t="n">
-        <v>0.87639594078064</v>
+        <v>0.876395881175995</v>
       </c>
       <c r="H3" t="n">
         <v>20697</v>
@@ -485,7 +485,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H4" t="n">
         <v>1336</v>
@@ -514,7 +514,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H5" t="n">
         <v>26664</v>
@@ -543,7 +543,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H6" t="n">
         <v>22147</v>
@@ -572,7 +572,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H7" t="n">
         <v>1765</v>
@@ -601,7 +601,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>0.859297752380371</v>
+        <v>0.859297633171082</v>
       </c>
       <c r="H8" t="n">
         <v>31855</v>
@@ -630,7 +630,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G9" t="n">
-        <v>0.859297752380371</v>
+        <v>0.859297633171082</v>
       </c>
       <c r="H9" t="n">
         <v>7824</v>
@@ -688,7 +688,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G11" t="n">
-        <v>0.822470605373383</v>
+        <v>0.822470664978027</v>
       </c>
       <c r="H11" t="n">
         <v>23559</v>
@@ -775,7 +775,7 @@
         <v>0.889500021934509</v>
       </c>
       <c r="G14" t="n">
-        <v>0.779944241046906</v>
+        <v>0.779944181442261</v>
       </c>
       <c r="H14" t="n">
         <v>28651</v>
@@ -862,7 +862,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G17" t="n">
-        <v>0.797919273376465</v>
+        <v>0.79791933298111</v>
       </c>
       <c r="H17" t="n">
         <v>3738</v>
@@ -891,7 +891,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G18" t="n">
-        <v>0.806687593460083</v>
+        <v>0.806687533855438</v>
       </c>
       <c r="H18" t="n">
         <v>9091</v>
@@ -1007,7 +1007,7 @@
         <v>0.899500012397766</v>
       </c>
       <c r="G22" t="n">
-        <v>0.788712501525879</v>
+        <v>0.788712441921234</v>
       </c>
       <c r="H22" t="n">
         <v>11023</v>
@@ -1152,7 +1152,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G27" t="n">
-        <v>0.745309174060822</v>
+        <v>0.745309233665466</v>
       </c>
       <c r="H27" t="n">
         <v>8370</v>
@@ -1181,7 +1181,7 @@
         <v>0.844500005245209</v>
       </c>
       <c r="G28" t="n">
-        <v>0.740486621856689</v>
+        <v>0.740486562252045</v>
       </c>
       <c r="H28" t="n">
         <v>19217</v>
@@ -1239,7 +1239,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G30" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H30" t="n">
         <v>13001</v>
@@ -1355,7 +1355,7 @@
         <v>0.841499984264374</v>
       </c>
       <c r="G34" t="n">
-        <v>0.737856030464172</v>
+        <v>0.737856090068817</v>
       </c>
       <c r="H34" t="n">
         <v>13088</v>
@@ -1384,7 +1384,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G35" t="n">
-        <v>0.745309174060822</v>
+        <v>0.745309233665466</v>
       </c>
       <c r="H35" t="n">
         <v>8182</v>
@@ -1442,7 +1442,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G37" t="n">
-        <v>0.745309174060822</v>
+        <v>0.745309233665466</v>
       </c>
       <c r="H37" t="n">
         <v>2765</v>
@@ -1471,7 +1471,7 @@
         <v>0.854499995708466</v>
       </c>
       <c r="G38" t="n">
-        <v>0.749254941940308</v>
+        <v>0.749255001544952</v>
       </c>
       <c r="H38" t="n">
         <v>3746</v>
@@ -1558,7 +1558,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G41" t="n">
-        <v>0.754077553749084</v>
+        <v>0.754077613353729</v>
       </c>
       <c r="H41" t="n">
         <v>37349</v>
@@ -1616,7 +1616,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G43" t="n">
-        <v>0.797919273376465</v>
+        <v>0.79791933298111</v>
       </c>
       <c r="H43" t="n">
         <v>64169</v>
@@ -1761,7 +1761,7 @@
         <v>0.929000020027161</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8145791888237</v>
+        <v>0.814579129219055</v>
       </c>
       <c r="H48" t="n">
         <v>16277</v>
@@ -1819,7 +1819,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G50" t="n">
-        <v>0.797919273376465</v>
+        <v>0.79791933298111</v>
       </c>
       <c r="H50" t="n">
         <v>32069</v>
@@ -1906,7 +1906,7 @@
         <v>0.922999978065491</v>
       </c>
       <c r="G53" t="n">
-        <v>0.809318065643311</v>
+        <v>0.809318125247955</v>
       </c>
       <c r="H53" t="n">
         <v>3772</v>
@@ -1935,7 +1935,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G54" t="n">
-        <v>0.797919273376465</v>
+        <v>0.79791933298111</v>
       </c>
       <c r="H54" t="n">
         <v>1460</v>
@@ -1964,7 +1964,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G55" t="n">
-        <v>0.797919273376465</v>
+        <v>0.79791933298111</v>
       </c>
       <c r="H55" t="n">
         <v>4868</v>
@@ -2138,7 +2138,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G61" t="n">
-        <v>0.766353249549866</v>
+        <v>0.766353189945221</v>
       </c>
       <c r="H61" t="n">
         <v>13280</v>
@@ -2196,7 +2196,7 @@
         <v>0.889500021934509</v>
       </c>
       <c r="G63" t="n">
-        <v>0.779944241046906</v>
+        <v>0.779944181442261</v>
       </c>
       <c r="H63" t="n">
         <v>1930</v>
@@ -2254,7 +2254,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G65" t="n">
-        <v>0.768106877803802</v>
+        <v>0.768106818199158</v>
       </c>
       <c r="H65" t="n">
         <v>4469</v>
@@ -2283,7 +2283,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G66" t="n">
-        <v>0.764599561691284</v>
+        <v>0.764599502086639</v>
       </c>
       <c r="H66" t="n">
         <v>1430</v>
@@ -2312,7 +2312,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>0.755831182003021</v>
+        <v>0.755831241607666</v>
       </c>
       <c r="H67" t="n">
         <v>7264</v>
@@ -2341,7 +2341,7 @@
         <v>0.854499995708466</v>
       </c>
       <c r="G68" t="n">
-        <v>0.749254941940308</v>
+        <v>0.749255001544952</v>
       </c>
       <c r="H68" t="n">
         <v>16345</v>
@@ -2370,7 +2370,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G69" t="n">
-        <v>0.754077553749084</v>
+        <v>0.754077613353729</v>
       </c>
       <c r="H69" t="n">
         <v>18328</v>
@@ -2399,7 +2399,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G70" t="n">
-        <v>0.75933849811554</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H70" t="n">
         <v>23506</v>
@@ -2457,7 +2457,7 @@
         <v>0.873000025749207</v>
       </c>
       <c r="G72" t="n">
-        <v>0.765476405620575</v>
+        <v>0.76547646522522</v>
       </c>
       <c r="H72" t="n">
         <v>5345</v>
@@ -2573,7 +2573,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G76" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H76" t="n">
         <v>16340</v>
@@ -2602,7 +2602,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G77" t="n">
-        <v>0.754077553749084</v>
+        <v>0.754077613353729</v>
       </c>
       <c r="H77" t="n">
         <v>55275</v>
@@ -2631,7 +2631,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>0.758461773395538</v>
+        <v>0.758461713790894</v>
       </c>
       <c r="H78" t="n">
         <v>43265</v>
@@ -2660,7 +2660,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G79" t="n">
-        <v>0.754077553749084</v>
+        <v>0.754077613353729</v>
       </c>
       <c r="H79" t="n">
         <v>20202</v>
@@ -2689,7 +2689,7 @@
         <v>0.859000027179718</v>
       </c>
       <c r="G80" t="n">
-        <v>0.753200709819794</v>
+        <v>0.753200769424438</v>
       </c>
       <c r="H80" t="n">
         <v>589</v>
@@ -2718,7 +2718,7 @@
         <v>0.855000019073486</v>
       </c>
       <c r="G81" t="n">
-        <v>0.749693393707275</v>
+        <v>0.74969345331192</v>
       </c>
       <c r="H81" t="n">
         <v>100365</v>
@@ -2747,7 +2747,7 @@
         <v>0.867500007152557</v>
       </c>
       <c r="G82" t="n">
-        <v>0.760653853416443</v>
+        <v>0.760653793811798</v>
       </c>
       <c r="H82" t="n">
         <v>28421</v>
@@ -2805,7 +2805,7 @@
         <v>0.879499971866608</v>
       </c>
       <c r="G84" t="n">
-        <v>0.771175742149353</v>
+        <v>0.771175801753998</v>
       </c>
       <c r="H84" t="n">
         <v>57949</v>
@@ -2834,7 +2834,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G85" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H85" t="n">
         <v>2623</v>
@@ -2892,7 +2892,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H87" t="n">
         <v>17178</v>
@@ -2921,7 +2921,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G88" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H88" t="n">
         <v>3425</v>
@@ -2950,7 +2950,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G89" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H89" t="n">
         <v>8952</v>
@@ -2979,7 +2979,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G90" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H90" t="n">
         <v>2490</v>
@@ -3008,7 +3008,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G91" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H91" t="n">
         <v>1711</v>
@@ -3037,7 +3037,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G92" t="n">
-        <v>0.754077553749084</v>
+        <v>0.754077613353729</v>
       </c>
       <c r="H92" t="n">
         <v>6553</v>
@@ -3066,7 +3066,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G93" t="n">
-        <v>0.754077553749084</v>
+        <v>0.754077613353729</v>
       </c>
       <c r="H93" t="n">
         <v>29406</v>
@@ -3095,7 +3095,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G94" t="n">
-        <v>0.758461773395538</v>
+        <v>0.758461713790894</v>
       </c>
       <c r="H94" t="n">
         <v>3114</v>
@@ -3124,7 +3124,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G95" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H95" t="n">
         <v>8838</v>
@@ -3153,7 +3153,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G96" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G100" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H100" t="n">
         <v>19142</v>
@@ -3298,7 +3298,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G101" t="n">
-        <v>0.768106877803802</v>
+        <v>0.768106818199158</v>
       </c>
       <c r="H101" t="n">
         <v>7475</v>
@@ -3327,7 +3327,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G102" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H102" t="n">
         <v>3338</v>
@@ -3356,7 +3356,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G103" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H103" t="n">
         <v>998</v>
@@ -3385,7 +3385,7 @@
         <v>0.865000009536743</v>
       </c>
       <c r="G104" t="n">
-        <v>0.758461773395538</v>
+        <v>0.758461713790894</v>
       </c>
       <c r="H104" t="n">
         <v>48296</v>
@@ -3472,7 +3472,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G107" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H107" t="n">
         <v>27549</v>
@@ -3501,7 +3501,7 @@
         <v>0.876500010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>0.76854532957077</v>
+        <v>0.768545269966125</v>
       </c>
       <c r="H108" t="n">
         <v>1338</v>
@@ -3617,7 +3617,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H112" t="n">
         <v>2675</v>
@@ -3704,7 +3704,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G115" t="n">
-        <v>0.754077553749084</v>
+        <v>0.754077613353729</v>
       </c>
       <c r="H115" t="n">
         <v>10445</v>
@@ -3733,7 +3733,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G116" t="n">
-        <v>0.745309174060822</v>
+        <v>0.745309233665466</v>
       </c>
       <c r="H116" t="n">
         <v>8993</v>
@@ -3820,7 +3820,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G119" t="n">
-        <v>0.748816549777985</v>
+        <v>0.74881649017334</v>
       </c>
       <c r="H119" t="n">
         <v>785</v>
@@ -3878,7 +3878,7 @@
         <v>0.897499978542328</v>
       </c>
       <c r="G121" t="n">
-        <v>0.786958813667297</v>
+        <v>0.786958754062653</v>
       </c>
       <c r="H121" t="n">
         <v>1982</v>
@@ -3936,7 +3936,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G123" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H123" t="n">
         <v>8153</v>
@@ -3965,7 +3965,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G124" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H124" t="n">
         <v>43553</v>
@@ -3994,7 +3994,7 @@
         <v>0.739499986171722</v>
       </c>
       <c r="G125" t="n">
-        <v>0.64841902256012</v>
+        <v>0.648418962955475</v>
       </c>
       <c r="H125" t="n">
         <v>74974</v>
@@ -4081,7 +4081,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G128" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H128" t="n">
         <v>23103</v>
@@ -4139,7 +4139,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G130" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H130" t="n">
         <v>1643</v>
@@ -4197,7 +4197,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G132" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H132" t="n">
         <v>21968</v>
@@ -4284,7 +4284,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G135" t="n">
-        <v>0.687438130378723</v>
+        <v>0.687438189983368</v>
       </c>
       <c r="H135" t="n">
         <v>6650</v>
@@ -4342,7 +4342,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G137" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H137" t="n">
         <v>3668</v>
@@ -4371,7 +4371,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G138" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H138" t="n">
         <v>41982</v>
@@ -4429,7 +4429,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G140" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H140" t="n">
         <v>11600</v>
@@ -4516,7 +4516,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G143" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H143" t="n">
         <v>4620</v>
@@ -4545,7 +4545,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G144" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H144" t="n">
         <v>6350</v>
@@ -4603,7 +4603,7 @@
         <v>0.809000015258789</v>
       </c>
       <c r="G146" t="n">
-        <v>0.709358990192413</v>
+        <v>0.709359049797058</v>
       </c>
       <c r="H146" t="n">
         <v>13493</v>
@@ -4661,7 +4661,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G148" t="n">
-        <v>0.72163462638855</v>
+        <v>0.721634685993195</v>
       </c>
       <c r="H148" t="n">
         <v>16450</v>
@@ -4719,7 +4719,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G150" t="n">
-        <v>0.745309174060822</v>
+        <v>0.745309233665466</v>
       </c>
       <c r="H150" t="n">
         <v>40613</v>
@@ -4777,7 +4777,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G152" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H152" t="n">
         <v>12311</v>
@@ -4864,7 +4864,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G155" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H155" t="n">
         <v>1476</v>
@@ -4893,7 +4893,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G156" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H156" t="n">
         <v>4250</v>
@@ -4922,7 +4922,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G157" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H157" t="n">
         <v>1750</v>
@@ -4951,7 +4951,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G158" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H158" t="n">
         <v>550</v>
@@ -5038,7 +5038,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G161" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H161" t="n">
         <v>550</v>
@@ -5125,7 +5125,7 @@
         <v>0.80349999666214</v>
       </c>
       <c r="G164" t="n">
-        <v>0.704536378383636</v>
+        <v>0.704536437988281</v>
       </c>
       <c r="H164" t="n">
         <v>910</v>
@@ -5241,7 +5241,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G168" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H168" t="n">
         <v>2725</v>
@@ -5270,7 +5270,7 @@
         <v>0.792999982833862</v>
       </c>
       <c r="G169" t="n">
-        <v>0.695329666137695</v>
+        <v>0.695329606533051</v>
       </c>
       <c r="H169" t="n">
         <v>2424</v>
@@ -5328,7 +5328,7 @@
         <v>0.808499991893768</v>
       </c>
       <c r="G171" t="n">
-        <v>0.708920657634735</v>
+        <v>0.70892059803009</v>
       </c>
       <c r="H171" t="n">
         <v>1666</v>
@@ -5357,7 +5357,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G172" t="n">
-        <v>0.699713826179504</v>
+        <v>0.69971376657486</v>
       </c>
       <c r="H172" t="n">
         <v>25236</v>
@@ -5415,7 +5415,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G174" t="n">
-        <v>0.696206510066986</v>
+        <v>0.696206450462341</v>
       </c>
       <c r="H174" t="n">
         <v>7384</v>
@@ -5531,7 +5531,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G178" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H178" t="n">
         <v>40995</v>
@@ -5560,7 +5560,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G179" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H179" t="n">
         <v>7350</v>
@@ -5647,7 +5647,7 @@
         <v>0.779500007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>0.683492302894592</v>
+        <v>0.683492362499237</v>
       </c>
       <c r="H182" t="n">
         <v>2275</v>
@@ -5734,7 +5734,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G185" t="n">
-        <v>0.67340874671936</v>
+        <v>0.673408806324005</v>
       </c>
       <c r="H185" t="n">
         <v>8233</v>
@@ -5821,7 +5821,7 @@
         <v>0.75900000333786</v>
       </c>
       <c r="G188" t="n">
-        <v>0.665517210960388</v>
+        <v>0.665517270565033</v>
       </c>
       <c r="H188" t="n">
         <v>9025</v>
@@ -5937,7 +5937,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G192" t="n">
-        <v>0.670778274536133</v>
+        <v>0.670778214931488</v>
       </c>
       <c r="H192" t="n">
         <v>743</v>
@@ -5966,7 +5966,7 @@
         <v>0.75900000333786</v>
       </c>
       <c r="G193" t="n">
-        <v>0.665517210960388</v>
+        <v>0.665517270565033</v>
       </c>
       <c r="H193" t="n">
         <v>1755</v>
@@ -6053,7 +6053,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G196" t="n">
-        <v>0.633074462413788</v>
+        <v>0.633074402809143</v>
       </c>
       <c r="H196" t="n">
         <v>37830</v>
@@ -6082,7 +6082,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G197" t="n">
-        <v>0.633074462413788</v>
+        <v>0.633074402809143</v>
       </c>
       <c r="H197" t="n">
         <v>5250</v>
@@ -6169,7 +6169,7 @@
         <v>0.739000022411346</v>
       </c>
       <c r="G200" t="n">
-        <v>0.647980630397797</v>
+        <v>0.647980570793152</v>
       </c>
       <c r="H200" t="n">
         <v>4900</v>
@@ -6256,7 +6256,7 @@
         <v>0.709500014781952</v>
       </c>
       <c r="G203" t="n">
-        <v>0.622113943099976</v>
+        <v>0.62211400270462</v>
       </c>
       <c r="H203" t="n">
         <v>8635</v>
@@ -6314,7 +6314,7 @@
         <v>0.704500019550323</v>
       </c>
       <c r="G205" t="n">
-        <v>0.617729783058167</v>
+        <v>0.617729842662811</v>
       </c>
       <c r="H205" t="n">
         <v>26282</v>
@@ -6343,7 +6343,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G206" t="n">
-        <v>0.613784074783325</v>
+        <v>0.61378401517868</v>
       </c>
       <c r="H206" t="n">
         <v>13832</v>
@@ -6372,7 +6372,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G207" t="n">
-        <v>0.613784074783325</v>
+        <v>0.61378401517868</v>
       </c>
       <c r="H207" t="n">
         <v>101543</v>
@@ -6459,7 +6459,7 @@
         <v>0.69650000333786</v>
       </c>
       <c r="G210" t="n">
-        <v>0.61071515083313</v>
+        <v>0.610715091228485</v>
       </c>
       <c r="H210" t="n">
         <v>42761</v>
@@ -6488,7 +6488,7 @@
         <v>0.693000018596649</v>
       </c>
       <c r="G211" t="n">
-        <v>0.607646226882935</v>
+        <v>0.60764616727829</v>
       </c>
       <c r="H211" t="n">
         <v>141366</v>
@@ -6517,7 +6517,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G212" t="n">
-        <v>0.613784074783325</v>
+        <v>0.61378401517868</v>
       </c>
       <c r="H212" t="n">
         <v>46287</v>
@@ -6546,7 +6546,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G213" t="n">
-        <v>0.613784074783325</v>
+        <v>0.61378401517868</v>
       </c>
       <c r="H213" t="n">
         <v>3395</v>
@@ -6575,7 +6575,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>0.607207715511322</v>
+        <v>0.607207775115967</v>
       </c>
       <c r="H214" t="n">
         <v>9856</v>
@@ -6604,7 +6604,7 @@
         <v>0.692499995231628</v>
       </c>
       <c r="G215" t="n">
-        <v>0.607207715511322</v>
+        <v>0.607207775115967</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G217" t="n">
-        <v>0.615537762641907</v>
+        <v>0.615537822246552</v>
       </c>
       <c r="H217" t="n">
         <v>130014</v>
@@ -6720,7 +6720,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G219" t="n">
-        <v>0.613784074783325</v>
+        <v>0.61378401517868</v>
       </c>
       <c r="H219" t="n">
         <v>13547</v>
@@ -6749,7 +6749,7 @@
         <v>0.689499974250793</v>
       </c>
       <c r="G220" t="n">
-        <v>0.604577302932739</v>
+        <v>0.604577243328094</v>
       </c>
       <c r="H220" t="n">
         <v>28791</v>
@@ -6778,7 +6778,7 @@
         <v>0.675000011920929</v>
       </c>
       <c r="G221" t="n">
-        <v>0.59186315536499</v>
+        <v>0.591863214969635</v>
       </c>
       <c r="H221" t="n">
         <v>9848</v>
@@ -6952,7 +6952,7 @@
         <v>0.672999978065491</v>
       </c>
       <c r="G227" t="n">
-        <v>0.590109407901764</v>
+        <v>0.590109467506409</v>
       </c>
       <c r="H227" t="n">
         <v>29937</v>
@@ -6981,7 +6981,7 @@
         <v>0.669000029563904</v>
       </c>
       <c r="G228" t="n">
-        <v>0.58660227060318</v>
+        <v>0.586602210998535</v>
       </c>
       <c r="H228" t="n">
         <v>1455</v>
@@ -7010,7 +7010,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G229" t="n">
-        <v>0.605015635490417</v>
+        <v>0.605015695095062</v>
       </c>
       <c r="H229" t="n">
         <v>139134</v>
@@ -7039,7 +7039,7 @@
         <v>0.697499990463257</v>
       </c>
       <c r="G230" t="n">
-        <v>0.611591935157776</v>
+        <v>0.611591875553131</v>
       </c>
       <c r="H230" t="n">
         <v>26773</v>
@@ -7068,7 +7068,7 @@
         <v>0.700500011444092</v>
       </c>
       <c r="G231" t="n">
-        <v>0.614222407341003</v>
+        <v>0.614222466945648</v>
       </c>
       <c r="H231" t="n">
         <v>2425</v>
@@ -7097,7 +7097,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G232" t="n">
-        <v>0.605015635490417</v>
+        <v>0.605015695095062</v>
       </c>
       <c r="H232" t="n">
         <v>21335</v>
@@ -7126,7 +7126,7 @@
         <v>0.709500014781952</v>
       </c>
       <c r="G233" t="n">
-        <v>0.622113943099976</v>
+        <v>0.62211400270462</v>
       </c>
       <c r="H233" t="n">
         <v>54598</v>
@@ -7213,7 +7213,7 @@
         <v>0.697000026702881</v>
       </c>
       <c r="G236" t="n">
-        <v>0.611153542995453</v>
+        <v>0.611153602600098</v>
       </c>
       <c r="H236" t="n">
         <v>21370</v>
@@ -7329,7 +7329,7 @@
         <v>0.672999978065491</v>
       </c>
       <c r="G240" t="n">
-        <v>0.590109407901764</v>
+        <v>0.590109467506409</v>
       </c>
       <c r="H240" t="n">
         <v>24415</v>
@@ -7358,7 +7358,7 @@
         <v>0.679000020027161</v>
       </c>
       <c r="G241" t="n">
-        <v>0.595370531082153</v>
+        <v>0.595370590686798</v>
       </c>
       <c r="H241" t="n">
         <v>64867</v>
@@ -7503,7 +7503,7 @@
         <v>0.703499972820282</v>
       </c>
       <c r="G246" t="n">
-        <v>0.616852939128876</v>
+        <v>0.616852998733521</v>
       </c>
       <c r="H246" t="n">
         <v>257723</v>
@@ -7532,7 +7532,7 @@
         <v>0.749499976634979</v>
       </c>
       <c r="G247" t="n">
-        <v>0.657187402248383</v>
+        <v>0.657187342643738</v>
       </c>
       <c r="H247" t="n">
         <v>47403</v>
@@ -7590,7 +7590,7 @@
         <v>0.700999975204468</v>
       </c>
       <c r="G249" t="n">
-        <v>0.614660799503326</v>
+        <v>0.614660859107971</v>
       </c>
       <c r="H249" t="n">
         <v>124636</v>
@@ -7677,7 +7677,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G252" t="n">
-        <v>0.615537762641907</v>
+        <v>0.615537822246552</v>
       </c>
       <c r="H252" t="n">
         <v>45959</v>
@@ -7735,7 +7735,7 @@
         <v>0.699500024318695</v>
       </c>
       <c r="G254" t="n">
-        <v>0.613345742225647</v>
+        <v>0.613345682621002</v>
       </c>
       <c r="H254" t="n">
         <v>21545</v>
@@ -7996,7 +7996,7 @@
         <v>0.771499991416931</v>
       </c>
       <c r="G263" t="n">
-        <v>0.676477670669556</v>
+        <v>0.676477611064911</v>
       </c>
       <c r="H263" t="n">
         <v>57247</v>
@@ -8025,7 +8025,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G264" t="n">
-        <v>0.676916182041168</v>
+        <v>0.676916062831879</v>
       </c>
       <c r="H264" t="n">
         <v>45881</v>
@@ -8054,7 +8054,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G265" t="n">
-        <v>0.669901371002197</v>
+        <v>0.669901430606842</v>
       </c>
       <c r="H265" t="n">
         <v>69089</v>
@@ -8112,7 +8112,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G267" t="n">
-        <v>0.690945386886597</v>
+        <v>0.690945446491241</v>
       </c>
       <c r="H267" t="n">
         <v>73207</v>
@@ -8141,7 +8141,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G268" t="n">
-        <v>0.682177126407623</v>
+        <v>0.682177186012268</v>
       </c>
       <c r="H268" t="n">
         <v>16778</v>
@@ -8170,7 +8170,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G269" t="n">
-        <v>0.682177126407623</v>
+        <v>0.682177186012268</v>
       </c>
       <c r="H269" t="n">
         <v>3371</v>
@@ -8315,7 +8315,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G274" t="n">
-        <v>0.699713826179504</v>
+        <v>0.69971376657486</v>
       </c>
       <c r="H274" t="n">
         <v>307037</v>
@@ -8402,7 +8402,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G277" t="n">
-        <v>0.696206510066986</v>
+        <v>0.696206450462341</v>
       </c>
       <c r="H277" t="n">
         <v>6650</v>
@@ -8605,7 +8605,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G284" t="n">
-        <v>0.670778274536133</v>
+        <v>0.670778214931488</v>
       </c>
       <c r="H284" t="n">
         <v>9639</v>
@@ -8663,7 +8663,7 @@
         <v>0.767000019550323</v>
       </c>
       <c r="G286" t="n">
-        <v>0.672532021999359</v>
+        <v>0.672531962394714</v>
       </c>
       <c r="H286" t="n">
         <v>20362</v>
@@ -8779,7 +8779,7 @@
         <v>0.764999985694885</v>
       </c>
       <c r="G290" t="n">
-        <v>0.670778274536133</v>
+        <v>0.670778214931488</v>
       </c>
       <c r="H290" t="n">
         <v>24850</v>
@@ -8837,7 +8837,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G292" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H292" t="n">
         <v>79494</v>
@@ -8924,7 +8924,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G295" t="n">
-        <v>0.713743150234222</v>
+        <v>0.713743209838867</v>
       </c>
       <c r="H295" t="n">
         <v>20790</v>
@@ -8982,7 +8982,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G297" t="n">
-        <v>0.714619994163513</v>
+        <v>0.714619934558868</v>
       </c>
       <c r="H297" t="n">
         <v>56669</v>
@@ -9011,7 +9011,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G298" t="n">
-        <v>0.714619994163513</v>
+        <v>0.714619934558868</v>
       </c>
       <c r="H298" t="n">
         <v>173530</v>
@@ -9069,7 +9069,7 @@
         <v>0.817499995231628</v>
       </c>
       <c r="G300" t="n">
-        <v>0.716812074184418</v>
+        <v>0.716812014579773</v>
       </c>
       <c r="H300" t="n">
         <v>75157</v>
@@ -9098,7 +9098,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G301" t="n">
-        <v>0.713743150234222</v>
+        <v>0.713743209838867</v>
       </c>
       <c r="H301" t="n">
         <v>53335</v>
@@ -9156,7 +9156,7 @@
         <v>0.829500019550323</v>
       </c>
       <c r="G303" t="n">
-        <v>0.727334082126617</v>
+        <v>0.727334141731262</v>
       </c>
       <c r="H303" t="n">
         <v>119194</v>
@@ -9214,7 +9214,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G305" t="n">
-        <v>0.714619994163513</v>
+        <v>0.714619934558868</v>
       </c>
       <c r="H305" t="n">
         <v>22473</v>
@@ -9243,7 +9243,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G306" t="n">
-        <v>0.745309174060822</v>
+        <v>0.745309233665466</v>
       </c>
       <c r="H306" t="n">
         <v>256201</v>
@@ -9272,7 +9272,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G307" t="n">
-        <v>0.745309174060822</v>
+        <v>0.745309233665466</v>
       </c>
       <c r="H307" t="n">
         <v>17161</v>
@@ -9330,7 +9330,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G309" t="n">
-        <v>0.726018846035004</v>
+        <v>0.726018905639648</v>
       </c>
       <c r="H309" t="n">
         <v>8917</v>
@@ -9359,7 +9359,7 @@
         <v>0.82150000333786</v>
       </c>
       <c r="G310" t="n">
-        <v>0.720319449901581</v>
+        <v>0.720319390296936</v>
       </c>
       <c r="H310" t="n">
         <v>47114</v>
@@ -9446,7 +9446,7 @@
         <v>0.810999989509583</v>
       </c>
       <c r="G313" t="n">
-        <v>0.711112678050995</v>
+        <v>0.71111273765564</v>
       </c>
       <c r="H313" t="n">
         <v>8419</v>
@@ -9475,7 +9475,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G314" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H314" t="n">
         <v>204381</v>
@@ -9533,7 +9533,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G316" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H316" t="n">
         <v>28170</v>
@@ -9562,7 +9562,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G317" t="n">
-        <v>0.717250466346741</v>
+        <v>0.717250525951385</v>
       </c>
       <c r="H317" t="n">
         <v>100281</v>
@@ -9591,7 +9591,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G318" t="n">
-        <v>0.72163462638855</v>
+        <v>0.721634685993195</v>
       </c>
       <c r="H318" t="n">
         <v>17358</v>
@@ -9620,7 +9620,7 @@
         <v>0.829500019550323</v>
       </c>
       <c r="G319" t="n">
-        <v>0.727334082126617</v>
+        <v>0.727334141731262</v>
       </c>
       <c r="H319" t="n">
         <v>39385</v>
@@ -9649,7 +9649,7 @@
         <v>0.829500019550323</v>
       </c>
       <c r="G320" t="n">
-        <v>0.727334082126617</v>
+        <v>0.727334141731262</v>
       </c>
       <c r="H320" t="n">
         <v>6363</v>
@@ -9678,7 +9678,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G321" t="n">
-        <v>0.731279850006104</v>
+        <v>0.731279909610748</v>
       </c>
       <c r="H321" t="n">
         <v>8308</v>
@@ -9707,7 +9707,7 @@
         <v>0.833000004291534</v>
       </c>
       <c r="G322" t="n">
-        <v>0.730402946472168</v>
+        <v>0.730403006076813</v>
       </c>
       <c r="H322" t="n">
         <v>17249</v>
@@ -9765,7 +9765,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G324" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H324" t="n">
         <v>58494</v>
@@ -9823,7 +9823,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G326" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H326" t="n">
         <v>53179</v>
@@ -9852,7 +9852,7 @@
         <v>0.823000013828278</v>
       </c>
       <c r="G327" t="n">
-        <v>0.72163462638855</v>
+        <v>0.721634685993195</v>
       </c>
       <c r="H327" t="n">
         <v>5604</v>
@@ -9939,7 +9939,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G330" t="n">
-        <v>0.715496778488159</v>
+        <v>0.715496838092804</v>
       </c>
       <c r="H330" t="n">
         <v>11350</v>
@@ -10055,7 +10055,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G334" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H334" t="n">
         <v>2300</v>
@@ -10171,7 +10171,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G338" t="n">
-        <v>0.714619994163513</v>
+        <v>0.714619934558868</v>
       </c>
       <c r="H338" t="n">
         <v>24555</v>
@@ -10200,7 +10200,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G339" t="n">
-        <v>0.714619994163513</v>
+        <v>0.714619934558868</v>
       </c>
       <c r="H339" t="n">
         <v>32316</v>
@@ -10229,7 +10229,7 @@
         <v>0.813000023365021</v>
       </c>
       <c r="G340" t="n">
-        <v>0.712866365909576</v>
+        <v>0.712866306304932</v>
       </c>
       <c r="H340" t="n">
         <v>93552</v>
@@ -10258,7 +10258,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G341" t="n">
-        <v>0.714619994163513</v>
+        <v>0.714619934558868</v>
       </c>
       <c r="H341" t="n">
         <v>64043</v>
@@ -10316,7 +10316,7 @@
         <v>0.810999989509583</v>
       </c>
       <c r="G343" t="n">
-        <v>0.711112678050995</v>
+        <v>0.71111273765564</v>
       </c>
       <c r="H343" t="n">
         <v>17325</v>
@@ -10345,7 +10345,7 @@
         <v>0.816999971866608</v>
       </c>
       <c r="G344" t="n">
-        <v>0.71637374162674</v>
+        <v>0.716373682022095</v>
       </c>
       <c r="H344" t="n">
         <v>21541</v>
@@ -10374,7 +10374,7 @@
         <v>0.8125</v>
       </c>
       <c r="G345" t="n">
-        <v>0.712427914142609</v>
+        <v>0.712427854537964</v>
       </c>
       <c r="H345" t="n">
         <v>41063</v>
@@ -10432,7 +10432,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G347" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H347" t="n">
         <v>59031</v>
@@ -10461,7 +10461,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G348" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H348" t="n">
         <v>11115</v>
@@ -10490,7 +10490,7 @@
         <v>0.813000023365021</v>
       </c>
       <c r="G349" t="n">
-        <v>0.712866365909576</v>
+        <v>0.712866306304932</v>
       </c>
       <c r="H349" t="n">
         <v>79133</v>
@@ -10548,7 +10548,7 @@
         <v>0.8125</v>
       </c>
       <c r="G351" t="n">
-        <v>0.712427914142609</v>
+        <v>0.712427854537964</v>
       </c>
       <c r="H351" t="n">
         <v>23641</v>
@@ -10606,7 +10606,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G353" t="n">
-        <v>0.717250466346741</v>
+        <v>0.717250525951385</v>
       </c>
       <c r="H353" t="n">
         <v>27307</v>
@@ -10635,7 +10635,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G354" t="n">
-        <v>0.713743150234222</v>
+        <v>0.713743209838867</v>
       </c>
       <c r="H354" t="n">
         <v>32345</v>
@@ -10664,7 +10664,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G355" t="n">
-        <v>0.714619994163513</v>
+        <v>0.714619934558868</v>
       </c>
       <c r="H355" t="n">
         <v>31784</v>
@@ -10693,7 +10693,7 @@
         <v>0.810999989509583</v>
       </c>
       <c r="G356" t="n">
-        <v>0.711112678050995</v>
+        <v>0.71111273765564</v>
       </c>
       <c r="H356" t="n">
         <v>16337</v>
@@ -10809,7 +10809,7 @@
         <v>0.823499977588654</v>
       </c>
       <c r="G360" t="n">
-        <v>0.722073078155518</v>
+        <v>0.722073018550873</v>
       </c>
       <c r="H360" t="n">
         <v>5474</v>
@@ -10838,7 +10838,7 @@
         <v>0.827499985694885</v>
       </c>
       <c r="G361" t="n">
-        <v>0.725580394268036</v>
+        <v>0.725580453872681</v>
       </c>
       <c r="H361" t="n">
         <v>13413</v>
@@ -10867,7 +10867,7 @@
         <v>0.82150000333786</v>
       </c>
       <c r="G362" t="n">
-        <v>0.720319449901581</v>
+        <v>0.720319390296936</v>
       </c>
       <c r="H362" t="n">
         <v>15100</v>
@@ -10925,7 +10925,7 @@
         <v>0.814999997615814</v>
       </c>
       <c r="G364" t="n">
-        <v>0.714619994163513</v>
+        <v>0.714619934558868</v>
       </c>
       <c r="H364" t="n">
         <v>300</v>
@@ -10954,7 +10954,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G365" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H365" t="n">
         <v>22527</v>
@@ -10983,7 +10983,7 @@
         <v>0.826499998569489</v>
       </c>
       <c r="G366" t="n">
-        <v>0.72470360994339</v>
+        <v>0.724703550338745</v>
       </c>
       <c r="H366" t="n">
         <v>7911</v>
@@ -11186,7 +11186,7 @@
         <v>1.05099999904633</v>
       </c>
       <c r="G373" t="n">
-        <v>0.921552956104279</v>
+        <v>0.921552896499634</v>
       </c>
       <c r="H373" t="n">
         <v>728694</v>
@@ -11302,7 +11302,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G377" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H377" t="n">
         <v>377714</v>
@@ -11331,7 +11331,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G378" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H378" t="n">
         <v>217206</v>
@@ -11505,7 +11505,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G384" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H384" t="n">
         <v>205434</v>
@@ -11563,7 +11563,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G386" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H386" t="n">
         <v>498552</v>
@@ -11592,7 +11592,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G387" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H387" t="n">
         <v>206784</v>
@@ -11621,7 +11621,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G388" t="n">
-        <v>1.05307793617249</v>
+        <v>1.05307817459106</v>
       </c>
       <c r="H388" t="n">
         <v>176162</v>
@@ -11679,7 +11679,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G390" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H390" t="n">
         <v>32853</v>
@@ -11708,7 +11708,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G391" t="n">
-        <v>1.055708527565</v>
+        <v>1.05570864677429</v>
       </c>
       <c r="H391" t="n">
         <v>105693</v>
@@ -11737,7 +11737,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H392" t="n">
         <v>67105</v>
@@ -11766,7 +11766,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G393" t="n">
-        <v>1.04781711101532</v>
+        <v>1.04781699180603</v>
       </c>
       <c r="H393" t="n">
         <v>93924</v>
@@ -11824,7 +11824,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G395" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H395" t="n">
         <v>65260</v>
@@ -11853,7 +11853,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G396" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H396" t="n">
         <v>51370</v>
@@ -11882,7 +11882,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G397" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H397" t="n">
         <v>42446</v>
@@ -11911,7 +11911,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G398" t="n">
-        <v>1.055708527565</v>
+        <v>1.05570864677429</v>
       </c>
       <c r="H398" t="n">
         <v>44879</v>
@@ -11969,7 +11969,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G400" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H400" t="n">
         <v>490686</v>
@@ -11998,7 +11998,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H401" t="n">
         <v>263123</v>
@@ -12027,7 +12027,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H402" t="n">
         <v>146261</v>
@@ -12056,7 +12056,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H403" t="n">
         <v>106009</v>
@@ -12085,7 +12085,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G404" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H404" t="n">
         <v>166550</v>
@@ -12114,7 +12114,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G405" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H405" t="n">
         <v>46551</v>
@@ -12143,7 +12143,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G406" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H406" t="n">
         <v>102218</v>
@@ -12201,7 +12201,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G408" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H408" t="n">
         <v>188200</v>
@@ -12259,7 +12259,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H410" t="n">
         <v>68286</v>
@@ -12288,7 +12288,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G411" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H411" t="n">
         <v>73435</v>
@@ -12317,7 +12317,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G412" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H412" t="n">
         <v>36256</v>
@@ -12375,7 +12375,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G414" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H414" t="n">
         <v>81706</v>
@@ -12404,7 +12404,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G415" t="n">
-        <v>1.05307793617249</v>
+        <v>1.05307817459106</v>
       </c>
       <c r="H415" t="n">
         <v>9979</v>
@@ -12433,7 +12433,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G416" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H416" t="n">
         <v>67937</v>
@@ -12462,7 +12462,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G417" t="n">
-        <v>1.05395483970642</v>
+        <v>1.05395495891571</v>
       </c>
       <c r="H417" t="n">
         <v>60625</v>
@@ -12491,7 +12491,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G418" t="n">
-        <v>1.05395483970642</v>
+        <v>1.05395495891571</v>
       </c>
       <c r="H418" t="n">
         <v>48376</v>
@@ -12520,7 +12520,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G419" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H419" t="n">
         <v>153517</v>
@@ -12549,7 +12549,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G420" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H420" t="n">
         <v>122295</v>
@@ -12607,7 +12607,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G422" t="n">
-        <v>1.055708527565</v>
+        <v>1.05570864677429</v>
       </c>
       <c r="H422" t="n">
         <v>963332</v>
@@ -12636,7 +12636,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G423" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H423" t="n">
         <v>45637</v>
@@ -12665,7 +12665,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G424" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H424" t="n">
         <v>31212</v>
@@ -12694,7 +12694,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G425" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H425" t="n">
         <v>880481</v>
@@ -12723,7 +12723,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G426" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H426" t="n">
         <v>2835819</v>
@@ -12752,7 +12752,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G427" t="n">
-        <v>1.055708527565</v>
+        <v>1.05570864677429</v>
       </c>
       <c r="H427" t="n">
         <v>73306</v>
@@ -12781,7 +12781,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G428" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H428" t="n">
         <v>863371</v>
@@ -12810,7 +12810,7 @@
         <v>1.5</v>
       </c>
       <c r="G429" t="n">
-        <v>1.31525158882141</v>
+        <v>1.31525146961212</v>
       </c>
       <c r="H429" t="n">
         <v>2326885</v>
@@ -12868,7 +12868,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G431" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H431" t="n">
         <v>368325</v>
@@ -12926,7 +12926,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H433" t="n">
         <v>410171</v>
@@ -12955,7 +12955,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G434" t="n">
-        <v>1.17671179771423</v>
+        <v>1.17671167850494</v>
       </c>
       <c r="H434" t="n">
         <v>132175</v>
@@ -13042,7 +13042,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G437" t="n">
-        <v>1.11621010303497</v>
+        <v>1.11620998382568</v>
       </c>
       <c r="H437" t="n">
         <v>82599</v>
@@ -13071,7 +13071,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G438" t="n">
-        <v>1.09691989421844</v>
+        <v>1.09691977500916</v>
       </c>
       <c r="H438" t="n">
         <v>107701</v>
@@ -13100,7 +13100,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G439" t="n">
-        <v>1.1276091337204</v>
+        <v>1.12760901451111</v>
       </c>
       <c r="H439" t="n">
         <v>136868</v>
@@ -13158,7 +13158,7 @@
         <v>1.26699995994568</v>
       </c>
       <c r="G441" t="n">
-        <v>1.11094903945923</v>
+        <v>1.11094915866852</v>
       </c>
       <c r="H441" t="n">
         <v>50270</v>
@@ -13187,7 +13187,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G442" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H442" t="n">
         <v>37216</v>
@@ -13245,7 +13245,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G444" t="n">
-        <v>1.14163827896118</v>
+        <v>1.14163839817047</v>
       </c>
       <c r="H444" t="n">
         <v>19878</v>
@@ -13303,7 +13303,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G446" t="n">
-        <v>1.14952969551086</v>
+        <v>1.14952993392944</v>
       </c>
       <c r="H446" t="n">
         <v>122663</v>
@@ -13361,7 +13361,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G448" t="n">
-        <v>1.14076137542725</v>
+        <v>1.14076149463654</v>
       </c>
       <c r="H448" t="n">
         <v>15048</v>
@@ -13390,7 +13390,7 @@
         <v>1.31700003147125</v>
       </c>
       <c r="G449" t="n">
-        <v>1.15479099750519</v>
+        <v>1.1547908782959</v>
       </c>
       <c r="H449" t="n">
         <v>12077</v>
@@ -13651,7 +13651,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G458" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H458" t="n">
         <v>19932</v>
@@ -13680,7 +13680,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G459" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H459" t="n">
         <v>21834</v>
@@ -13796,7 +13796,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G463" t="n">
-        <v>1.18372631072998</v>
+        <v>1.18372642993927</v>
       </c>
       <c r="H463" t="n">
         <v>3371</v>
@@ -13883,7 +13883,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G466" t="n">
-        <v>1.18372631072998</v>
+        <v>1.18372642993927</v>
       </c>
       <c r="H466" t="n">
         <v>10414</v>
@@ -13912,7 +13912,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G467" t="n">
-        <v>1.20038628578186</v>
+        <v>1.20038616657257</v>
       </c>
       <c r="H467" t="n">
         <v>43103</v>
@@ -13941,7 +13941,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G468" t="n">
-        <v>1.21441543102264</v>
+        <v>1.21441555023193</v>
       </c>
       <c r="H468" t="n">
         <v>135322</v>
@@ -13970,7 +13970,7 @@
         <v>1.37899994850159</v>
       </c>
       <c r="G469" t="n">
-        <v>1.20915460586548</v>
+        <v>1.20915448665619</v>
       </c>
       <c r="H469" t="n">
         <v>5403</v>
@@ -14086,7 +14086,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G473" t="n">
-        <v>1.213538646698</v>
+        <v>1.21353876590729</v>
       </c>
       <c r="H473" t="n">
         <v>31961</v>
@@ -14115,7 +14115,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G474" t="n">
-        <v>1.21003127098083</v>
+        <v>1.21003139019012</v>
       </c>
       <c r="H474" t="n">
         <v>13451</v>
@@ -14202,7 +14202,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G477" t="n">
-        <v>1.20038628578186</v>
+        <v>1.20038616657257</v>
       </c>
       <c r="H477" t="n">
         <v>34087</v>
@@ -14260,7 +14260,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G479" t="n">
-        <v>1.19074106216431</v>
+        <v>1.1907411813736</v>
       </c>
       <c r="H479" t="n">
         <v>26933</v>
@@ -14289,7 +14289,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G480" t="n">
-        <v>1.17934226989746</v>
+        <v>1.17934215068817</v>
       </c>
       <c r="H480" t="n">
         <v>30831</v>
@@ -14376,7 +14376,7 @@
         <v>1.31700003147125</v>
       </c>
       <c r="G483" t="n">
-        <v>1.15479099750519</v>
+        <v>1.1547908782959</v>
       </c>
       <c r="H483" t="n">
         <v>8395</v>
@@ -14434,7 +14434,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G485" t="n">
-        <v>1.14076137542725</v>
+        <v>1.14076149463654</v>
       </c>
       <c r="H485" t="n">
         <v>41876</v>
@@ -14463,7 +14463,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G486" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H486" t="n">
         <v>30808</v>
@@ -14492,7 +14492,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G487" t="n">
-        <v>1.14952969551086</v>
+        <v>1.14952993392944</v>
       </c>
       <c r="H487" t="n">
         <v>3984</v>
@@ -14579,7 +14579,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G490" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H490" t="n">
         <v>20191</v>
@@ -14608,7 +14608,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G491" t="n">
-        <v>1.18109583854675</v>
+        <v>1.18109571933746</v>
       </c>
       <c r="H491" t="n">
         <v>1837</v>
@@ -14637,7 +14637,7 @@
         <v>1.375</v>
       </c>
       <c r="G492" t="n">
-        <v>1.20564711093903</v>
+        <v>1.20564723014832</v>
       </c>
       <c r="H492" t="n">
         <v>75630</v>
@@ -14724,7 +14724,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G495" t="n">
-        <v>1.18547999858856</v>
+        <v>1.18548011779785</v>
       </c>
       <c r="H495" t="n">
         <v>17500</v>
@@ -14753,7 +14753,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G496" t="n">
-        <v>1.18372631072998</v>
+        <v>1.18372642993927</v>
       </c>
       <c r="H496" t="n">
         <v>8901</v>
@@ -14782,7 +14782,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G497" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H497" t="n">
         <v>18239</v>
@@ -14811,7 +14811,7 @@
         <v>1.32400000095367</v>
       </c>
       <c r="G498" t="n">
-        <v>1.160928606987</v>
+        <v>1.16092848777771</v>
       </c>
       <c r="H498" t="n">
         <v>15874</v>
@@ -14840,7 +14840,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G499" t="n">
-        <v>1.18109583854675</v>
+        <v>1.18109571933746</v>
       </c>
       <c r="H499" t="n">
         <v>2106</v>
@@ -14927,7 +14927,7 @@
         <v>1.32400000095367</v>
       </c>
       <c r="G502" t="n">
-        <v>1.160928606987</v>
+        <v>1.16092848777771</v>
       </c>
       <c r="H502" t="n">
         <v>16848</v>
@@ -14956,7 +14956,7 @@
         <v>1.30200004577637</v>
       </c>
       <c r="G503" t="n">
-        <v>1.14163827896118</v>
+        <v>1.14163839817047</v>
       </c>
       <c r="H503" t="n">
         <v>26388</v>
@@ -15072,7 +15072,7 @@
         <v>1.28299999237061</v>
       </c>
       <c r="G507" t="n">
-        <v>1.12497842311859</v>
+        <v>1.1249783039093</v>
       </c>
       <c r="H507" t="n">
         <v>93337</v>
@@ -15101,7 +15101,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G508" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H508" t="n">
         <v>33224</v>
@@ -15217,7 +15217,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G512" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H512" t="n">
         <v>4100</v>
@@ -15275,7 +15275,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G514" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H514" t="n">
         <v>21747</v>
@@ -15304,7 +15304,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G515" t="n">
-        <v>1.13550043106079</v>
+        <v>1.1355003118515</v>
       </c>
       <c r="H515" t="n">
         <v>43247</v>
@@ -15333,7 +15333,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H516" t="n">
         <v>6400</v>
@@ -15449,7 +15449,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G520" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H520" t="n">
         <v>12164</v>
@@ -15507,7 +15507,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G522" t="n">
-        <v>1.17934226989746</v>
+        <v>1.17934215068817</v>
       </c>
       <c r="H522" t="n">
         <v>55246</v>
@@ -15652,7 +15652,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G527" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H527" t="n">
         <v>13255</v>
@@ -15710,7 +15710,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G529" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H529" t="n">
         <v>9513</v>
@@ -15797,7 +15797,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G532" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H532" t="n">
         <v>7057</v>
@@ -15855,7 +15855,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G534" t="n">
-        <v>1.21441543102264</v>
+        <v>1.21441555023193</v>
       </c>
       <c r="H534" t="n">
         <v>2766</v>
@@ -15913,7 +15913,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G536" t="n">
-        <v>1.21441543102264</v>
+        <v>1.21441555023193</v>
       </c>
       <c r="H536" t="n">
         <v>10463</v>
@@ -15971,7 +15971,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G538" t="n">
-        <v>1.21003127098083</v>
+        <v>1.21003139019012</v>
       </c>
       <c r="H538" t="n">
         <v>4966</v>
@@ -16029,7 +16029,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G540" t="n">
-        <v>1.22756814956665</v>
+        <v>1.22756803035736</v>
       </c>
       <c r="H540" t="n">
         <v>15423</v>
@@ -16058,7 +16058,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>1.22318387031555</v>
+        <v>1.22318375110626</v>
       </c>
       <c r="H541" t="n">
         <v>3500</v>
@@ -16203,7 +16203,7 @@
         <v>1.375</v>
       </c>
       <c r="G546" t="n">
-        <v>1.20564711093903</v>
+        <v>1.20564723014832</v>
       </c>
       <c r="H546" t="n">
         <v>10659</v>
@@ -16319,7 +16319,7 @@
         <v>1.375</v>
       </c>
       <c r="G550" t="n">
-        <v>1.20564711093903</v>
+        <v>1.20564723014832</v>
       </c>
       <c r="H550" t="n">
         <v>5600</v>
@@ -16348,7 +16348,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G551" t="n">
-        <v>1.17934226989746</v>
+        <v>1.17934215068817</v>
       </c>
       <c r="H551" t="n">
         <v>26766</v>
@@ -16406,7 +16406,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G553" t="n">
-        <v>1.18372631072998</v>
+        <v>1.18372642993927</v>
       </c>
       <c r="H553" t="n">
         <v>6016</v>
@@ -16435,7 +16435,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G554" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H554" t="n">
         <v>20375</v>
@@ -16522,7 +16522,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G557" t="n">
-        <v>1.18372631072998</v>
+        <v>1.18372642993927</v>
       </c>
       <c r="H557" t="n">
         <v>3364</v>
@@ -16551,7 +16551,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G558" t="n">
-        <v>1.17934226989746</v>
+        <v>1.17934215068817</v>
       </c>
       <c r="H558" t="n">
         <v>8168</v>
@@ -16696,7 +16696,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G563" t="n">
-        <v>1.18372631072998</v>
+        <v>1.18372642993927</v>
       </c>
       <c r="H563" t="n">
         <v>1675</v>
@@ -16725,7 +16725,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>1.17934226989746</v>
+        <v>1.17934215068817</v>
       </c>
       <c r="H564" t="n">
         <v>16280</v>
@@ -16754,7 +16754,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G565" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H565" t="n">
         <v>16993</v>
@@ -16812,7 +16812,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G567" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H567" t="n">
         <v>118613</v>
@@ -16899,7 +16899,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G570" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H570" t="n">
         <v>91328</v>
@@ -16928,7 +16928,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G571" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H571" t="n">
         <v>90400</v>
@@ -16957,7 +16957,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G572" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H572" t="n">
         <v>93929</v>
@@ -17044,7 +17044,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G575" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H575" t="n">
         <v>7623</v>
@@ -17073,7 +17073,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G576" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H576" t="n">
         <v>1950</v>
@@ -17160,7 +17160,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G579" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H579" t="n">
         <v>29587</v>
@@ -17392,7 +17392,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H587" t="n">
         <v>3995</v>
@@ -17421,7 +17421,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G588" t="n">
-        <v>1.13550043106079</v>
+        <v>1.1355003118515</v>
       </c>
       <c r="H588" t="n">
         <v>5105</v>
@@ -17450,7 +17450,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G589" t="n">
-        <v>1.13550043106079</v>
+        <v>1.1355003118515</v>
       </c>
       <c r="H589" t="n">
         <v>1200</v>
@@ -17508,7 +17508,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G591" t="n">
-        <v>1.13550043106079</v>
+        <v>1.1355003118515</v>
       </c>
       <c r="H591" t="n">
         <v>4200</v>
@@ -17537,7 +17537,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H592" t="n">
         <v>12470</v>
@@ -17566,7 +17566,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G593" t="n">
-        <v>1.13550043106079</v>
+        <v>1.1355003118515</v>
       </c>
       <c r="H593" t="n">
         <v>8843</v>
@@ -17595,7 +17595,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G594" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H594" t="n">
         <v>2043</v>
@@ -17624,7 +17624,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H595" t="n">
         <v>4150</v>
@@ -17653,7 +17653,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G596" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H596" t="n">
         <v>5408</v>
@@ -17682,7 +17682,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G597" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H597" t="n">
         <v>173192</v>
@@ -17798,7 +17798,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G601" t="n">
-        <v>1.15742135047913</v>
+        <v>1.15742146968842</v>
       </c>
       <c r="H601" t="n">
         <v>8044</v>
@@ -17885,7 +17885,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G604" t="n">
-        <v>1.13550043106079</v>
+        <v>1.1355003118515</v>
       </c>
       <c r="H604" t="n">
         <v>6160</v>
@@ -17914,7 +17914,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G605" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H605" t="n">
         <v>20794</v>
@@ -17943,7 +17943,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G606" t="n">
-        <v>1.11796379089355</v>
+        <v>1.11796391010284</v>
       </c>
       <c r="H606" t="n">
         <v>93153</v>
@@ -17972,7 +17972,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G607" t="n">
-        <v>1.11796379089355</v>
+        <v>1.11796391010284</v>
       </c>
       <c r="H607" t="n">
         <v>111466</v>
@@ -18001,7 +18001,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G608" t="n">
-        <v>1.11796379089355</v>
+        <v>1.11796391010284</v>
       </c>
       <c r="H608" t="n">
         <v>12348</v>
@@ -18059,7 +18059,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G610" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H610" t="n">
         <v>1934</v>
@@ -18175,7 +18175,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G614" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H614" t="n">
         <v>63710</v>
@@ -18204,7 +18204,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G615" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H615" t="n">
         <v>18202</v>
@@ -18233,7 +18233,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H616" t="n">
         <v>12900</v>
@@ -18262,7 +18262,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G617" t="n">
-        <v>1.13988471031189</v>
+        <v>1.1398845911026</v>
       </c>
       <c r="H617" t="n">
         <v>25518</v>
@@ -18320,7 +18320,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G619" t="n">
-        <v>1.11796379089355</v>
+        <v>1.11796391010284</v>
       </c>
       <c r="H619" t="n">
         <v>19111</v>
@@ -18378,7 +18378,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H621" t="n">
         <v>20331</v>
@@ -18407,7 +18407,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G622" t="n">
-        <v>1.13550043106079</v>
+        <v>1.1355003118515</v>
       </c>
       <c r="H622" t="n">
         <v>25445</v>
@@ -18436,7 +18436,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G623" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H623" t="n">
         <v>11748</v>
@@ -18465,7 +18465,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H624" t="n">
         <v>13185</v>
@@ -18494,7 +18494,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G625" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H625" t="n">
         <v>4200</v>
@@ -18523,7 +18523,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G626" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H626" t="n">
         <v>10050</v>
@@ -18552,7 +18552,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H627" t="n">
         <v>4150</v>
@@ -18581,7 +18581,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G628" t="n">
-        <v>1.13550043106079</v>
+        <v>1.1355003118515</v>
       </c>
       <c r="H628" t="n">
         <v>4400</v>
@@ -18610,7 +18610,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G629" t="n">
-        <v>1.13550043106079</v>
+        <v>1.1355003118515</v>
       </c>
       <c r="H629" t="n">
         <v>5096</v>
@@ -18639,7 +18639,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G630" t="n">
-        <v>1.13550043106079</v>
+        <v>1.1355003118515</v>
       </c>
       <c r="H630" t="n">
         <v>5089</v>
@@ -18755,7 +18755,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G634" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H634" t="n">
         <v>4402</v>
@@ -18784,7 +18784,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G635" t="n">
-        <v>1.13550043106079</v>
+        <v>1.1355003118515</v>
       </c>
       <c r="H635" t="n">
         <v>10278</v>
@@ -18842,7 +18842,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G637" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H637" t="n">
         <v>11115</v>
@@ -18900,7 +18900,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G639" t="n">
-        <v>1.11796379089355</v>
+        <v>1.11796391010284</v>
       </c>
       <c r="H639" t="n">
         <v>9440</v>
@@ -18987,7 +18987,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G642" t="n">
-        <v>1.11796379089355</v>
+        <v>1.11796391010284</v>
       </c>
       <c r="H642" t="n">
         <v>4208</v>
@@ -19045,7 +19045,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G644" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H644" t="n">
         <v>6679</v>
@@ -19074,7 +19074,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G645" t="n">
-        <v>1.13550043106079</v>
+        <v>1.1355003118515</v>
       </c>
       <c r="H645" t="n">
         <v>23427</v>
@@ -19103,7 +19103,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G646" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H646" t="n">
         <v>4700</v>
@@ -19132,7 +19132,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G647" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H647" t="n">
         <v>1700</v>
@@ -19451,7 +19451,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H658" t="n">
         <v>19437</v>
@@ -19770,7 +19770,7 @@
         <v>1.25</v>
       </c>
       <c r="G669" t="n">
-        <v>1.09604287147522</v>
+        <v>1.09604299068451</v>
       </c>
       <c r="H669" t="n">
         <v>750</v>
@@ -19828,7 +19828,7 @@
         <v>1.25</v>
       </c>
       <c r="G671" t="n">
-        <v>1.09604287147522</v>
+        <v>1.09604299068451</v>
       </c>
       <c r="H671" t="n">
         <v>530</v>
@@ -19915,7 +19915,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G674" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H674" t="n">
         <v>12565</v>
@@ -19944,7 +19944,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G675" t="n">
-        <v>1.06973791122437</v>
+        <v>1.06973803043365</v>
       </c>
       <c r="H675" t="n">
         <v>2430</v>
@@ -19973,7 +19973,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G676" t="n">
-        <v>1.06973791122437</v>
+        <v>1.06973803043365</v>
       </c>
       <c r="H676" t="n">
         <v>1107</v>
@@ -20002,7 +20002,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G677" t="n">
-        <v>1.06973791122437</v>
+        <v>1.06973803043365</v>
       </c>
       <c r="H677" t="n">
         <v>271</v>
@@ -20031,7 +20031,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G678" t="n">
-        <v>1.04343295097351</v>
+        <v>1.04343283176422</v>
       </c>
       <c r="H678" t="n">
         <v>1415</v>
@@ -20060,7 +20060,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G679" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H679" t="n">
         <v>6305</v>
@@ -20089,7 +20089,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G680" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H680" t="n">
         <v>4175</v>
@@ -20176,7 +20176,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>1.06973791122437</v>
+        <v>1.06973803043365</v>
       </c>
       <c r="H683" t="n">
         <v>2400</v>
@@ -20263,7 +20263,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G686" t="n">
-        <v>1.06973791122437</v>
+        <v>1.06973803043365</v>
       </c>
       <c r="H686" t="n">
         <v>7381</v>
@@ -20379,7 +20379,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G690" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H690" t="n">
         <v>2152</v>
@@ -20408,7 +20408,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G691" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H691" t="n">
         <v>401</v>
@@ -20437,7 +20437,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H692" t="n">
         <v>16598</v>
@@ -20466,7 +20466,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G693" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H693" t="n">
         <v>7050</v>
@@ -20495,7 +20495,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G694" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H694" t="n">
         <v>13331</v>
@@ -20611,7 +20611,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G698" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H698" t="n">
         <v>16430</v>
@@ -20669,7 +20669,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G700" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H700" t="n">
         <v>5350</v>
@@ -20698,7 +20698,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>1.13111627101898</v>
+        <v>1.13111615180969</v>
       </c>
       <c r="H701" t="n">
         <v>11038</v>
@@ -20756,7 +20756,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H703" t="n">
         <v>7800</v>
@@ -20785,7 +20785,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H704" t="n">
         <v>7603</v>
@@ -20814,7 +20814,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G705" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H705" t="n">
         <v>3530</v>
@@ -20843,7 +20843,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G706" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H706" t="n">
         <v>8450</v>
@@ -20901,7 +20901,7 @@
         <v>1.25</v>
       </c>
       <c r="G708" t="n">
-        <v>1.09604287147522</v>
+        <v>1.09604299068451</v>
       </c>
       <c r="H708" t="n">
         <v>6801</v>
@@ -21046,7 +21046,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G713" t="n">
-        <v>1.11357963085175</v>
+        <v>1.11357975006104</v>
       </c>
       <c r="H713" t="n">
         <v>5650</v>
@@ -21191,7 +21191,7 @@
         <v>1.25</v>
       </c>
       <c r="G718" t="n">
-        <v>1.09604287147522</v>
+        <v>1.09604299068451</v>
       </c>
       <c r="H718" t="n">
         <v>4572</v>
@@ -21220,7 +21220,7 @@
         <v>1.25</v>
       </c>
       <c r="G719" t="n">
-        <v>1.09604287147522</v>
+        <v>1.09604299068451</v>
       </c>
       <c r="H719" t="n">
         <v>2300</v>
@@ -21278,7 +21278,7 @@
         <v>1.25</v>
       </c>
       <c r="G721" t="n">
-        <v>1.09604287147522</v>
+        <v>1.09604299068451</v>
       </c>
       <c r="H721" t="n">
         <v>1000</v>
@@ -21307,7 +21307,7 @@
         <v>1.25</v>
       </c>
       <c r="G722" t="n">
-        <v>1.09604287147522</v>
+        <v>1.09604299068451</v>
       </c>
       <c r="H722" t="n">
         <v>350</v>
@@ -21336,7 +21336,7 @@
         <v>1.25</v>
       </c>
       <c r="G723" t="n">
-        <v>1.09604287147522</v>
+        <v>1.09604299068451</v>
       </c>
       <c r="H723" t="n">
         <v>600</v>
@@ -21365,7 +21365,7 @@
         <v>1.25</v>
       </c>
       <c r="G724" t="n">
-        <v>1.09604287147522</v>
+        <v>1.09604299068451</v>
       </c>
       <c r="H724" t="n">
         <v>1000</v>
@@ -21394,7 +21394,7 @@
         <v>1.25</v>
       </c>
       <c r="G725" t="n">
-        <v>1.09604287147522</v>
+        <v>1.09604299068451</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -21423,7 +21423,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G726" t="n">
-        <v>1.0916588306427</v>
+        <v>1.09165871143341</v>
       </c>
       <c r="H726" t="n">
         <v>4700</v>
@@ -21510,7 +21510,7 @@
         <v>1.25</v>
       </c>
       <c r="G729" t="n">
-        <v>1.09604287147522</v>
+        <v>1.09604299068451</v>
       </c>
       <c r="H729" t="n">
         <v>1800</v>
@@ -21568,7 +21568,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G731" t="n">
-        <v>1.0916588306427</v>
+        <v>1.09165871143341</v>
       </c>
       <c r="H731" t="n">
         <v>1304</v>
@@ -21626,7 +21626,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G733" t="n">
-        <v>1.0916588306427</v>
+        <v>1.09165871143341</v>
       </c>
       <c r="H733" t="n">
         <v>2532</v>
@@ -21655,7 +21655,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G734" t="n">
-        <v>1.0916588306427</v>
+        <v>1.09165871143341</v>
       </c>
       <c r="H734" t="n">
         <v>512</v>
@@ -21684,7 +21684,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G735" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H735" t="n">
         <v>15114</v>
@@ -21713,7 +21713,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G736" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H736" t="n">
         <v>1538</v>
@@ -21742,7 +21742,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G737" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H737" t="n">
         <v>1700</v>
@@ -21771,7 +21771,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G738" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712799072266</v>
       </c>
       <c r="H738" t="n">
         <v>16057</v>
@@ -21974,7 +21974,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.02151203155518</v>
+        <v>1.02151215076447</v>
       </c>
       <c r="H745" t="n">
         <v>24237</v>
@@ -22032,7 +22032,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G747" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712799072266</v>
       </c>
       <c r="H747" t="n">
         <v>6096</v>
@@ -22061,7 +22061,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G748" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712799072266</v>
       </c>
       <c r="H748" t="n">
         <v>705</v>
@@ -22090,7 +22090,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G749" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H749" t="n">
         <v>1815</v>
@@ -22119,7 +22119,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G750" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H750" t="n">
         <v>325</v>
@@ -22148,7 +22148,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G751" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H751" t="n">
         <v>1000</v>
@@ -22177,7 +22177,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G752" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H752" t="n">
         <v>2375</v>
@@ -22264,7 +22264,7 @@
         <v>1.125</v>
       </c>
       <c r="G755" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H755" t="n">
         <v>675</v>
@@ -22351,7 +22351,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G758" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H758" t="n">
         <v>2000</v>
@@ -22380,7 +22380,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G759" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H759" t="n">
         <v>250</v>
@@ -22438,7 +22438,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G761" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H761" t="n">
         <v>12032</v>
@@ -22496,7 +22496,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H763" t="n">
         <v>6944</v>
@@ -22525,7 +22525,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G764" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H764" t="n">
         <v>5162</v>
@@ -22554,7 +22554,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H765" t="n">
         <v>766</v>
@@ -22641,7 +22641,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G768" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H768" t="n">
         <v>21123</v>
@@ -22699,7 +22699,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G770" t="n">
-        <v>1.01274383068085</v>
+        <v>1.01274371147156</v>
       </c>
       <c r="H770" t="n">
         <v>2275</v>
@@ -22902,7 +22902,7 @@
         <v>1.125</v>
       </c>
       <c r="G777" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H777" t="n">
         <v>16848</v>
@@ -22960,7 +22960,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G779" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H779" t="n">
         <v>5722</v>
@@ -23134,7 +23134,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G785" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H785" t="n">
         <v>1050</v>
@@ -23163,7 +23163,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G786" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H786" t="n">
         <v>39305</v>
@@ -23192,7 +23192,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G787" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H787" t="n">
         <v>2450</v>
@@ -23221,7 +23221,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G788" t="n">
-        <v>0.96013355255127</v>
+        <v>0.960133612155914</v>
       </c>
       <c r="H788" t="n">
         <v>4108</v>
@@ -23395,7 +23395,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G794" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H794" t="n">
         <v>28648</v>
@@ -23424,7 +23424,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G795" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H795" t="n">
         <v>5545</v>
@@ -23453,7 +23453,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G796" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H796" t="n">
         <v>10150</v>
@@ -23482,7 +23482,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G797" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712799072266</v>
       </c>
       <c r="H797" t="n">
         <v>16615</v>
@@ -23511,7 +23511,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G798" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H798" t="n">
         <v>1122</v>
@@ -23540,7 +23540,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H799" t="n">
         <v>13650</v>
@@ -23598,7 +23598,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H801" t="n">
         <v>3770</v>
@@ -23685,7 +23685,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G804" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H804" t="n">
         <v>9541</v>
@@ -23830,7 +23830,7 @@
         <v>1.125</v>
       </c>
       <c r="G809" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H809" t="n">
         <v>4394</v>
@@ -23859,7 +23859,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H810" t="n">
         <v>56003</v>
@@ -23946,7 +23946,7 @@
         <v>1.125</v>
       </c>
       <c r="G813" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H813" t="n">
         <v>10204</v>
@@ -24033,7 +24033,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G816" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H816" t="n">
         <v>4300</v>
@@ -24207,7 +24207,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G822" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H822" t="n">
         <v>1300</v>
@@ -24236,7 +24236,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G823" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H823" t="n">
         <v>3690</v>
@@ -24265,7 +24265,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G824" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H824" t="n">
         <v>5751</v>
@@ -24294,7 +24294,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G825" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H825" t="n">
         <v>14762</v>
@@ -24323,7 +24323,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G826" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H826" t="n">
         <v>21750</v>
@@ -24352,7 +24352,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G827" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H827" t="n">
         <v>950</v>
@@ -24381,7 +24381,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H828" t="n">
         <v>1000</v>
@@ -24468,7 +24468,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G831" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H831" t="n">
         <v>600</v>
@@ -24613,7 +24613,7 @@
         <v>1.125</v>
       </c>
       <c r="G836" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H836" t="n">
         <v>7450</v>
@@ -24642,7 +24642,7 @@
         <v>1.125</v>
       </c>
       <c r="G837" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H837" t="n">
         <v>2400</v>
@@ -24671,7 +24671,7 @@
         <v>1.125</v>
       </c>
       <c r="G838" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H838" t="n">
         <v>400</v>
@@ -24700,7 +24700,7 @@
         <v>1.125</v>
       </c>
       <c r="G839" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H839" t="n">
         <v>900</v>
@@ -24729,7 +24729,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H840" t="n">
         <v>830</v>
@@ -24758,7 +24758,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G841" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H841" t="n">
         <v>1100</v>
@@ -24932,7 +24932,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H847" t="n">
         <v>475</v>
@@ -24961,7 +24961,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G848" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H848" t="n">
         <v>137</v>
@@ -25019,7 +25019,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G850" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H850" t="n">
         <v>1680</v>
@@ -25048,7 +25048,7 @@
         <v>1.125</v>
       </c>
       <c r="G851" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H851" t="n">
         <v>5800</v>
@@ -25077,7 +25077,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G852" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H852" t="n">
         <v>150</v>
@@ -25106,7 +25106,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G853" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H853" t="n">
         <v>2450</v>
@@ -25222,7 +25222,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G857" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H857" t="n">
         <v>6419</v>
@@ -25251,7 +25251,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G858" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H858" t="n">
         <v>1595</v>
@@ -25338,7 +25338,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G861" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H861" t="n">
         <v>400</v>
@@ -25396,7 +25396,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G863" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H863" t="n">
         <v>350</v>
@@ -25425,7 +25425,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G864" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H864" t="n">
         <v>725</v>
@@ -25454,7 +25454,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G865" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H865" t="n">
         <v>0</v>
@@ -25483,7 +25483,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G866" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H866" t="n">
         <v>1600</v>
@@ -25541,7 +25541,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G868" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H868" t="n">
         <v>5309</v>
@@ -25570,7 +25570,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G869" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H869" t="n">
         <v>1100</v>
@@ -25628,7 +25628,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H871" t="n">
         <v>2350</v>
@@ -25686,7 +25686,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G873" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H873" t="n">
         <v>3670</v>
@@ -25715,7 +25715,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H874" t="n">
         <v>8150</v>
@@ -25744,7 +25744,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G875" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H875" t="n">
         <v>650</v>
@@ -25889,7 +25889,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G880" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H880" t="n">
         <v>4350</v>
@@ -25947,7 +25947,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G882" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H882" t="n">
         <v>5025</v>
@@ -26063,7 +26063,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G886" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H886" t="n">
         <v>8451</v>
@@ -26121,7 +26121,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G888" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H888" t="n">
         <v>14150</v>
@@ -26150,7 +26150,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G889" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H889" t="n">
         <v>1300</v>
@@ -26179,7 +26179,7 @@
         <v>1.125</v>
       </c>
       <c r="G890" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H890" t="n">
         <v>400</v>
@@ -26440,7 +26440,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G899" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H899" t="n">
         <v>400</v>
@@ -26469,7 +26469,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G900" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H900" t="n">
         <v>600</v>
@@ -26498,7 +26498,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G901" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H901" t="n">
         <v>1344</v>
@@ -26527,7 +26527,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G902" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H902" t="n">
         <v>680</v>
@@ -26556,7 +26556,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G903" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H903" t="n">
         <v>172</v>
@@ -26585,7 +26585,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G904" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H904" t="n">
         <v>5082</v>
@@ -26614,7 +26614,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G905" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H905" t="n">
         <v>1700</v>
@@ -26701,7 +26701,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G908" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H908" t="n">
         <v>2876</v>
@@ -26759,7 +26759,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G910" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H910" t="n">
         <v>21638</v>
@@ -26817,7 +26817,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G912" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H912" t="n">
         <v>4050</v>
@@ -26846,7 +26846,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G913" t="n">
-        <v>0.96013355255127</v>
+        <v>0.960133612155914</v>
       </c>
       <c r="H913" t="n">
         <v>215</v>
@@ -26875,7 +26875,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G914" t="n">
-        <v>0.96013355255127</v>
+        <v>0.960133612155914</v>
       </c>
       <c r="H914" t="n">
         <v>800</v>
@@ -26904,7 +26904,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G915" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H915" t="n">
         <v>150</v>
@@ -26933,7 +26933,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G916" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H916" t="n">
         <v>3550</v>
@@ -26962,7 +26962,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G917" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H917" t="n">
         <v>1550</v>
@@ -26991,7 +26991,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G918" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -27020,7 +27020,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G919" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H919" t="n">
         <v>296004</v>
@@ -27049,7 +27049,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G920" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H920" t="n">
         <v>16383</v>
@@ -27165,7 +27165,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G924" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H924" t="n">
         <v>300</v>
@@ -27310,7 +27310,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G929" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H929" t="n">
         <v>2500</v>
@@ -27368,7 +27368,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G931" t="n">
-        <v>0.907523572444916</v>
+        <v>0.907523512840271</v>
       </c>
       <c r="H931" t="n">
         <v>39160</v>
@@ -27397,7 +27397,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G932" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H932" t="n">
         <v>6000</v>
@@ -27629,7 +27629,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G940" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H940" t="n">
         <v>51800</v>
@@ -27658,7 +27658,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G941" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H941" t="n">
         <v>7800</v>
@@ -27716,7 +27716,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G943" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H943" t="n">
         <v>9713</v>
@@ -27745,7 +27745,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G944" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H944" t="n">
         <v>3224</v>
@@ -27774,7 +27774,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G945" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H945" t="n">
         <v>10767</v>
@@ -27832,7 +27832,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G947" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H947" t="n">
         <v>3050</v>
@@ -27890,7 +27890,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G949" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H949" t="n">
         <v>600</v>
@@ -27919,7 +27919,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G950" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H950" t="n">
         <v>3650</v>
@@ -28412,7 +28412,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G967" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H967" t="n">
         <v>31404</v>
@@ -28441,7 +28441,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G968" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H968" t="n">
         <v>1550</v>
@@ -28847,7 +28847,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G982" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H982" t="n">
         <v>5136</v>
@@ -28876,7 +28876,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G983" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H983" t="n">
         <v>3577</v>
@@ -28905,7 +28905,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G984" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H984" t="n">
         <v>8600</v>
@@ -28963,7 +28963,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G986" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H986" t="n">
         <v>96187</v>
@@ -28992,7 +28992,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G987" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H987" t="n">
         <v>34816</v>
@@ -29137,7 +29137,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G992" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H992" t="n">
         <v>341</v>
@@ -29311,7 +29311,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G998" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H998" t="n">
         <v>28188</v>
@@ -29514,7 +29514,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1005" t="n">
-        <v>0.96013355255127</v>
+        <v>0.960133612155914</v>
       </c>
       <c r="H1005" t="n">
         <v>4949</v>
@@ -29543,7 +29543,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1006" t="n">
         <v>6657</v>
@@ -29601,7 +29601,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1008" t="n">
         <v>3778</v>
@@ -29630,7 +29630,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1009" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1009" t="n">
         <v>6074</v>
@@ -29659,7 +29659,7 @@
         <v>1.125</v>
       </c>
       <c r="G1010" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1010" t="n">
         <v>5505</v>
@@ -29688,7 +29688,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1011" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H1011" t="n">
         <v>31151</v>
@@ -29746,7 +29746,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1013" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H1013" t="n">
         <v>100</v>
@@ -29775,7 +29775,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1014" t="n">
         <v>2250</v>
@@ -29804,7 +29804,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1015" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1015" t="n">
         <v>9850</v>
@@ -29833,7 +29833,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1016" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1016" t="n">
         <v>2100</v>
@@ -29949,7 +29949,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.96013355255127</v>
+        <v>0.960133612155914</v>
       </c>
       <c r="H1020" t="n">
         <v>1750</v>
@@ -29978,7 +29978,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1021" t="n">
-        <v>0.96013355255127</v>
+        <v>0.960133612155914</v>
       </c>
       <c r="H1021" t="n">
         <v>2826</v>
@@ -30007,7 +30007,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.96013355255127</v>
+        <v>0.960133612155914</v>
       </c>
       <c r="H1022" t="n">
         <v>2950</v>
@@ -30065,7 +30065,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1024" t="n">
         <v>900</v>
@@ -30094,7 +30094,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1025" t="n">
         <v>1150</v>
@@ -30123,7 +30123,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1026" t="n">
         <v>450</v>
@@ -30152,7 +30152,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1027" t="n">
         <v>3884</v>
@@ -30326,7 +30326,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H1033" t="n">
         <v>12350</v>
@@ -30471,7 +30471,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H1038" t="n">
         <v>12529</v>
@@ -30500,7 +30500,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1039" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H1039" t="n">
         <v>52078</v>
@@ -30703,7 +30703,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.885602712631226</v>
+        <v>0.88560277223587</v>
       </c>
       <c r="H1046" t="n">
         <v>22154</v>
@@ -30761,7 +30761,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.885602712631226</v>
+        <v>0.88560277223587</v>
       </c>
       <c r="H1048" t="n">
         <v>17792</v>
@@ -30790,7 +30790,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1049" t="n">
         <v>10404</v>
@@ -30819,7 +30819,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1050" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1050" t="n">
         <v>3345</v>
@@ -30848,7 +30848,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1051" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1051" t="n">
         <v>1040</v>
@@ -30877,7 +30877,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1052" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1052" t="n">
         <v>7998</v>
@@ -30906,7 +30906,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.875080764293671</v>
+        <v>0.875080704689026</v>
       </c>
       <c r="H1053" t="n">
         <v>14456</v>
@@ -30964,7 +30964,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1055" t="n">
         <v>3900</v>
@@ -31022,7 +31022,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.866312325000763</v>
+        <v>0.866312384605408</v>
       </c>
       <c r="H1057" t="n">
         <v>12295</v>
@@ -31051,7 +31051,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1058" t="n">
         <v>4972</v>
@@ -31109,7 +31109,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1060" t="n">
         <v>8382</v>
@@ -31138,7 +31138,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1061" t="n">
         <v>2900</v>
@@ -31167,7 +31167,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.8680659532547</v>
+        <v>0.868066012859344</v>
       </c>
       <c r="H1062" t="n">
         <v>3362</v>
@@ -31225,7 +31225,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.768106877803802</v>
+        <v>0.768106818199158</v>
       </c>
       <c r="H1064" t="n">
         <v>110295</v>
@@ -31312,7 +31312,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1067" t="n">
         <v>38922</v>
@@ -31370,7 +31370,7 @@
         <v>0.75</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1069" t="n">
         <v>1500</v>
@@ -31515,7 +31515,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.754077553749084</v>
+        <v>0.754077613353729</v>
       </c>
       <c r="H1074" t="n">
         <v>10601</v>
@@ -31573,7 +31573,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.766353249549866</v>
+        <v>0.766353189945221</v>
       </c>
       <c r="H1076" t="n">
         <v>12268</v>
@@ -31631,7 +31631,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.715496778488159</v>
+        <v>0.715496838092804</v>
       </c>
       <c r="H1078" t="n">
         <v>5548</v>
@@ -31660,7 +31660,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1079" t="n">
         <v>1650</v>
@@ -31718,7 +31718,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.734787106513977</v>
+        <v>0.734787166118622</v>
       </c>
       <c r="H1081" t="n">
         <v>1250</v>
@@ -31747,7 +31747,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.720757901668549</v>
+        <v>0.720757842063904</v>
       </c>
       <c r="H1082" t="n">
         <v>6300</v>
@@ -31776,7 +31776,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.734787106513977</v>
+        <v>0.734787166118622</v>
       </c>
       <c r="H1083" t="n">
         <v>4449</v>
@@ -31834,7 +31834,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1085" t="n">
         <v>3850</v>
@@ -31863,7 +31863,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H1086" t="n">
         <v>5450</v>
@@ -31892,7 +31892,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.754077553749084</v>
+        <v>0.754077613353729</v>
       </c>
       <c r="H1087" t="n">
         <v>2296</v>
@@ -31950,7 +31950,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.752323925495148</v>
+        <v>0.752323865890503</v>
       </c>
       <c r="H1089" t="n">
         <v>1410</v>
@@ -31979,7 +31979,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.752323925495148</v>
+        <v>0.752323865890503</v>
       </c>
       <c r="H1090" t="n">
         <v>4287</v>
@@ -32008,7 +32008,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.754077553749084</v>
+        <v>0.754077613353729</v>
       </c>
       <c r="H1091" t="n">
         <v>8076</v>
@@ -32066,7 +32066,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.755831182003021</v>
+        <v>0.755831241607666</v>
       </c>
       <c r="H1093" t="n">
         <v>2960</v>
@@ -32095,7 +32095,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.722511529922485</v>
+        <v>0.722511470317841</v>
       </c>
       <c r="H1094" t="n">
         <v>5507</v>
@@ -32124,7 +32124,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.755831182003021</v>
+        <v>0.755831241607666</v>
       </c>
       <c r="H1095" t="n">
         <v>1768</v>
@@ -32153,7 +32153,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.755831182003021</v>
+        <v>0.755831241607666</v>
       </c>
       <c r="H1096" t="n">
         <v>10</v>
@@ -32182,7 +32182,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.755831182003021</v>
+        <v>0.755831241607666</v>
       </c>
       <c r="H1097" t="n">
         <v>10883</v>
@@ -32211,7 +32211,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.752323925495148</v>
+        <v>0.752323865890503</v>
       </c>
       <c r="H1098" t="n">
         <v>90</v>
@@ -32327,7 +32327,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.745309174060822</v>
+        <v>0.745309233665466</v>
       </c>
       <c r="H1102" t="n">
         <v>51</v>
@@ -32472,7 +32472,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.720757901668549</v>
+        <v>0.720757842063904</v>
       </c>
       <c r="H1107" t="n">
         <v>6000</v>
@@ -32559,7 +32559,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.748816549777985</v>
+        <v>0.74881649017334</v>
       </c>
       <c r="H1110" t="n">
         <v>1200</v>
@@ -32588,7 +32588,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.745309174060822</v>
+        <v>0.745309233665466</v>
       </c>
       <c r="H1111" t="n">
         <v>687</v>
@@ -32617,7 +32617,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.726018846035004</v>
+        <v>0.726018905639648</v>
       </c>
       <c r="H1112" t="n">
         <v>1325</v>
@@ -32675,7 +32675,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.731279850006104</v>
+        <v>0.731279909610748</v>
       </c>
       <c r="H1114" t="n">
         <v>200</v>
@@ -32762,7 +32762,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.708482205867767</v>
+        <v>0.708482146263123</v>
       </c>
       <c r="H1117" t="n">
         <v>1178</v>
@@ -32791,7 +32791,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.722511529922485</v>
+        <v>0.722511470317841</v>
       </c>
       <c r="H1118" t="n">
         <v>720</v>
@@ -32820,7 +32820,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1119" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1119" t="n">
         <v>570</v>
@@ -32849,7 +32849,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.708482205867767</v>
+        <v>0.708482146263123</v>
       </c>
       <c r="H1120" t="n">
         <v>6800</v>
@@ -32907,7 +32907,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.713743150234222</v>
+        <v>0.713743209838867</v>
       </c>
       <c r="H1122" t="n">
         <v>1350</v>
@@ -32994,7 +32994,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H1125" t="n">
         <v>49187</v>
@@ -33023,7 +33023,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.713743150234222</v>
+        <v>0.713743209838867</v>
       </c>
       <c r="H1126" t="n">
         <v>13740</v>
@@ -33052,7 +33052,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.717250466346741</v>
+        <v>0.717250525951385</v>
       </c>
       <c r="H1127" t="n">
         <v>8000</v>
@@ -33168,7 +33168,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.690945386886597</v>
+        <v>0.690945446491241</v>
       </c>
       <c r="H1131" t="n">
         <v>11750</v>
@@ -33371,7 +33371,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1138" t="n">
         <v>2160</v>
@@ -33400,7 +33400,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.690945386886597</v>
+        <v>0.690945446491241</v>
       </c>
       <c r="H1139" t="n">
         <v>300</v>
@@ -33429,7 +33429,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1140" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1140" t="n">
         <v>270</v>
@@ -33487,7 +33487,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.690945386886597</v>
+        <v>0.690945446491241</v>
       </c>
       <c r="H1142" t="n">
         <v>4300</v>
@@ -33516,7 +33516,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.676916182041168</v>
+        <v>0.676916062831879</v>
       </c>
       <c r="H1143" t="n">
         <v>5575</v>
@@ -33545,7 +33545,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.676916182041168</v>
+        <v>0.676916062831879</v>
       </c>
       <c r="H1144" t="n">
         <v>450</v>
@@ -33574,7 +33574,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.678669810295105</v>
+        <v>0.67866975069046</v>
       </c>
       <c r="H1145" t="n">
         <v>550</v>
@@ -33603,7 +33603,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.664640545845032</v>
+        <v>0.664640486240387</v>
       </c>
       <c r="H1146" t="n">
         <v>9151</v>
@@ -33632,7 +33632,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.664640545845032</v>
+        <v>0.664640486240387</v>
       </c>
       <c r="H1147" t="n">
         <v>8179</v>
@@ -33690,7 +33690,7 @@
         <v>0.75</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1149" t="n">
         <v>11104</v>
@@ -33719,7 +33719,7 @@
         <v>0.75</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1150" t="n">
         <v>8568</v>
@@ -33777,7 +33777,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.643596410751343</v>
+        <v>0.643596470355988</v>
       </c>
       <c r="H1152" t="n">
         <v>300</v>
@@ -33835,7 +33835,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.676916182041168</v>
+        <v>0.676916062831879</v>
       </c>
       <c r="H1154" t="n">
         <v>7250</v>
@@ -33893,7 +33893,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.655872166156769</v>
+        <v>0.655872106552124</v>
       </c>
       <c r="H1156" t="n">
         <v>4915</v>
@@ -33951,7 +33951,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.690945386886597</v>
+        <v>0.690945446491241</v>
       </c>
       <c r="H1158" t="n">
         <v>20151</v>
@@ -33980,7 +33980,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.680423498153687</v>
+        <v>0.680423438549042</v>
       </c>
       <c r="H1159" t="n">
         <v>450</v>
@@ -34009,7 +34009,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.680423498153687</v>
+        <v>0.680423438549042</v>
       </c>
       <c r="H1160" t="n">
         <v>150</v>
@@ -34038,7 +34038,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.682177126407623</v>
+        <v>0.682177186012268</v>
       </c>
       <c r="H1161" t="n">
         <v>10635</v>
@@ -34299,7 +34299,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H1170" t="n">
         <v>68323</v>
@@ -34328,7 +34328,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.734787106513977</v>
+        <v>0.734787166118622</v>
       </c>
       <c r="H1171" t="n">
         <v>7626</v>
@@ -34386,7 +34386,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.720757901668549</v>
+        <v>0.720757842063904</v>
       </c>
       <c r="H1173" t="n">
         <v>1300</v>
@@ -34415,7 +34415,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H1174" t="n">
         <v>6010</v>
@@ -34444,7 +34444,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.722511529922485</v>
+        <v>0.722511470317841</v>
       </c>
       <c r="H1175" t="n">
         <v>3713</v>
@@ -34473,7 +34473,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.752323925495148</v>
+        <v>0.752323865890503</v>
       </c>
       <c r="H1176" t="n">
         <v>4938</v>
@@ -34560,7 +34560,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.719004154205322</v>
+        <v>0.719004094600677</v>
       </c>
       <c r="H1179" t="n">
         <v>1150</v>
@@ -34589,7 +34589,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.704974889755249</v>
+        <v>0.704974830150604</v>
       </c>
       <c r="H1180" t="n">
         <v>10005</v>
@@ -34618,7 +34618,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.726018846035004</v>
+        <v>0.726018905639648</v>
       </c>
       <c r="H1181" t="n">
         <v>6455</v>
@@ -34647,7 +34647,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.726018846035004</v>
+        <v>0.726018905639648</v>
       </c>
       <c r="H1182" t="n">
         <v>0</v>
@@ -34676,7 +34676,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.726018846035004</v>
+        <v>0.726018905639648</v>
       </c>
       <c r="H1183" t="n">
         <v>200</v>
@@ -34705,7 +34705,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1184" t="n">
         <v>1100</v>
@@ -34734,7 +34734,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.726018846035004</v>
+        <v>0.726018905639648</v>
       </c>
       <c r="H1185" t="n">
         <v>351</v>
@@ -34763,7 +34763,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.704974889755249</v>
+        <v>0.704974830150604</v>
       </c>
       <c r="H1186" t="n">
         <v>1100</v>
@@ -34792,7 +34792,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.704974889755249</v>
+        <v>0.704974830150604</v>
       </c>
       <c r="H1187" t="n">
         <v>1250</v>
@@ -34821,7 +34821,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.704974889755249</v>
+        <v>0.704974830150604</v>
       </c>
       <c r="H1188" t="n">
         <v>2827</v>
@@ -34850,7 +34850,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1189" t="n">
         <v>300</v>
@@ -34879,7 +34879,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1190" t="n">
         <v>0</v>
@@ -34937,7 +34937,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.717250466346741</v>
+        <v>0.717250525951385</v>
       </c>
       <c r="H1192" t="n">
         <v>5450</v>
@@ -34966,7 +34966,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.717250466346741</v>
+        <v>0.717250525951385</v>
       </c>
       <c r="H1193" t="n">
         <v>7747</v>
@@ -34995,7 +34995,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.722511529922485</v>
+        <v>0.722511470317841</v>
       </c>
       <c r="H1194" t="n">
         <v>6200</v>
@@ -35082,7 +35082,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1197" t="n">
         <v>7200</v>
@@ -35111,7 +35111,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1198" t="n">
         <v>6</v>
@@ -35198,7 +35198,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.687438130378723</v>
+        <v>0.687438189983368</v>
       </c>
       <c r="H1201" t="n">
         <v>3947</v>
@@ -35256,7 +35256,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.664640545845032</v>
+        <v>0.664640486240387</v>
       </c>
       <c r="H1203" t="n">
         <v>18592</v>
@@ -35285,7 +35285,7 @@
         <v>0.75</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1204" t="n">
         <v>2524</v>
@@ -35314,7 +35314,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.67340874671936</v>
+        <v>0.673408806324005</v>
       </c>
       <c r="H1205" t="n">
         <v>20447</v>
@@ -35430,7 +35430,7 @@
         <v>0.75</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1209" t="n">
         <v>26135</v>
@@ -35459,7 +35459,7 @@
         <v>0.75</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1210" t="n">
         <v>14840</v>
@@ -35517,7 +35517,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.659379363059998</v>
+        <v>0.659379422664642</v>
       </c>
       <c r="H1212" t="n">
         <v>3000</v>
@@ -35575,7 +35575,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.669901371002197</v>
+        <v>0.669901430606842</v>
       </c>
       <c r="H1214" t="n">
         <v>16550</v>
@@ -35604,7 +35604,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.669901371002197</v>
+        <v>0.669901430606842</v>
       </c>
       <c r="H1215" t="n">
         <v>0</v>
@@ -35633,7 +35633,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.669901371002197</v>
+        <v>0.669901430606842</v>
       </c>
       <c r="H1216" t="n">
         <v>0</v>
@@ -35662,7 +35662,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.669901371002197</v>
+        <v>0.669901430606842</v>
       </c>
       <c r="H1217" t="n">
         <v>4100</v>
@@ -35778,7 +35778,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.699713826179504</v>
+        <v>0.69971376657486</v>
       </c>
       <c r="H1221" t="n">
         <v>1840</v>
@@ -35807,7 +35807,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.699713826179504</v>
+        <v>0.69971376657486</v>
       </c>
       <c r="H1222" t="n">
         <v>0</v>
@@ -35981,7 +35981,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.676916182041168</v>
+        <v>0.676916062831879</v>
       </c>
       <c r="H1228" t="n">
         <v>11563</v>
@@ -36068,7 +36068,7 @@
         <v>0.75</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.657625794410706</v>
+        <v>0.657625734806061</v>
       </c>
       <c r="H1231" t="n">
         <v>5100</v>
@@ -36097,7 +36097,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.652364790439606</v>
+        <v>0.652364730834961</v>
       </c>
       <c r="H1232" t="n">
         <v>2438</v>
@@ -36155,7 +36155,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.626059651374817</v>
+        <v>0.626059710979462</v>
       </c>
       <c r="H1234" t="n">
         <v>11723</v>
@@ -36184,7 +36184,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.655872166156769</v>
+        <v>0.655872106552124</v>
       </c>
       <c r="H1235" t="n">
         <v>61153</v>
@@ -36271,7 +36271,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.652364790439606</v>
+        <v>0.652364730834961</v>
       </c>
       <c r="H1238" t="n">
         <v>17873</v>
@@ -36358,7 +36358,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.699713826179504</v>
+        <v>0.69971376657486</v>
       </c>
       <c r="H1241" t="n">
         <v>68600</v>
@@ -36387,7 +36387,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1242" t="n">
         <v>8508</v>
@@ -36503,7 +36503,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.720757901668549</v>
+        <v>0.720757842063904</v>
       </c>
       <c r="H1246" t="n">
         <v>21967</v>
@@ -36532,7 +36532,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1247" t="n">
         <v>33446</v>
@@ -36590,7 +36590,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.704974889755249</v>
+        <v>0.704974830150604</v>
       </c>
       <c r="H1249" t="n">
         <v>46900</v>
@@ -36677,7 +36677,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.715496778488159</v>
+        <v>0.715496838092804</v>
       </c>
       <c r="H1252" t="n">
         <v>11952</v>
@@ -36706,7 +36706,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.717250466346741</v>
+        <v>0.717250525951385</v>
       </c>
       <c r="H1253" t="n">
         <v>4049</v>
@@ -36793,7 +36793,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.708482205867767</v>
+        <v>0.708482146263123</v>
       </c>
       <c r="H1256" t="n">
         <v>600</v>
@@ -36822,7 +36822,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.724265158176422</v>
+        <v>0.724265098571777</v>
       </c>
       <c r="H1257" t="n">
         <v>6564</v>
@@ -36851,7 +36851,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.701467454433441</v>
+        <v>0.701467514038086</v>
       </c>
       <c r="H1258" t="n">
         <v>2900</v>
@@ -36909,7 +36909,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1260" t="n">
         <v>810814</v>
@@ -37054,7 +37054,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.822470605373383</v>
+        <v>0.822470664978027</v>
       </c>
       <c r="H1265" t="n">
         <v>63120</v>
@@ -37083,7 +37083,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.808441281318665</v>
+        <v>0.80844122171402</v>
       </c>
       <c r="H1266" t="n">
         <v>16831</v>
@@ -37141,7 +37141,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.797919273376465</v>
+        <v>0.79791933298111</v>
       </c>
       <c r="H1268" t="n">
         <v>46480</v>
@@ -37170,7 +37170,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.801426529884338</v>
+        <v>0.801426589488983</v>
       </c>
       <c r="H1269" t="n">
         <v>8720</v>
@@ -37286,7 +37286,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.768106877803802</v>
+        <v>0.768106818199158</v>
       </c>
       <c r="H1273" t="n">
         <v>49707</v>
@@ -37315,7 +37315,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.75933849811554</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H1274" t="n">
         <v>26378</v>
@@ -37344,7 +37344,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H1275" t="n">
         <v>27171</v>
@@ -37373,7 +37373,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H1276" t="n">
         <v>4000</v>
@@ -37402,7 +37402,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.755831182003021</v>
+        <v>0.755831241607666</v>
       </c>
       <c r="H1277" t="n">
         <v>29235</v>
@@ -37431,7 +37431,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H1278" t="n">
         <v>1700</v>
@@ -37489,7 +37489,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.764599561691284</v>
+        <v>0.764599502086639</v>
       </c>
       <c r="H1280" t="n">
         <v>16065</v>
@@ -37518,7 +37518,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.747062861919403</v>
+        <v>0.747062802314758</v>
       </c>
       <c r="H1281" t="n">
         <v>5198</v>
@@ -37576,7 +37576,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.75933849811554</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H1283" t="n">
         <v>24416</v>
@@ -37605,7 +37605,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H1284" t="n">
         <v>9857</v>
@@ -37634,7 +37634,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.754077553749084</v>
+        <v>0.754077613353729</v>
       </c>
       <c r="H1285" t="n">
         <v>13116</v>
@@ -37663,7 +37663,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H1286" t="n">
         <v>19954</v>
@@ -37692,7 +37692,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H1287" t="n">
         <v>12616</v>
@@ -37721,7 +37721,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.762845933437347</v>
+        <v>0.762845873832703</v>
       </c>
       <c r="H1288" t="n">
         <v>400</v>
@@ -37779,7 +37779,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.757584810256958</v>
+        <v>0.757584869861603</v>
       </c>
       <c r="H1290" t="n">
         <v>3137</v>
@@ -37837,7 +37837,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.75933849811554</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H1292" t="n">
         <v>3300</v>
@@ -37866,7 +37866,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.75933849811554</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H1293" t="n">
         <v>28216</v>
@@ -37924,7 +37924,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.778628885746002</v>
+        <v>0.778628945350647</v>
       </c>
       <c r="H1295" t="n">
         <v>29012</v>
@@ -37953,7 +37953,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.797919273376465</v>
+        <v>0.79791933298111</v>
       </c>
       <c r="H1296" t="n">
         <v>81386</v>
@@ -38069,7 +38069,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.806687593460083</v>
+        <v>0.806687533855438</v>
       </c>
       <c r="H1300" t="n">
         <v>5762</v>
@@ -38127,7 +38127,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.773367941379547</v>
+        <v>0.773368000984192</v>
       </c>
       <c r="H1302" t="n">
         <v>10464</v>
@@ -38214,7 +38214,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1305" t="n">
         <v>160</v>
@@ -38243,7 +38243,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1306" t="n">
         <v>5510</v>
@@ -38330,7 +38330,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.75933849811554</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H1309" t="n">
         <v>4900</v>
@@ -38359,7 +38359,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.757584810256958</v>
+        <v>0.757584869861603</v>
       </c>
       <c r="H1310" t="n">
         <v>1000</v>
@@ -38388,7 +38388,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.748816549777985</v>
+        <v>0.74881649017334</v>
       </c>
       <c r="H1311" t="n">
         <v>9601</v>
@@ -38417,7 +38417,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.747062861919403</v>
+        <v>0.747062802314758</v>
       </c>
       <c r="H1312" t="n">
         <v>225</v>
@@ -38446,7 +38446,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.745309174060822</v>
+        <v>0.745309233665466</v>
       </c>
       <c r="H1313" t="n">
         <v>14924</v>
@@ -38475,7 +38475,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.754077553749084</v>
+        <v>0.754077613353729</v>
       </c>
       <c r="H1314" t="n">
         <v>4728</v>
@@ -38504,7 +38504,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.778628885746002</v>
+        <v>0.778628945350647</v>
       </c>
       <c r="H1315" t="n">
         <v>12125</v>
@@ -38562,7 +38562,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.778628885746002</v>
+        <v>0.778628945350647</v>
       </c>
       <c r="H1317" t="n">
         <v>13318</v>
@@ -38678,7 +38678,7 @@
         <v>0.86599999666214</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.75933849811554</v>
+        <v>0.759338557720184</v>
       </c>
       <c r="H1321" t="n">
         <v>6573</v>
@@ -38707,7 +38707,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.773367941379547</v>
+        <v>0.773368000984192</v>
       </c>
       <c r="H1322" t="n">
         <v>99014</v>
@@ -38765,7 +38765,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1324" t="n">
         <v>15288</v>
@@ -38881,7 +38881,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1328" t="n">
         <v>5938</v>
@@ -39055,7 +39055,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1334" t="n">
         <v>79220</v>
@@ -39171,7 +39171,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.797919273376465</v>
+        <v>0.79791933298111</v>
       </c>
       <c r="H1338" t="n">
         <v>95484</v>
@@ -39229,7 +39229,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1340" t="n">
         <v>21126</v>
@@ -39316,7 +39316,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1343" t="n">
         <v>18194</v>
@@ -39345,7 +39345,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1344" t="n">
         <v>10200</v>
@@ -39461,7 +39461,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.78739732503891</v>
+        <v>0.787397265434265</v>
       </c>
       <c r="H1348" t="n">
         <v>4600</v>
@@ -39548,7 +39548,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.797919273376465</v>
+        <v>0.79791933298111</v>
       </c>
       <c r="H1351" t="n">
         <v>31000</v>
@@ -39722,7 +39722,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.797919273376465</v>
+        <v>0.79791933298111</v>
       </c>
       <c r="H1357" t="n">
         <v>67495</v>
@@ -40099,7 +40099,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.831238985061646</v>
+        <v>0.831238925457001</v>
       </c>
       <c r="H1370" t="n">
         <v>14603</v>
@@ -40302,7 +40302,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.834746360778809</v>
+        <v>0.834746301174164</v>
       </c>
       <c r="H1377" t="n">
         <v>61095</v>
@@ -40331,7 +40331,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1378" t="n">
         <v>42170</v>
@@ -40737,7 +40737,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.834746360778809</v>
+        <v>0.834746301174164</v>
       </c>
       <c r="H1392" t="n">
         <v>20575</v>
@@ -40766,7 +40766,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1393" t="n">
         <v>211690</v>
@@ -40824,7 +40824,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.843514621257782</v>
+        <v>0.843514680862427</v>
       </c>
       <c r="H1395" t="n">
         <v>23039</v>
@@ -41085,7 +41085,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1404" t="n">
         <v>6325</v>
@@ -41201,7 +41201,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.841760993003845</v>
+        <v>0.84176105260849</v>
       </c>
       <c r="H1408" t="n">
         <v>100</v>
@@ -41259,7 +41259,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.831238985061646</v>
+        <v>0.831238925457001</v>
       </c>
       <c r="H1410" t="n">
         <v>13195</v>
@@ -41462,7 +41462,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.885602712631226</v>
+        <v>0.88560277223587</v>
       </c>
       <c r="H1417" t="n">
         <v>167920</v>
@@ -41665,7 +41665,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.907523572444916</v>
+        <v>0.907523512840271</v>
       </c>
       <c r="H1424" t="n">
         <v>25090</v>
@@ -41694,7 +41694,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1425" t="n">
         <v>23120</v>
@@ -41752,7 +41752,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H1427" t="n">
         <v>9350</v>
@@ -41781,7 +41781,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1428" t="n">
         <v>20550</v>
@@ -41839,7 +41839,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.907523572444916</v>
+        <v>0.907523512840271</v>
       </c>
       <c r="H1430" t="n">
         <v>18948</v>
@@ -42071,7 +42071,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.875080764293671</v>
+        <v>0.875080704689026</v>
       </c>
       <c r="H1438" t="n">
         <v>4723</v>
@@ -42129,7 +42129,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.885602712631226</v>
+        <v>0.88560277223587</v>
       </c>
       <c r="H1440" t="n">
         <v>13850</v>
@@ -42187,7 +42187,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1442" t="n">
         <v>6430</v>
@@ -42216,7 +42216,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H1443" t="n">
         <v>4820</v>
@@ -42245,7 +42245,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H1444" t="n">
         <v>30099</v>
@@ -42332,7 +42332,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H1447" t="n">
         <v>7450</v>
@@ -42390,7 +42390,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H1449" t="n">
         <v>650</v>
@@ -42448,7 +42448,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H1451" t="n">
         <v>2950</v>
@@ -42477,7 +42477,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1452" t="n">
         <v>1850</v>
@@ -42593,7 +42593,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H1456" t="n">
         <v>79094</v>
@@ -42651,7 +42651,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.01274383068085</v>
+        <v>1.01274371147156</v>
       </c>
       <c r="H1458" t="n">
         <v>15028</v>
@@ -42680,7 +42680,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.01274383068085</v>
+        <v>1.01274371147156</v>
       </c>
       <c r="H1459" t="n">
         <v>6028</v>
@@ -42709,7 +42709,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1460" t="n">
         <v>12250</v>
@@ -42738,7 +42738,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H1461" t="n">
         <v>25327</v>
@@ -42767,7 +42767,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1462" t="n">
         <v>11940</v>
@@ -42796,7 +42796,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1463" t="n">
         <v>27461</v>
@@ -42825,7 +42825,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1464" t="n">
         <v>6983</v>
@@ -42854,7 +42854,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H1465" t="n">
         <v>5335</v>
@@ -42912,7 +42912,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1467" t="n">
         <v>20530</v>
@@ -42941,7 +42941,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H1468" t="n">
         <v>26115</v>
@@ -42999,7 +42999,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H1470" t="n">
         <v>4600</v>
@@ -43028,7 +43028,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1471" t="n">
         <v>5959</v>
@@ -43057,7 +43057,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1472" t="n">
         <v>14330</v>
@@ -43173,7 +43173,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H1476" t="n">
         <v>18831</v>
@@ -43260,7 +43260,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.06535375118256</v>
+        <v>1.06535387039185</v>
       </c>
       <c r="H1479" t="n">
         <v>36700</v>
@@ -43289,7 +43289,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1480" t="n">
-        <v>1.06973791122437</v>
+        <v>1.06973803043365</v>
       </c>
       <c r="H1480" t="n">
         <v>5619</v>
@@ -43347,7 +43347,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H1482" t="n">
         <v>6256</v>
@@ -43376,7 +43376,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.05220139026642</v>
+        <v>1.05220127105713</v>
       </c>
       <c r="H1483" t="n">
         <v>18337</v>
@@ -43405,7 +43405,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.04343295097351</v>
+        <v>1.04343283176422</v>
       </c>
       <c r="H1484" t="n">
         <v>4211</v>
@@ -43550,7 +43550,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.01274383068085</v>
+        <v>1.01274371147156</v>
       </c>
       <c r="H1489" t="n">
         <v>11289</v>
@@ -43608,7 +43608,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.04343295097351</v>
+        <v>1.04343283176422</v>
       </c>
       <c r="H1491" t="n">
         <v>24095</v>
@@ -43695,7 +43695,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712799072266</v>
       </c>
       <c r="H1494" t="n">
         <v>7014</v>
@@ -43753,7 +43753,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.06973791122437</v>
+        <v>1.06973803043365</v>
       </c>
       <c r="H1496" t="n">
         <v>47692</v>
@@ -43782,7 +43782,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.06535375118256</v>
+        <v>1.06535387039185</v>
       </c>
       <c r="H1497" t="n">
         <v>11328</v>
@@ -43869,7 +43869,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H1500" t="n">
         <v>43292</v>
@@ -43898,7 +43898,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1501" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H1501" t="n">
         <v>27581</v>
@@ -43956,7 +43956,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1503" t="n">
         <v>7694</v>
@@ -43985,7 +43985,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1504" t="n">
         <v>6900</v>
@@ -44043,7 +44043,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H1506" t="n">
         <v>2753</v>
@@ -44072,7 +44072,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H1507" t="n">
         <v>2177</v>
@@ -44101,7 +44101,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1508" t="n">
         <v>300</v>
@@ -44130,7 +44130,7 @@
         <v>1.125</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1509" t="n">
         <v>4100</v>
@@ -44188,7 +44188,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1511" t="n">
         <v>7519</v>
@@ -44246,7 +44246,7 @@
         <v>1.125</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1513" t="n">
         <v>4453</v>
@@ -44275,7 +44275,7 @@
         <v>1.125</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1514" t="n">
         <v>8187</v>
@@ -44304,7 +44304,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1515" t="n">
         <v>3300</v>
@@ -44333,7 +44333,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.995207011699677</v>
+        <v>0.995206952095032</v>
       </c>
       <c r="H1516" t="n">
         <v>7294</v>
@@ -44507,7 +44507,7 @@
         <v>1.125</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1522" t="n">
         <v>13150</v>
@@ -44536,7 +44536,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1523" t="n">
         <v>5919</v>
@@ -44623,7 +44623,7 @@
         <v>1.125</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1526" t="n">
         <v>17350</v>
@@ -44681,7 +44681,7 @@
         <v>1.125</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1528" t="n">
         <v>27071</v>
@@ -44739,7 +44739,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.96013355255127</v>
+        <v>0.960133612155914</v>
       </c>
       <c r="H1530" t="n">
         <v>32088</v>
@@ -44768,7 +44768,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1531" t="n">
         <v>37012</v>
@@ -44826,7 +44826,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1533" t="n">
         <v>1578</v>
@@ -44855,7 +44855,7 @@
         <v>1.125</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1534" t="n">
         <v>9800</v>
@@ -44884,7 +44884,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1535" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H1535" t="n">
         <v>8990</v>
@@ -44942,7 +44942,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1537" t="n">
         <v>1789</v>
@@ -45000,7 +45000,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H1539" t="n">
         <v>525</v>
@@ -45029,7 +45029,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H1540" t="n">
         <v>2350</v>
@@ -45058,7 +45058,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.96013355255127</v>
+        <v>0.960133612155914</v>
       </c>
       <c r="H1541" t="n">
         <v>32992</v>
@@ -45116,7 +45116,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1543" t="n">
         <v>1083</v>
@@ -45145,7 +45145,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1544" t="n">
         <v>2923</v>
@@ -45261,7 +45261,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1548" t="n">
         <v>1947</v>
@@ -45290,7 +45290,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1549" t="n">
         <v>1600</v>
@@ -45348,7 +45348,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1551" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1551" t="n">
         <v>2123</v>
@@ -45377,7 +45377,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1552" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1552" t="n">
         <v>15148</v>
@@ -45406,7 +45406,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1553" t="n">
         <v>300</v>
@@ -45435,7 +45435,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1554" t="n">
         <v>774</v>
@@ -45464,7 +45464,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1555" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1555" t="n">
         <v>12092</v>
@@ -45493,7 +45493,7 @@
         <v>1.125</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1556" t="n">
         <v>22758</v>
@@ -45522,7 +45522,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.946981191635132</v>
+        <v>0.946981132030487</v>
       </c>
       <c r="H1557" t="n">
         <v>25631</v>
@@ -45580,7 +45580,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1559" t="n">
         <v>150</v>
@@ -45609,7 +45609,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1560" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1560" t="n">
         <v>7300</v>
@@ -45638,7 +45638,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1561" t="n">
         <v>10850</v>
@@ -45667,7 +45667,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1562" t="n">
         <v>600</v>
@@ -45725,7 +45725,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1564" t="n">
         <v>8850</v>
@@ -45754,7 +45754,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H1565" t="n">
         <v>25665</v>
@@ -45841,7 +45841,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H1568" t="n">
         <v>7700</v>
@@ -45870,7 +45870,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.91190767288208</v>
+        <v>0.911907732486725</v>
       </c>
       <c r="H1569" t="n">
         <v>450</v>
@@ -45899,7 +45899,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1570" t="n">
         <v>29110</v>
@@ -45957,7 +45957,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G1572" t="n">
-        <v>0.859297752380371</v>
+        <v>0.859297633171082</v>
       </c>
       <c r="H1572" t="n">
         <v>19670</v>
@@ -45986,7 +45986,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.885602712631226</v>
+        <v>0.88560277223587</v>
       </c>
       <c r="H1573" t="n">
         <v>19750</v>
@@ -46073,7 +46073,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.916291832923889</v>
+        <v>0.916291892528534</v>
       </c>
       <c r="H1576" t="n">
         <v>27717</v>
@@ -46102,7 +46102,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1577" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1577" t="n">
         <v>35938</v>
@@ -46131,7 +46131,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.903139412403107</v>
+        <v>0.903139293193817</v>
       </c>
       <c r="H1578" t="n">
         <v>10501</v>
@@ -46392,7 +46392,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1587" t="n">
         <v>27573</v>
@@ -46421,7 +46421,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1588" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1588" t="n">
         <v>25200</v>
@@ -46450,7 +46450,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1589" t="n">
         <v>10000</v>
@@ -46508,7 +46508,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712799072266</v>
       </c>
       <c r="H1591" t="n">
         <v>55161</v>
@@ -46537,7 +46537,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712799072266</v>
       </c>
       <c r="H1592" t="n">
         <v>13872</v>
@@ -46566,7 +46566,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.01274383068085</v>
+        <v>1.01274371147156</v>
       </c>
       <c r="H1593" t="n">
         <v>27395</v>
@@ -46711,7 +46711,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.00835943222046</v>
+        <v>1.00835955142975</v>
       </c>
       <c r="H1598" t="n">
         <v>10325</v>
@@ -46740,7 +46740,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.01712787151337</v>
+        <v>1.01712799072266</v>
       </c>
       <c r="H1599" t="n">
         <v>6320</v>
@@ -46769,7 +46769,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.00397539138794</v>
+        <v>1.00397527217865</v>
       </c>
       <c r="H1600" t="n">
         <v>11249</v>
@@ -46943,7 +46943,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.982054352760315</v>
+        <v>0.982054471969604</v>
       </c>
       <c r="H1606" t="n">
         <v>11917</v>
@@ -47117,7 +47117,7 @@
         <v>1.125</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1612" t="n">
         <v>2350</v>
@@ -47175,7 +47175,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H1614" t="n">
         <v>23461</v>
@@ -47204,7 +47204,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.96013355255127</v>
+        <v>0.960133612155914</v>
       </c>
       <c r="H1615" t="n">
         <v>22377</v>
@@ -47233,7 +47233,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.96013355255127</v>
+        <v>0.960133612155914</v>
       </c>
       <c r="H1616" t="n">
         <v>3045</v>
@@ -47320,7 +47320,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.95574951171875</v>
+        <v>0.955749452114105</v>
       </c>
       <c r="H1619" t="n">
         <v>1935</v>
@@ -47349,7 +47349,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.964517712593079</v>
+        <v>0.964517772197723</v>
       </c>
       <c r="H1620" t="n">
         <v>4058</v>
@@ -47407,7 +47407,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.968901872634888</v>
+        <v>0.968901932239532</v>
       </c>
       <c r="H1622" t="n">
         <v>2257</v>
@@ -47436,7 +47436,7 @@
         <v>1.125</v>
       </c>
       <c r="G1623" t="n">
-        <v>0.986438691616058</v>
+        <v>0.986438632011414</v>
       </c>
       <c r="H1623" t="n">
         <v>2207</v>
@@ -47494,7 +47494,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1625" t="n">
-        <v>0.99983024597168</v>
+        <v>0.999830305576324</v>
       </c>
       <c r="H1625" t="n">
         <v>314</v>
@@ -47523,7 +47523,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1626" t="n">
-        <v>1.00883769989014</v>
+        <v>1.00883781909943</v>
       </c>
       <c r="H1626" t="n">
         <v>100</v>
@@ -47552,7 +47552,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1627" t="n">
-        <v>1.00883769989014</v>
+        <v>1.00883781909943</v>
       </c>
       <c r="H1627" t="n">
         <v>0</v>
@@ -47581,7 +47581,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1628" t="n">
-        <v>1.00883769989014</v>
+        <v>1.00883781909943</v>
       </c>
       <c r="H1628" t="n">
         <v>0</v>
@@ -47610,7 +47610,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.99983024597168</v>
+        <v>0.999830305576324</v>
       </c>
       <c r="H1629" t="n">
         <v>27540</v>
@@ -47639,7 +47639,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1630" t="n">
-        <v>0.99983024597168</v>
+        <v>0.999830305576324</v>
       </c>
       <c r="H1630" t="n">
         <v>0</v>
@@ -47726,7 +47726,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.00433397293091</v>
+        <v>1.0043340921402</v>
       </c>
       <c r="H1633" t="n">
         <v>6758</v>
@@ -47755,7 +47755,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1634" t="n">
-        <v>1.00883769989014</v>
+        <v>1.00883781909943</v>
       </c>
       <c r="H1634" t="n">
         <v>9553</v>
@@ -47784,7 +47784,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1635" t="n">
-        <v>1.00883769989014</v>
+        <v>1.00883781909943</v>
       </c>
       <c r="H1635" t="n">
         <v>1089</v>
@@ -47842,7 +47842,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.99983024597168</v>
+        <v>0.999830305576324</v>
       </c>
       <c r="H1637" t="n">
         <v>2420</v>
@@ -47871,7 +47871,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.99983024597168</v>
+        <v>0.999830305576324</v>
       </c>
       <c r="H1638" t="n">
         <v>0</v>
@@ -48480,7 +48480,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1659" t="n">
-        <v>0.927770495414734</v>
+        <v>0.927770435810089</v>
       </c>
       <c r="H1659" t="n">
         <v>750</v>
@@ -48509,7 +48509,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.927770495414734</v>
+        <v>0.927770435810089</v>
       </c>
       <c r="H1660" t="n">
         <v>31417</v>
@@ -48567,7 +48567,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.914259254932404</v>
+        <v>0.914259195327759</v>
       </c>
       <c r="H1662" t="n">
         <v>2300</v>
@@ -48596,7 +48596,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.914259254932404</v>
+        <v>0.914259195327759</v>
       </c>
       <c r="H1663" t="n">
         <v>0</v>
@@ -48654,7 +48654,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.927770495414734</v>
+        <v>0.927770435810089</v>
       </c>
       <c r="H1665" t="n">
         <v>5149</v>
@@ -49205,7 +49205,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.927770495414734</v>
+        <v>0.927770435810089</v>
       </c>
       <c r="H1684" t="n">
         <v>3455</v>
@@ -49234,7 +49234,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1685" t="n">
-        <v>0.914259254932404</v>
+        <v>0.914259195327759</v>
       </c>
       <c r="H1685" t="n">
         <v>2370</v>
@@ -49350,7 +49350,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.914259254932404</v>
+        <v>0.914259195327759</v>
       </c>
       <c r="H1689" t="n">
         <v>8867</v>
@@ -49379,7 +49379,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.914259254932404</v>
+        <v>0.914259195327759</v>
       </c>
       <c r="H1690" t="n">
         <v>1079</v>
@@ -49408,7 +49408,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.914259254932404</v>
+        <v>0.914259195327759</v>
       </c>
       <c r="H1691" t="n">
         <v>628</v>
@@ -49466,7 +49466,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1693" t="n">
-        <v>0.927770495414734</v>
+        <v>0.927770435810089</v>
       </c>
       <c r="H1693" t="n">
         <v>2</v>
@@ -49495,7 +49495,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1694" t="n">
-        <v>0.914259254932404</v>
+        <v>0.914259195327759</v>
       </c>
       <c r="H1694" t="n">
         <v>150</v>
@@ -49524,7 +49524,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.914259254932404</v>
+        <v>0.914259195327759</v>
       </c>
       <c r="H1695" t="n">
         <v>4</v>
@@ -49553,7 +49553,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.914259254932404</v>
+        <v>0.914259195327759</v>
       </c>
       <c r="H1696" t="n">
         <v>30800</v>
@@ -49582,7 +49582,7 @@
         <v>1</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1697" t="n">
         <v>4500</v>
@@ -49611,7 +49611,7 @@
         <v>1</v>
       </c>
       <c r="G1698" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1698" t="n">
         <v>0</v>
@@ -49669,7 +49669,7 @@
         <v>1</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1700" t="n">
         <v>3000</v>
@@ -49698,7 +49698,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.891740500926971</v>
+        <v>0.891740560531616</v>
       </c>
       <c r="H1701" t="n">
         <v>10301</v>
@@ -49727,7 +49727,7 @@
         <v>1</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1702" t="n">
         <v>154</v>
@@ -49843,7 +49843,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.880931615829468</v>
+        <v>0.880931556224823</v>
       </c>
       <c r="H1706" t="n">
         <v>58809</v>
@@ -49930,7 +49930,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1709" t="n">
         <v>1400</v>
@@ -50017,7 +50017,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.891740500926971</v>
+        <v>0.891740560531616</v>
       </c>
       <c r="H1712" t="n">
         <v>24561</v>
@@ -50075,7 +50075,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1714" t="n">
         <v>10700</v>
@@ -50104,7 +50104,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1715" t="n">
         <v>3100</v>
@@ -50162,7 +50162,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.853909134864807</v>
+        <v>0.853909075260162</v>
       </c>
       <c r="H1717" t="n">
         <v>4061</v>
@@ -50481,7 +50481,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.879130065441132</v>
+        <v>0.879130005836487</v>
       </c>
       <c r="H1728" t="n">
         <v>28923</v>
@@ -50539,7 +50539,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G1730" t="n">
-        <v>0.880931615829468</v>
+        <v>0.880931556224823</v>
       </c>
       <c r="H1730" t="n">
         <v>9067</v>
@@ -50713,7 +50713,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1736" t="n">
         <v>2370</v>
@@ -50742,7 +50742,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1737" t="n">
         <v>2250</v>
@@ -50771,7 +50771,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1738" t="n">
         <v>0</v>
@@ -50858,7 +50858,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1741" t="n">
         <v>100</v>
@@ -50945,7 +50945,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.852107644081116</v>
+        <v>0.852107584476471</v>
       </c>
       <c r="H1744" t="n">
         <v>4015</v>
@@ -50974,7 +50974,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1745" t="n">
         <v>3250</v>
@@ -51061,7 +51061,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.861115097999573</v>
+        <v>0.861115038394928</v>
       </c>
       <c r="H1748" t="n">
         <v>2975</v>
@@ -51090,7 +51090,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1749" t="n">
         <v>2745</v>
@@ -51148,7 +51148,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1751" t="n">
         <v>3725</v>
@@ -51206,7 +51206,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1753" t="n">
         <v>2600</v>
@@ -51235,7 +51235,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.852107644081116</v>
+        <v>0.852107584476471</v>
       </c>
       <c r="H1754" t="n">
         <v>2661</v>
@@ -51409,7 +51409,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.853909134864807</v>
+        <v>0.853909075260162</v>
       </c>
       <c r="H1760" t="n">
         <v>800</v>
@@ -51438,7 +51438,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.853909134864807</v>
+        <v>0.853909075260162</v>
       </c>
       <c r="H1761" t="n">
         <v>0</v>
@@ -51612,7 +51612,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.880931615829468</v>
+        <v>0.880931556224823</v>
       </c>
       <c r="H1767" t="n">
         <v>10300</v>
@@ -51815,7 +51815,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1774" t="n">
         <v>1000</v>
@@ -52279,7 +52279,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.861115097999573</v>
+        <v>0.861115038394928</v>
       </c>
       <c r="H1790" t="n">
         <v>16846</v>
@@ -52627,7 +52627,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1802" t="n">
-        <v>0.927770495414734</v>
+        <v>0.927770435810089</v>
       </c>
       <c r="H1802" t="n">
         <v>66891</v>
@@ -52656,7 +52656,7 @@
         <v>1</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1803" t="n">
         <v>62498</v>
@@ -52830,7 +52830,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.914259254932404</v>
+        <v>0.914259195327759</v>
       </c>
       <c r="H1809" t="n">
         <v>2913</v>
@@ -52859,7 +52859,7 @@
         <v>1</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1810" t="n">
         <v>29198</v>
@@ -52946,7 +52946,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1813" t="n">
-        <v>0.927770495414734</v>
+        <v>0.927770435810089</v>
       </c>
       <c r="H1813" t="n">
         <v>56846</v>
@@ -52975,7 +52975,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.927770495414734</v>
+        <v>0.927770435810089</v>
       </c>
       <c r="H1814" t="n">
         <v>42120</v>
@@ -53062,7 +53062,7 @@
         <v>1</v>
       </c>
       <c r="G1817" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1817" t="n">
         <v>22937</v>
@@ -53091,7 +53091,7 @@
         <v>1</v>
       </c>
       <c r="G1818" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1818" t="n">
         <v>20841</v>
@@ -53120,7 +53120,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1819" t="n">
-        <v>0.891740500926971</v>
+        <v>0.891740560531616</v>
       </c>
       <c r="H1819" t="n">
         <v>26772</v>
@@ -53178,7 +53178,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G1821" t="n">
-        <v>0.880931615829468</v>
+        <v>0.880931556224823</v>
       </c>
       <c r="H1821" t="n">
         <v>35862</v>
@@ -53265,7 +53265,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1824" t="n">
         <v>30101</v>
@@ -53410,7 +53410,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.891740500926971</v>
+        <v>0.891740560531616</v>
       </c>
       <c r="H1829" t="n">
         <v>29257</v>
@@ -53816,7 +53816,7 @@
         <v>1</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1843" t="n">
         <v>67983</v>
@@ -53903,7 +53903,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.864718079566956</v>
+        <v>0.8647181391716</v>
       </c>
       <c r="H1846" t="n">
         <v>5725</v>
@@ -54077,7 +54077,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.891740500926971</v>
+        <v>0.891740560531616</v>
       </c>
       <c r="H1852" t="n">
         <v>55567</v>
@@ -54251,7 +54251,7 @@
         <v>1</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1858" t="n">
         <v>300</v>
@@ -54309,7 +54309,7 @@
         <v>1</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1860" t="n">
         <v>1301</v>
@@ -54454,7 +54454,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.927770495414734</v>
+        <v>0.927770435810089</v>
       </c>
       <c r="H1865" t="n">
         <v>14050</v>
@@ -54570,7 +54570,7 @@
         <v>1</v>
       </c>
       <c r="G1869" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1869" t="n">
         <v>450</v>
@@ -54599,7 +54599,7 @@
         <v>1</v>
       </c>
       <c r="G1870" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1870" t="n">
         <v>2550</v>
@@ -54628,7 +54628,7 @@
         <v>1</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1871" t="n">
         <v>3150</v>
@@ -54686,7 +54686,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1873" t="n">
-        <v>0.891740500926971</v>
+        <v>0.891740560531616</v>
       </c>
       <c r="H1873" t="n">
         <v>75</v>
@@ -54773,7 +54773,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.891740500926971</v>
+        <v>0.891740560531616</v>
       </c>
       <c r="H1876" t="n">
         <v>150</v>
@@ -54802,7 +54802,7 @@
         <v>1</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.900748074054718</v>
+        <v>0.900748014450073</v>
       </c>
       <c r="H1877" t="n">
         <v>18100</v>
@@ -54947,7 +54947,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.973739683628082</v>
+        <v>0.973739743232727</v>
       </c>
       <c r="H1882" t="n">
         <v>5013</v>
@@ -54976,7 +54976,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.973739683628082</v>
+        <v>0.973739743232727</v>
       </c>
       <c r="H1883" t="n">
         <v>151</v>
@@ -55005,7 +55005,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.964465975761414</v>
+        <v>0.964465916156769</v>
       </c>
       <c r="H1884" t="n">
         <v>109816</v>
@@ -55034,7 +55034,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.950555384159088</v>
+        <v>0.950555443763733</v>
       </c>
       <c r="H1885" t="n">
         <v>142128</v>
@@ -55063,7 +55063,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.969102799892426</v>
+        <v>0.969102740287781</v>
       </c>
       <c r="H1886" t="n">
         <v>112863</v>
@@ -55092,7 +55092,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.973739683628082</v>
+        <v>0.973739743232727</v>
       </c>
       <c r="H1887" t="n">
         <v>60000</v>
@@ -55121,7 +55121,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.973739683628082</v>
+        <v>0.973739743232727</v>
       </c>
       <c r="H1888" t="n">
         <v>2500</v>
@@ -55150,7 +55150,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.00156092643738</v>
+        <v>1.00156080722809</v>
       </c>
       <c r="H1889" t="n">
         <v>9000</v>
@@ -55237,7 +55237,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.00156092643738</v>
+        <v>1.00156080722809</v>
       </c>
       <c r="H1892" t="n">
         <v>5606</v>
@@ -55324,7 +55324,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.996924161911011</v>
+        <v>0.996924102306366</v>
       </c>
       <c r="H1895" t="n">
         <v>7967</v>
@@ -55382,7 +55382,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.01547133922577</v>
+        <v>1.01547145843506</v>
       </c>
       <c r="H1897" t="n">
         <v>6602</v>
@@ -55440,7 +55440,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.00156092643738</v>
+        <v>1.00156080722809</v>
       </c>
       <c r="H1899" t="n">
         <v>5515</v>
@@ -55469,7 +55469,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1900" t="n">
-        <v>0.996924161911011</v>
+        <v>0.996924102306366</v>
       </c>
       <c r="H1900" t="n">
         <v>1050</v>
@@ -55817,7 +55817,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1912" t="n">
-        <v>0.969102799892426</v>
+        <v>0.969102740287781</v>
       </c>
       <c r="H1912" t="n">
         <v>6540</v>
@@ -56078,7 +56078,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.914387941360474</v>
+        <v>0.914388000965118</v>
       </c>
       <c r="H1921" t="n">
         <v>2360</v>
@@ -56136,7 +56136,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1923" t="n">
-        <v>0.914387941360474</v>
+        <v>0.914388000965118</v>
       </c>
       <c r="H1923" t="n">
         <v>27300</v>
@@ -56165,7 +56165,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.914387941360474</v>
+        <v>0.914388000965118</v>
       </c>
       <c r="H1924" t="n">
         <v>15358</v>
@@ -56339,7 +56339,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1930" t="n">
-        <v>0.950555384159088</v>
+        <v>0.950555443763733</v>
       </c>
       <c r="H1930" t="n">
         <v>50550</v>
@@ -56571,7 +56571,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.969102799892426</v>
+        <v>0.969102740287781</v>
       </c>
       <c r="H1938" t="n">
         <v>42300</v>
@@ -56600,7 +56600,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1939" t="n">
-        <v>0.969102799892426</v>
+        <v>0.969102740287781</v>
       </c>
       <c r="H1939" t="n">
         <v>500</v>
@@ -56629,7 +56629,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1940" t="n">
-        <v>0.969102799892426</v>
+        <v>0.969102740287781</v>
       </c>
       <c r="H1940" t="n">
         <v>2700</v>
@@ -56658,7 +56658,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.969102799892426</v>
+        <v>0.969102740287781</v>
       </c>
       <c r="H1941" t="n">
         <v>18525</v>
@@ -56861,7 +56861,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1948" t="n">
-        <v>0.950555384159088</v>
+        <v>0.950555443763733</v>
       </c>
       <c r="H1948" t="n">
         <v>2178</v>
@@ -56948,7 +56948,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.00156092643738</v>
+        <v>1.00156080722809</v>
       </c>
       <c r="H1951" t="n">
         <v>59726</v>
@@ -57006,7 +57006,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1953" t="n">
-        <v>0.973739683628082</v>
+        <v>0.973739743232727</v>
       </c>
       <c r="H1953" t="n">
         <v>12091</v>
@@ -57035,7 +57035,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1954" t="n">
-        <v>0.973739683628082</v>
+        <v>0.973739743232727</v>
       </c>
       <c r="H1954" t="n">
         <v>10600</v>
@@ -57180,7 +57180,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.964465975761414</v>
+        <v>0.964465916156769</v>
       </c>
       <c r="H1959" t="n">
         <v>7477</v>
@@ -57238,7 +57238,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1961" t="n">
-        <v>0.964465975761414</v>
+        <v>0.964465916156769</v>
       </c>
       <c r="H1961" t="n">
         <v>11399</v>
@@ -57354,7 +57354,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1965" t="n">
-        <v>0.964465975761414</v>
+        <v>0.964465916156769</v>
       </c>
       <c r="H1965" t="n">
         <v>26101</v>
@@ -57383,7 +57383,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1966" t="n">
-        <v>0.964465975761414</v>
+        <v>0.964465916156769</v>
       </c>
       <c r="H1966" t="n">
         <v>44563</v>
@@ -57412,7 +57412,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1967" t="n">
-        <v>0.964465975761414</v>
+        <v>0.964465916156769</v>
       </c>
       <c r="H1967" t="n">
         <v>107588</v>
@@ -57499,7 +57499,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1970" t="n">
-        <v>0.973739683628082</v>
+        <v>0.973739743232727</v>
       </c>
       <c r="H1970" t="n">
         <v>49360</v>
@@ -57528,7 +57528,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.964465975761414</v>
+        <v>0.964465916156769</v>
       </c>
       <c r="H1971" t="n">
         <v>29685</v>
@@ -57557,7 +57557,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1972" t="n">
-        <v>0.969102799892426</v>
+        <v>0.969102740287781</v>
       </c>
       <c r="H1972" t="n">
         <v>40554</v>
@@ -57586,7 +57586,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1973" t="n">
-        <v>0.973739683628082</v>
+        <v>0.973739743232727</v>
       </c>
       <c r="H1973" t="n">
         <v>4588</v>
@@ -57644,7 +57644,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1975" t="n">
-        <v>0.950555384159088</v>
+        <v>0.950555443763733</v>
       </c>
       <c r="H1975" t="n">
         <v>13668</v>
@@ -57905,7 +57905,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1984" t="n">
-        <v>0.969102799892426</v>
+        <v>0.969102740287781</v>
       </c>
       <c r="H1984" t="n">
         <v>2601</v>
@@ -57934,7 +57934,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1985" t="n">
-        <v>0.964465975761414</v>
+        <v>0.964465916156769</v>
       </c>
       <c r="H1985" t="n">
         <v>4600</v>
@@ -57963,7 +57963,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1986" t="n">
-        <v>0.950555384159088</v>
+        <v>0.950555443763733</v>
       </c>
       <c r="H1986" t="n">
         <v>150</v>
@@ -57992,7 +57992,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1987" t="n">
-        <v>0.950555384159088</v>
+        <v>0.950555443763733</v>
       </c>
       <c r="H1987" t="n">
         <v>1210</v>
@@ -58920,7 +58920,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2019" t="n">
-        <v>0.925516366958618</v>
+        <v>0.925516426563263</v>
       </c>
       <c r="H2019" t="n">
         <v>15750</v>
@@ -58978,7 +58978,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2021" t="n">
-        <v>0.925516366958618</v>
+        <v>0.925516426563263</v>
       </c>
       <c r="H2021" t="n">
         <v>20500</v>
@@ -59152,7 +59152,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G2027" t="n">
-        <v>0.910678505897522</v>
+        <v>0.910678446292877</v>
       </c>
       <c r="H2027" t="n">
         <v>25164</v>
@@ -59181,7 +59181,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2028" t="n">
-        <v>0.916242718696594</v>
+        <v>0.916242659091949</v>
       </c>
       <c r="H2028" t="n">
         <v>36510</v>
@@ -59210,7 +59210,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G2029" t="n">
-        <v>0.914387941360474</v>
+        <v>0.914388000965118</v>
       </c>
       <c r="H2029" t="n">
         <v>12021</v>
@@ -59239,7 +59239,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G2030" t="n">
-        <v>0.912533164024353</v>
+        <v>0.912533223628998</v>
       </c>
       <c r="H2030" t="n">
         <v>9605</v>
@@ -59355,7 +59355,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2034" t="n">
-        <v>0.925516366958618</v>
+        <v>0.925516426563263</v>
       </c>
       <c r="H2034" t="n">
         <v>6338</v>
@@ -59413,7 +59413,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G2036" t="n">
-        <v>0.916242718696594</v>
+        <v>0.916242659091949</v>
       </c>
       <c r="H2036" t="n">
         <v>3911</v>
@@ -59587,7 +59587,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G2042" t="n">
-        <v>0.914387941360474</v>
+        <v>0.914388000965118</v>
       </c>
       <c r="H2042" t="n">
         <v>3600</v>
@@ -59616,7 +59616,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2043" t="n">
-        <v>0.925516366958618</v>
+        <v>0.925516426563263</v>
       </c>
       <c r="H2043" t="n">
         <v>31100</v>
@@ -59674,7 +59674,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2045" t="n">
-        <v>0.925516366958618</v>
+        <v>0.925516426563263</v>
       </c>
       <c r="H2045" t="n">
         <v>48520</v>
@@ -59848,7 +59848,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2051" t="n">
-        <v>0.925516366958618</v>
+        <v>0.925516426563263</v>
       </c>
       <c r="H2051" t="n">
         <v>13836</v>
@@ -60138,7 +60138,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G2061" t="n">
-        <v>0.925516366958618</v>
+        <v>0.925516426563263</v>
       </c>
       <c r="H2061" t="n">
         <v>30418</v>
@@ -60486,7 +60486,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G2073" t="n">
-        <v>0.950555384159088</v>
+        <v>0.950555443763733</v>
       </c>
       <c r="H2073" t="n">
         <v>16918</v>
@@ -60544,7 +60544,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G2075" t="n">
-        <v>0.996924161911011</v>
+        <v>0.996924102306366</v>
       </c>
       <c r="H2075" t="n">
         <v>140712</v>
@@ -60602,7 +60602,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2077" t="n">
-        <v>0.978376507759094</v>
+        <v>0.978376567363739</v>
       </c>
       <c r="H2077" t="n">
         <v>56267</v>
@@ -60631,7 +60631,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2078" t="n">
-        <v>0.978376507759094</v>
+        <v>0.978376567363739</v>
       </c>
       <c r="H2078" t="n">
         <v>4334</v>
@@ -60660,7 +60660,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G2079" t="n">
-        <v>0.964465975761414</v>
+        <v>0.964465916156769</v>
       </c>
       <c r="H2079" t="n">
         <v>39147</v>
@@ -60689,7 +60689,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2080" t="n">
-        <v>0.978376507759094</v>
+        <v>0.978376567363739</v>
       </c>
       <c r="H2080" t="n">
         <v>34229</v>
@@ -60805,7 +60805,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G2084" t="n">
-        <v>0.969102799892426</v>
+        <v>0.969102740287781</v>
       </c>
       <c r="H2084" t="n">
         <v>13170</v>
@@ -61124,7 +61124,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G2095" t="n">
-        <v>0.978376507759094</v>
+        <v>0.978376567363739</v>
       </c>
       <c r="H2095" t="n">
         <v>60899</v>
@@ -61327,7 +61327,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G2102" t="n">
-        <v>1.02474510669708</v>
+        <v>1.02474522590637</v>
       </c>
       <c r="H2102" t="n">
         <v>42742</v>
@@ -61443,7 +61443,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2106" t="n">
-        <v>1.0572030544281</v>
+        <v>1.05720317363739</v>
       </c>
       <c r="H2106" t="n">
         <v>19244</v>
@@ -61588,7 +61588,7 @@
         <v>1.125</v>
       </c>
       <c r="G2111" t="n">
-        <v>1.04329264163971</v>
+        <v>1.04329252243042</v>
       </c>
       <c r="H2111" t="n">
         <v>69011</v>
@@ -61617,7 +61617,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2112" t="n">
-        <v>1.0572030544281</v>
+        <v>1.05720317363739</v>
       </c>
       <c r="H2112" t="n">
         <v>6000</v>
@@ -61704,7 +61704,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2115" t="n">
-        <v>1.0572030544281</v>
+        <v>1.05720317363739</v>
       </c>
       <c r="H2115" t="n">
         <v>33866</v>
@@ -61733,7 +61733,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.07111358642578</v>
+        <v>1.07111370563507</v>
       </c>
       <c r="H2116" t="n">
         <v>73758</v>
@@ -61762,7 +61762,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2117" t="n">
-        <v>1.0572030544281</v>
+        <v>1.05720317363739</v>
       </c>
       <c r="H2117" t="n">
         <v>10294</v>
@@ -61849,7 +61849,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G2120" t="n">
-        <v>1.02474510669708</v>
+        <v>1.02474522590637</v>
       </c>
       <c r="H2120" t="n">
         <v>121338</v>
@@ -62023,7 +62023,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G2126" t="n">
-        <v>1.0572030544281</v>
+        <v>1.05720317363739</v>
       </c>
       <c r="H2126" t="n">
         <v>110587</v>
@@ -62052,7 +62052,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G2127" t="n">
-        <v>1.10357165336609</v>
+        <v>1.10357177257538</v>
       </c>
       <c r="H2127" t="n">
         <v>118531</v>
@@ -62081,7 +62081,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G2128" t="n">
-        <v>1.08966112136841</v>
+        <v>1.08966100215912</v>
       </c>
       <c r="H2128" t="n">
         <v>56546</v>
@@ -62110,7 +62110,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G2129" t="n">
-        <v>1.08038723468781</v>
+        <v>1.08038735389709</v>
       </c>
       <c r="H2129" t="n">
         <v>16745</v>
@@ -62545,7 +62545,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2144" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2144" t="n">
         <v>29824</v>
@@ -62632,7 +62632,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2147" t="n">
-        <v>1.19028902053833</v>
+        <v>1.19028890132904</v>
       </c>
       <c r="H2147" t="n">
         <v>24981</v>
@@ -62661,7 +62661,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2148" t="n">
-        <v>1.19028902053833</v>
+        <v>1.19028890132904</v>
       </c>
       <c r="H2148" t="n">
         <v>57923</v>
@@ -62690,7 +62690,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G2149" t="n">
-        <v>1.19508850574493</v>
+        <v>1.19508862495422</v>
       </c>
       <c r="H2149" t="n">
         <v>51407</v>
@@ -62864,7 +62864,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G2155" t="n">
-        <v>1.32467651367188</v>
+        <v>1.32467639446259</v>
       </c>
       <c r="H2155" t="n">
         <v>33041</v>
@@ -62893,7 +62893,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2156" t="n">
-        <v>1.33427548408508</v>
+        <v>1.33427560329437</v>
       </c>
       <c r="H2156" t="n">
         <v>11294</v>
@@ -63009,7 +63009,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G2160" t="n">
-        <v>1.32467651367188</v>
+        <v>1.32467639446259</v>
       </c>
       <c r="H2160" t="n">
         <v>18536</v>
@@ -63154,7 +63154,7 @@
         <v>1.2849999666214</v>
       </c>
       <c r="G2165" t="n">
-        <v>1.23348486423492</v>
+        <v>1.23348498344421</v>
       </c>
       <c r="H2165" t="n">
         <v>2443</v>
@@ -63415,7 +63415,7 @@
         <v>1.25</v>
       </c>
       <c r="G2174" t="n">
-        <v>1.19988799095154</v>
+        <v>1.19988811016083</v>
       </c>
       <c r="H2174" t="n">
         <v>7821</v>
@@ -63444,7 +63444,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G2175" t="n">
-        <v>1.19508850574493</v>
+        <v>1.19508862495422</v>
       </c>
       <c r="H2175" t="n">
         <v>18538</v>
@@ -63792,7 +63792,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2187" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2187" t="n">
         <v>15397</v>
@@ -64169,7 +64169,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2200" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2200" t="n">
         <v>13236</v>
@@ -64198,7 +64198,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2201" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2201" t="n">
         <v>3180</v>
@@ -64227,7 +64227,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2202" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2202" t="n">
         <v>6761</v>
@@ -64256,7 +64256,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2203" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2203" t="n">
         <v>5800</v>
@@ -64343,7 +64343,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2206" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2206" t="n">
         <v>9450</v>
@@ -64401,7 +64401,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G2208" t="n">
-        <v>1.16629123687744</v>
+        <v>1.16629135608673</v>
       </c>
       <c r="H2208" t="n">
         <v>24150</v>
@@ -64488,7 +64488,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2211" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2211" t="n">
         <v>6800</v>
@@ -64546,7 +64546,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2213" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2213" t="n">
         <v>21456</v>
@@ -64575,7 +64575,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2214" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2214" t="n">
         <v>6990</v>
@@ -64633,7 +64633,7 @@
         <v>1.25</v>
       </c>
       <c r="G2216" t="n">
-        <v>1.19988799095154</v>
+        <v>1.19988811016083</v>
       </c>
       <c r="H2216" t="n">
         <v>8232</v>
@@ -64662,7 +64662,7 @@
         <v>1.25</v>
       </c>
       <c r="G2217" t="n">
-        <v>1.19988799095154</v>
+        <v>1.19988811016083</v>
       </c>
       <c r="H2217" t="n">
         <v>16601</v>
@@ -64720,7 +64720,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G2219" t="n">
-        <v>1.19028902053833</v>
+        <v>1.19028890132904</v>
       </c>
       <c r="H2219" t="n">
         <v>9910</v>
@@ -64749,7 +64749,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G2220" t="n">
-        <v>1.19508850574493</v>
+        <v>1.19508862495422</v>
       </c>
       <c r="H2220" t="n">
         <v>19197</v>
@@ -64778,7 +64778,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G2221" t="n">
-        <v>1.18548953533173</v>
+        <v>1.18548941612244</v>
       </c>
       <c r="H2221" t="n">
         <v>40525</v>
@@ -64807,7 +64807,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2222" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2222" t="n">
         <v>2315</v>
@@ -64836,7 +64836,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G2223" t="n">
-        <v>1.18548953533173</v>
+        <v>1.18548941612244</v>
       </c>
       <c r="H2223" t="n">
         <v>10318</v>
@@ -64865,7 +64865,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G2224" t="n">
-        <v>1.18548953533173</v>
+        <v>1.18548941612244</v>
       </c>
       <c r="H2224" t="n">
         <v>1650</v>
@@ -64923,7 +64923,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G2226" t="n">
-        <v>1.20468771457672</v>
+        <v>1.20468759536743</v>
       </c>
       <c r="H2226" t="n">
         <v>42492</v>
@@ -64952,7 +64952,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2227" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2227" t="n">
         <v>80550</v>
@@ -64981,7 +64981,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G2228" t="n">
-        <v>1.20468771457672</v>
+        <v>1.20468759536743</v>
       </c>
       <c r="H2228" t="n">
         <v>29000</v>
@@ -65010,7 +65010,7 @@
         <v>1.25</v>
       </c>
       <c r="G2229" t="n">
-        <v>1.19988799095154</v>
+        <v>1.19988811016083</v>
       </c>
       <c r="H2229" t="n">
         <v>29389</v>
@@ -65039,7 +65039,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G2230" t="n">
-        <v>1.16629123687744</v>
+        <v>1.16629135608673</v>
       </c>
       <c r="H2230" t="n">
         <v>131700</v>
@@ -65068,7 +65068,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G2231" t="n">
-        <v>1.19508850574493</v>
+        <v>1.19508862495422</v>
       </c>
       <c r="H2231" t="n">
         <v>44838</v>
@@ -65126,7 +65126,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2233" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2233" t="n">
         <v>4710</v>
@@ -65184,7 +65184,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2235" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2235" t="n">
         <v>17400</v>
@@ -65213,7 +65213,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G2236" t="n">
-        <v>1.18068981170654</v>
+        <v>1.18068993091583</v>
       </c>
       <c r="H2236" t="n">
         <v>26380</v>
@@ -65242,7 +65242,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G2237" t="n">
-        <v>1.19508850574493</v>
+        <v>1.19508862495422</v>
       </c>
       <c r="H2237" t="n">
         <v>24348</v>
@@ -65271,7 +65271,7 @@
         <v>1.25</v>
       </c>
       <c r="G2238" t="n">
-        <v>1.19988799095154</v>
+        <v>1.19988811016083</v>
       </c>
       <c r="H2238" t="n">
         <v>36307</v>
@@ -65300,7 +65300,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G2239" t="n">
-        <v>1.24788355827332</v>
+        <v>1.2478836774826</v>
       </c>
       <c r="H2239" t="n">
         <v>185336</v>
@@ -65329,7 +65329,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G2240" t="n">
-        <v>1.2766809463501</v>
+        <v>1.27668106555939</v>
       </c>
       <c r="H2240" t="n">
         <v>26857</v>
@@ -65358,7 +65358,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G2241" t="n">
-        <v>1.27188146114349</v>
+        <v>1.2718813419342</v>
       </c>
       <c r="H2241" t="n">
         <v>20494</v>
@@ -65474,7 +65474,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G2245" t="n">
-        <v>1.25268304347992</v>
+        <v>1.25268316268921</v>
       </c>
       <c r="H2245" t="n">
         <v>21670</v>
@@ -65503,7 +65503,7 @@
         <v>1.30499994754791</v>
       </c>
       <c r="G2246" t="n">
-        <v>1.25268304347992</v>
+        <v>1.25268316268921</v>
       </c>
       <c r="H2246" t="n">
         <v>8800</v>
@@ -65532,7 +65532,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G2247" t="n">
-        <v>1.27188146114349</v>
+        <v>1.2718813419342</v>
       </c>
       <c r="H2247" t="n">
         <v>40349</v>
@@ -65677,7 +65677,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G2252" t="n">
-        <v>1.32947599887848</v>
+        <v>1.32947587966919</v>
       </c>
       <c r="H2252" t="n">
         <v>20036</v>
@@ -65735,7 +65735,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2254" t="n">
-        <v>1.33427548408508</v>
+        <v>1.33427560329437</v>
       </c>
       <c r="H2254" t="n">
         <v>5150</v>
@@ -65822,7 +65822,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2257" t="n">
-        <v>1.33427548408508</v>
+        <v>1.33427560329437</v>
       </c>
       <c r="H2257" t="n">
         <v>24150</v>
@@ -65909,7 +65909,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G2260" t="n">
-        <v>1.30547821521759</v>
+        <v>1.30547833442688</v>
       </c>
       <c r="H2260" t="n">
         <v>34625</v>
@@ -65938,7 +65938,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G2261" t="n">
-        <v>1.32467651367188</v>
+        <v>1.32467639446259</v>
       </c>
       <c r="H2261" t="n">
         <v>23782</v>
@@ -65967,7 +65967,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2262" t="n">
-        <v>1.33427548408508</v>
+        <v>1.33427560329437</v>
       </c>
       <c r="H2262" t="n">
         <v>5324</v>
@@ -66025,7 +66025,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2264" t="n">
-        <v>1.33427548408508</v>
+        <v>1.33427560329437</v>
       </c>
       <c r="H2264" t="n">
         <v>2822</v>
@@ -66054,7 +66054,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2265" t="n">
-        <v>1.33427548408508</v>
+        <v>1.33427560329437</v>
       </c>
       <c r="H2265" t="n">
         <v>2104</v>
@@ -66083,7 +66083,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G2266" t="n">
-        <v>1.32467651367188</v>
+        <v>1.32467639446259</v>
       </c>
       <c r="H2266" t="n">
         <v>20202</v>
@@ -66373,7 +66373,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G2276" t="n">
-        <v>1.38227117061615</v>
+        <v>1.38227105140686</v>
       </c>
       <c r="H2276" t="n">
         <v>87747</v>
@@ -66460,7 +66460,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G2279" t="n">
-        <v>1.39187014102936</v>
+        <v>1.39187026023865</v>
       </c>
       <c r="H2279" t="n">
         <v>120217</v>
@@ -66489,7 +66489,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G2280" t="n">
-        <v>1.38707065582275</v>
+        <v>1.38707077503204</v>
       </c>
       <c r="H2280" t="n">
         <v>29004</v>
@@ -66518,7 +66518,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G2281" t="n">
-        <v>1.37267184257507</v>
+        <v>1.37267196178436</v>
       </c>
       <c r="H2281" t="n">
         <v>21713</v>
@@ -66547,7 +66547,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G2282" t="n">
-        <v>1.37267184257507</v>
+        <v>1.37267196178436</v>
       </c>
       <c r="H2282" t="n">
         <v>45528</v>
@@ -66576,7 +66576,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G2283" t="n">
-        <v>1.37267184257507</v>
+        <v>1.37267196178436</v>
       </c>
       <c r="H2283" t="n">
         <v>12184</v>
@@ -66663,7 +66663,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G2286" t="n">
-        <v>1.32947599887848</v>
+        <v>1.32947587966919</v>
       </c>
       <c r="H2286" t="n">
         <v>16249</v>
@@ -66692,7 +66692,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2287" t="n">
-        <v>1.33427548408508</v>
+        <v>1.33427560329437</v>
       </c>
       <c r="H2287" t="n">
         <v>4550</v>
@@ -66721,7 +66721,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2288" t="n">
-        <v>1.33427548408508</v>
+        <v>1.33427560329437</v>
       </c>
       <c r="H2288" t="n">
         <v>4900</v>
@@ -66779,7 +66779,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G2290" t="n">
-        <v>1.33427548408508</v>
+        <v>1.33427560329437</v>
       </c>
       <c r="H2290" t="n">
         <v>18915</v>
@@ -66924,7 +66924,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G2295" t="n">
-        <v>1.37747156620026</v>
+        <v>1.37747144699097</v>
       </c>
       <c r="H2295" t="n">
         <v>45778</v>
@@ -66953,7 +66953,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G2296" t="n">
-        <v>1.37747156620026</v>
+        <v>1.37747144699097</v>
       </c>
       <c r="H2296" t="n">
         <v>6019</v>
@@ -67011,7 +67011,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2298" t="n">
-        <v>1.41106843948364</v>
+        <v>1.41106832027435</v>
       </c>
       <c r="H2298" t="n">
         <v>64779</v>
@@ -67040,7 +67040,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2299" t="n">
-        <v>1.41106843948364</v>
+        <v>1.41106832027435</v>
       </c>
       <c r="H2299" t="n">
         <v>11452</v>
@@ -67098,7 +67098,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G2301" t="n">
-        <v>1.46866297721863</v>
+        <v>1.46866309642792</v>
       </c>
       <c r="H2301" t="n">
         <v>86211</v>
@@ -67156,7 +67156,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G2303" t="n">
-        <v>1.46866297721863</v>
+        <v>1.46866309642792</v>
       </c>
       <c r="H2303" t="n">
         <v>26679</v>
@@ -67214,7 +67214,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G2305" t="n">
-        <v>1.46866297721863</v>
+        <v>1.46866309642792</v>
       </c>
       <c r="H2305" t="n">
         <v>8550</v>
@@ -67243,7 +67243,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2306" t="n">
-        <v>1.5214581489563</v>
+        <v>1.52145802974701</v>
       </c>
       <c r="H2306" t="n">
         <v>199616</v>
@@ -67301,7 +67301,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2308" t="n">
-        <v>1.5262576341629</v>
+        <v>1.52625775337219</v>
       </c>
       <c r="H2308" t="n">
         <v>25950</v>
@@ -67359,7 +67359,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G2310" t="n">
-        <v>1.5214581489563</v>
+        <v>1.52145802974701</v>
       </c>
       <c r="H2310" t="n">
         <v>14208</v>
@@ -67446,7 +67446,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2313" t="n">
-        <v>1.56465399265289</v>
+        <v>1.56465411186218</v>
       </c>
       <c r="H2313" t="n">
         <v>40702</v>
@@ -67475,7 +67475,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G2314" t="n">
-        <v>1.57425320148468</v>
+        <v>1.57425308227539</v>
       </c>
       <c r="H2314" t="n">
         <v>100887</v>
@@ -67533,7 +67533,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2316" t="n">
-        <v>1.63184785842896</v>
+        <v>1.63184773921967</v>
       </c>
       <c r="H2316" t="n">
         <v>91717</v>
@@ -67562,7 +67562,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G2317" t="n">
-        <v>1.61744916439056</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H2317" t="n">
         <v>29067</v>
@@ -67620,7 +67620,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G2319" t="n">
-        <v>1.66064512729645</v>
+        <v>1.66064524650574</v>
       </c>
       <c r="H2319" t="n">
         <v>77255</v>
@@ -67765,7 +67765,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2324" t="n">
-        <v>1.70864069461823</v>
+        <v>1.70864057540894</v>
       </c>
       <c r="H2324" t="n">
         <v>110896</v>
@@ -67794,7 +67794,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2325" t="n">
-        <v>1.71823966503143</v>
+        <v>1.71823978424072</v>
       </c>
       <c r="H2325" t="n">
         <v>87009</v>
@@ -67823,7 +67823,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2326" t="n">
-        <v>1.74703705310822</v>
+        <v>1.7470371723175</v>
       </c>
       <c r="H2326" t="n">
         <v>60642</v>
@@ -67852,7 +67852,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G2327" t="n">
-        <v>1.75663626194</v>
+        <v>1.75663614273071</v>
       </c>
       <c r="H2327" t="n">
         <v>33986</v>
@@ -67881,7 +67881,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2328" t="n">
-        <v>1.74703705310822</v>
+        <v>1.7470371723175</v>
       </c>
       <c r="H2328" t="n">
         <v>60864</v>
@@ -67939,7 +67939,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G2330" t="n">
-        <v>1.66544461250305</v>
+        <v>1.66544473171234</v>
       </c>
       <c r="H2330" t="n">
         <v>124995</v>
@@ -67968,7 +67968,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G2331" t="n">
-        <v>1.65584564208984</v>
+        <v>1.65584552288055</v>
       </c>
       <c r="H2331" t="n">
         <v>52481</v>
@@ -68113,7 +68113,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2336" t="n">
-        <v>1.63184785842896</v>
+        <v>1.63184773921967</v>
       </c>
       <c r="H2336" t="n">
         <v>13851</v>
@@ -68142,7 +68142,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G2337" t="n">
-        <v>1.63184785842896</v>
+        <v>1.63184773921967</v>
       </c>
       <c r="H2337" t="n">
         <v>72112</v>
@@ -68200,7 +68200,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G2339" t="n">
-        <v>1.61744916439056</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H2339" t="n">
         <v>11201</v>
@@ -68258,7 +68258,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G2341" t="n">
-        <v>1.60784995555878</v>
+        <v>1.60785007476807</v>
       </c>
       <c r="H2341" t="n">
         <v>30078</v>
@@ -68345,7 +68345,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G2344" t="n">
-        <v>1.57905268669128</v>
+        <v>1.57905280590057</v>
       </c>
       <c r="H2344" t="n">
         <v>21417</v>
@@ -68519,7 +68519,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G2350" t="n">
-        <v>1.57425320148468</v>
+        <v>1.57425308227539</v>
       </c>
       <c r="H2350" t="n">
         <v>16885</v>
@@ -68606,7 +68606,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2353" t="n">
-        <v>1.56465399265289</v>
+        <v>1.56465411186218</v>
       </c>
       <c r="H2353" t="n">
         <v>71461</v>
@@ -68635,7 +68635,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G2354" t="n">
-        <v>1.57425320148468</v>
+        <v>1.57425308227539</v>
       </c>
       <c r="H2354" t="n">
         <v>16633</v>
@@ -68664,7 +68664,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G2355" t="n">
-        <v>1.53585684299469</v>
+        <v>1.5358567237854</v>
       </c>
       <c r="H2355" t="n">
         <v>26536</v>
@@ -68722,7 +68722,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G2357" t="n">
-        <v>1.46866297721863</v>
+        <v>1.46866309642792</v>
       </c>
       <c r="H2357" t="n">
         <v>60553</v>
@@ -68751,7 +68751,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G2358" t="n">
-        <v>1.5262576341629</v>
+        <v>1.52625775337219</v>
       </c>
       <c r="H2358" t="n">
         <v>36435</v>
@@ -68780,7 +68780,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G2359" t="n">
-        <v>1.46866297721863</v>
+        <v>1.46866309642792</v>
       </c>
       <c r="H2359" t="n">
         <v>46622</v>
@@ -68838,7 +68838,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G2361" t="n">
-        <v>1.51185894012451</v>
+        <v>1.5118590593338</v>
       </c>
       <c r="H2361" t="n">
         <v>36984</v>
@@ -69012,7 +69012,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G2367" t="n">
-        <v>1.61744916439056</v>
+        <v>1.61744904518127</v>
       </c>
       <c r="H2367" t="n">
         <v>35110</v>
@@ -69041,7 +69041,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G2368" t="n">
-        <v>1.71823966503143</v>
+        <v>1.71823978424072</v>
       </c>
       <c r="H2368" t="n">
         <v>117918</v>
@@ -69128,7 +69128,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G2371" t="n">
-        <v>1.70864069461823</v>
+        <v>1.70864057540894</v>
       </c>
       <c r="H2371" t="n">
         <v>34146</v>
@@ -69186,7 +69186,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G2373" t="n">
-        <v>1.71344017982483</v>
+        <v>1.71344006061554</v>
       </c>
       <c r="H2373" t="n">
         <v>35107</v>
@@ -69215,7 +69215,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2374" t="n">
-        <v>1.72783887386322</v>
+        <v>1.72783875465393</v>
       </c>
       <c r="H2374" t="n">
         <v>21867</v>
@@ -69331,7 +69331,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2378" t="n">
-        <v>1.72783887386322</v>
+        <v>1.72783875465393</v>
       </c>
       <c r="H2378" t="n">
         <v>27274</v>
@@ -69476,7 +69476,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G2383" t="n">
-        <v>1.74703705310822</v>
+        <v>1.7470371723175</v>
       </c>
       <c r="H2383" t="n">
         <v>16859</v>
@@ -80067,6 +80067,35 @@
         <v>3075</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>2.50999999046326</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>2.50999999046326</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>2.50999999046326</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>13179</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>
